--- a/SC Indicators Data Prep.xlsx
+++ b/SC Indicators Data Prep.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emree\CO3data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emree\Desktop\CO3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A609DC8B-5E03-46D2-B2F0-A955219E329C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81D52FC-EADD-46E2-A5E9-9EE84EFBA4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{55AA29CC-CDDC-4D64-AC5C-6644C21888DE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="128">
   <si>
     <t>Voted</t>
   </si>
@@ -155,12 +155,6 @@
     <t>Engagement of Citizens at EU Level</t>
   </si>
   <si>
-    <t>Role Given to CSOs</t>
-  </si>
-  <si>
-    <t>Role Given to Citizens</t>
-  </si>
-  <si>
     <t>Vote in local, national or European elections</t>
   </si>
   <si>
@@ -215,9 +209,6 @@
     <t>Trust in NATO</t>
   </si>
   <si>
-    <t>Trust</t>
-  </si>
-  <si>
     <t>Agree- I understand how the EU works</t>
   </si>
   <si>
@@ -248,9 +239,6 @@
     <t>Respect to the EU Values</t>
   </si>
   <si>
-    <t>Voice</t>
-  </si>
-  <si>
     <t>Voice in the EU</t>
   </si>
   <si>
@@ -272,12 +260,6 @@
     <t>Youth- The European Union</t>
   </si>
   <si>
-    <t>Efficacy- Youth</t>
-  </si>
-  <si>
-    <t>Voted in a local, national or European election</t>
-  </si>
-  <si>
     <t>Voting in (European or national) elections</t>
   </si>
   <si>
@@ -305,9 +287,6 @@
     <t>Sharing your views on social media platforms</t>
   </si>
   <si>
-    <t>Youth- Participation</t>
-  </si>
-  <si>
     <t>Youth-Created or signed a petition (on paper or online)</t>
   </si>
   <si>
@@ -341,13 +320,106 @@
     <t>Optimism about the EU's Future</t>
   </si>
   <si>
-    <t>COUNTRY</t>
-  </si>
-  <si>
-    <t>LEGITIMACY</t>
-  </si>
-  <si>
-    <t>Youth-Impact</t>
+    <t xml:space="preserve">Not Concerned- People voting although they are not entitled to vote </t>
+  </si>
+  <si>
+    <t>Not Concerned- The final result of an election being manipulated</t>
+  </si>
+  <si>
+    <t>Not Concerned- Plections being manipulated through cyberattacks</t>
+  </si>
+  <si>
+    <t>Not Concerned-People being pressured into voting in a particular way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Concerned-People basing their voting decision on disinformation </t>
+  </si>
+  <si>
+    <t>Not Concerned- Foreign countries influencing elections covertly</t>
+  </si>
+  <si>
+    <t>Agree-Nowadays in (YOUR COUNTRY) you have equal opportunities for getting ahead in life, like everyone else</t>
+  </si>
+  <si>
+    <t>Agree-Aujourd’hui, en (NOTRE PAYS), les différences de revenus entre les gens sont trop importantes</t>
+  </si>
+  <si>
+    <t>Agree-The (NATIONALITY) government should take measures to reduce differences in income levels</t>
+  </si>
+  <si>
+    <t>Agree-The EU institutions should support the (NATIONALITY) government to reduce differences in income levels</t>
+  </si>
+  <si>
+    <t>Electoral Integrity</t>
+  </si>
+  <si>
+    <t>Fairness</t>
+  </si>
+  <si>
+    <t>Equality</t>
+  </si>
+  <si>
+    <t>Respondent's level higher than their mother's</t>
+  </si>
+  <si>
+    <t>Respondent's level higher than their father's</t>
+  </si>
+  <si>
+    <t>Social Mobility</t>
+  </si>
+  <si>
+    <t>Pandemic Support</t>
+  </si>
+  <si>
+    <t>Agree- the core values of the EU, such as fundamental rights, democracy and the rule of law are well protected in (OUR COUNTRY)?</t>
+  </si>
+  <si>
+    <t>Justice&amp;Law</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informed-the rule of law in (OUR COUNTRY)? </t>
+  </si>
+  <si>
+    <t>Informed- the rule of law in other EU Member States?</t>
+  </si>
+  <si>
+    <t>Role of the EP</t>
+  </si>
+  <si>
+    <t>Role of the CSOs</t>
+  </si>
+  <si>
+    <t>Engagement</t>
+  </si>
+  <si>
+    <t>Political Interest</t>
+  </si>
+  <si>
+    <t>Trust-Domestic</t>
+  </si>
+  <si>
+    <t>Trust-EU</t>
+  </si>
+  <si>
+    <t>Trust-International</t>
+  </si>
+  <si>
+    <t>Efficacy</t>
+  </si>
+  <si>
+    <t>EU Image</t>
+  </si>
+  <si>
+    <t>Youth-Voted in a local, national or European election</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>SUBDOMAIN</t>
+  </si>
+  <si>
+    <t>INDICATORS</t>
   </si>
 </sst>
 </file>
@@ -355,7 +427,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -388,7 +460,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -723,12 +795,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA6585B-C499-45AD-87BE-134F9272F3A6}">
-  <dimension ref="A1:BL31"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="B1" t="s">
         <v>28</v>
@@ -919,37 +991,85 @@
       <c r="BL1" t="s">
         <v>28</v>
       </c>
+      <c r="BM1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>105</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>105</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>105</v>
+      </c>
     </row>
-    <row r="2" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
         <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="K2" t="s">
         <v>29</v>
@@ -973,118 +1093,118 @@
         <v>29</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="S2" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="T2" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="U2" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="V2" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="W2" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="X2" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="Y2" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="Z2" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="AA2" t="s">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="AB2" t="s">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="AC2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF2" t="s">
         <v>63</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AG2" t="s">
         <v>63</v>
       </c>
-      <c r="AE2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>66</v>
-      </c>
       <c r="AH2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="AI2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="AJ2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="AK2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="AL2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="AM2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="AN2" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="AO2" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="AP2" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="AQ2" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="AR2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="AS2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="AT2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="AU2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="AV2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="AW2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="AX2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="AY2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="AZ2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="BA2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="BB2" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="BC2" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="BD2" t="s">
         <v>29</v>
@@ -1113,10 +1233,58 @@
       <c r="BL2" t="s">
         <v>29</v>
       </c>
+      <c r="BM2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>112</v>
+      </c>
     </row>
-    <row r="3" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -1146,169 +1314,217 @@
         <v>38</v>
       </c>
       <c r="K3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" t="s">
         <v>41</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>42</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>43</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>44</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>45</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="S3" t="s">
         <v>47</v>
       </c>
-      <c r="R3" t="s">
+      <c r="T3" t="s">
         <v>48</v>
       </c>
-      <c r="S3" t="s">
+      <c r="U3" t="s">
         <v>49</v>
       </c>
-      <c r="T3" t="s">
+      <c r="V3" t="s">
         <v>50</v>
       </c>
-      <c r="U3" t="s">
+      <c r="W3" t="s">
         <v>51</v>
       </c>
-      <c r="V3" t="s">
+      <c r="X3" t="s">
         <v>52</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Y3" t="s">
         <v>53</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Z3" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AA3" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AB3" t="s">
         <v>56</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AC3" t="s">
         <v>57</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AD3" t="s">
         <v>58</v>
       </c>
-      <c r="AC3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF3" t="s">
         <v>61</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AG3" t="s">
         <v>62</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AH3" t="s">
         <v>64</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AI3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL3" t="s">
         <v>65</v>
       </c>
-      <c r="AH3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI3" t="s">
+      <c r="AM3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO3" t="s">
         <v>71</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AP3" t="s">
         <v>72</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AQ3" t="s">
         <v>73</v>
       </c>
-      <c r="AL3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN3" t="s">
+      <c r="AR3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>90</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>91</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD3" t="s">
         <v>74</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="BE3" t="s">
         <v>75</v>
       </c>
-      <c r="AP3" t="s">
+      <c r="BF3" t="s">
         <v>76</v>
       </c>
-      <c r="AQ3" t="s">
+      <c r="BG3" t="s">
         <v>77</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="BH3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BI3" t="s">
         <v>79</v>
       </c>
-      <c r="AS3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AW3" t="s">
+      <c r="BJ3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>81</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>82</v>
+      </c>
+      <c r="BM3" t="s">
         <v>94</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="BN3" t="s">
         <v>95</v>
       </c>
-      <c r="AY3" t="s">
+      <c r="BO3" t="s">
         <v>96</v>
       </c>
-      <c r="AZ3" t="s">
+      <c r="BP3" t="s">
         <v>97</v>
       </c>
-      <c r="BA3" t="s">
+      <c r="BQ3" t="s">
         <v>98</v>
       </c>
-      <c r="BB3" t="s">
+      <c r="BR3" t="s">
         <v>99</v>
       </c>
-      <c r="BC3" t="s">
+      <c r="BS3" t="s">
         <v>100</v>
       </c>
-      <c r="BD3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>81</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>82</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>83</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>84</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>85</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>86</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>88</v>
+      <c r="BT3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>102</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>103</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>107</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>108</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>110</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="CA3" t="s">
+        <v>114</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1501,8 +1717,56 @@
       <c r="BL4">
         <v>19</v>
       </c>
+      <c r="BM4">
+        <v>43.5</v>
+      </c>
+      <c r="BN4">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="BO4">
+        <v>25.8</v>
+      </c>
+      <c r="BP4">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="BQ4">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="BR4">
+        <v>27.6</v>
+      </c>
+      <c r="BS4">
+        <v>0.47</v>
+      </c>
+      <c r="BT4">
+        <v>0.81</v>
+      </c>
+      <c r="BU4">
+        <v>0.78</v>
+      </c>
+      <c r="BV4">
+        <v>0.73</v>
+      </c>
+      <c r="BW4">
+        <v>0.64</v>
+      </c>
+      <c r="BX4">
+        <v>0.61</v>
+      </c>
+      <c r="BY4">
+        <v>0.24</v>
+      </c>
+      <c r="BZ4">
+        <v>0.53</v>
+      </c>
+      <c r="CA4">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="CB4">
+        <v>0.66</v>
+      </c>
     </row>
-    <row r="5" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1695,8 +1959,56 @@
       <c r="BL5">
         <v>19</v>
       </c>
+      <c r="BM5">
+        <v>51.1</v>
+      </c>
+      <c r="BN5">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="BO5">
+        <v>28.1</v>
+      </c>
+      <c r="BP5">
+        <v>31.5</v>
+      </c>
+      <c r="BQ5">
+        <v>22.2</v>
+      </c>
+      <c r="BR5">
+        <v>26</v>
+      </c>
+      <c r="BS5">
+        <v>0.54</v>
+      </c>
+      <c r="BT5">
+        <v>0.7</v>
+      </c>
+      <c r="BU5">
+        <v>0.71</v>
+      </c>
+      <c r="BV5">
+        <v>0.66</v>
+      </c>
+      <c r="BW5">
+        <v>0.59</v>
+      </c>
+      <c r="BX5">
+        <v>0.6</v>
+      </c>
+      <c r="BY5">
+        <v>0.38</v>
+      </c>
+      <c r="BZ5">
+        <v>0.52</v>
+      </c>
+      <c r="CA5">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="CB5">
+        <v>0.75</v>
+      </c>
     </row>
-    <row r="6" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -1889,8 +2201,56 @@
       <c r="BL6">
         <v>19</v>
       </c>
+      <c r="BM6">
+        <v>27.9</v>
+      </c>
+      <c r="BN6">
+        <v>19.8</v>
+      </c>
+      <c r="BO6">
+        <v>22.8</v>
+      </c>
+      <c r="BP6">
+        <v>19</v>
+      </c>
+      <c r="BQ6">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="BR6">
+        <v>20.6</v>
+      </c>
+      <c r="BS6">
+        <v>0.27</v>
+      </c>
+      <c r="BT6">
+        <v>0.93</v>
+      </c>
+      <c r="BU6">
+        <v>0.87</v>
+      </c>
+      <c r="BV6">
+        <v>0.88</v>
+      </c>
+      <c r="BW6">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BX6">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BY6">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="BZ6">
+        <v>0.36</v>
+      </c>
+      <c r="CA6">
+        <v>0.19</v>
+      </c>
+      <c r="CB6">
+        <v>0.35</v>
+      </c>
     </row>
-    <row r="7" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2083,8 +2443,56 @@
       <c r="BL7">
         <v>15</v>
       </c>
+      <c r="BM7">
+        <v>33.9</v>
+      </c>
+      <c r="BN7">
+        <v>27.9</v>
+      </c>
+      <c r="BO7">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="BP7">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="BQ7">
+        <v>13.6</v>
+      </c>
+      <c r="BR7">
+        <v>19.5</v>
+      </c>
+      <c r="BS7">
+        <v>0.42</v>
+      </c>
+      <c r="BT7">
+        <v>0.77</v>
+      </c>
+      <c r="BU7">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BV7">
+        <v>0.59</v>
+      </c>
+      <c r="BW7">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="BX7">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="BY7">
+        <v>0.2</v>
+      </c>
+      <c r="BZ7">
+        <v>0.63</v>
+      </c>
+      <c r="CA7">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="CB7">
+        <v>0.66</v>
+      </c>
     </row>
-    <row r="8" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2277,8 +2685,56 @@
       <c r="BL8">
         <v>19</v>
       </c>
+      <c r="BM8">
+        <v>68.3</v>
+      </c>
+      <c r="BN8">
+        <v>54.3</v>
+      </c>
+      <c r="BO8">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="BP8">
+        <v>54.2</v>
+      </c>
+      <c r="BQ8">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="BR8">
+        <v>33.5</v>
+      </c>
+      <c r="BS8">
+        <v>0.63</v>
+      </c>
+      <c r="BT8">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BU8">
+        <v>0.45</v>
+      </c>
+      <c r="BV8">
+        <v>0.4</v>
+      </c>
+      <c r="BW8">
+        <v>0.53</v>
+      </c>
+      <c r="BX8">
+        <v>0.49</v>
+      </c>
+      <c r="BY8">
+        <v>0.12</v>
+      </c>
+      <c r="BZ8">
+        <v>0.66</v>
+      </c>
+      <c r="CA8">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="CB8">
+        <v>0.83</v>
+      </c>
     </row>
-    <row r="9" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2471,8 +2927,56 @@
       <c r="BL9">
         <v>18</v>
       </c>
+      <c r="BM9">
+        <v>57.3</v>
+      </c>
+      <c r="BN9">
+        <v>51.2</v>
+      </c>
+      <c r="BO9">
+        <v>32.1</v>
+      </c>
+      <c r="BP9">
+        <v>49.6</v>
+      </c>
+      <c r="BQ9">
+        <v>28.7</v>
+      </c>
+      <c r="BR9">
+        <v>36.4</v>
+      </c>
+      <c r="BS9">
+        <v>0.53</v>
+      </c>
+      <c r="BT9">
+        <v>0.87</v>
+      </c>
+      <c r="BU9">
+        <v>0.78</v>
+      </c>
+      <c r="BV9">
+        <v>0.7</v>
+      </c>
+      <c r="BW9">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="BX9">
+        <v>0.5</v>
+      </c>
+      <c r="BY9">
+        <v>0.21</v>
+      </c>
+      <c r="BZ9">
+        <v>0.61</v>
+      </c>
+      <c r="CA9">
+        <v>0.3</v>
+      </c>
+      <c r="CB9">
+        <v>0.78</v>
+      </c>
     </row>
-    <row r="10" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -2665,8 +3169,56 @@
       <c r="BL10">
         <v>16</v>
       </c>
+      <c r="BM10">
+        <v>59</v>
+      </c>
+      <c r="BN10">
+        <v>53.5</v>
+      </c>
+      <c r="BO10">
+        <v>44.3</v>
+      </c>
+      <c r="BP10">
+        <v>51.4</v>
+      </c>
+      <c r="BQ10">
+        <v>30.5</v>
+      </c>
+      <c r="BR10">
+        <v>46</v>
+      </c>
+      <c r="BS10">
+        <v>0.51</v>
+      </c>
+      <c r="BT10">
+        <v>0.84</v>
+      </c>
+      <c r="BU10">
+        <v>0.75</v>
+      </c>
+      <c r="BV10">
+        <v>0.69</v>
+      </c>
+      <c r="BW10">
+        <v>0.46</v>
+      </c>
+      <c r="BX10">
+        <v>0.45</v>
+      </c>
+      <c r="BY10">
+        <v>0.25</v>
+      </c>
+      <c r="BZ10">
+        <v>0.5</v>
+      </c>
+      <c r="CA10">
+        <v>0.21</v>
+      </c>
+      <c r="CB10">
+        <v>0.6</v>
+      </c>
     </row>
-    <row r="11" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -2859,8 +3411,56 @@
       <c r="BL11">
         <v>22</v>
       </c>
+      <c r="BM11">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="BN11">
+        <v>39.5</v>
+      </c>
+      <c r="BO11">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="BP11">
+        <v>39</v>
+      </c>
+      <c r="BQ11">
+        <v>18.3</v>
+      </c>
+      <c r="BR11">
+        <v>27.8</v>
+      </c>
+      <c r="BS11">
+        <v>0.6</v>
+      </c>
+      <c r="BT11">
+        <v>0.77</v>
+      </c>
+      <c r="BU11">
+        <v>0.8</v>
+      </c>
+      <c r="BV11">
+        <v>0.76</v>
+      </c>
+      <c r="BW11">
+        <v>0.67</v>
+      </c>
+      <c r="BX11">
+        <v>0.69</v>
+      </c>
+      <c r="BY11">
+        <v>0.23</v>
+      </c>
+      <c r="BZ11">
+        <v>0.68</v>
+      </c>
+      <c r="CA11">
+        <v>0.41</v>
+      </c>
+      <c r="CB11">
+        <v>0.78</v>
+      </c>
     </row>
-    <row r="12" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -3053,8 +3653,56 @@
       <c r="BL12">
         <v>23</v>
       </c>
+      <c r="BM12">
+        <v>45.4</v>
+      </c>
+      <c r="BN12">
+        <v>43.2</v>
+      </c>
+      <c r="BO12">
+        <v>37.1</v>
+      </c>
+      <c r="BP12">
+        <v>35.1</v>
+      </c>
+      <c r="BQ12">
+        <v>15.6</v>
+      </c>
+      <c r="BR12">
+        <v>26.6</v>
+      </c>
+      <c r="BS12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="BT12">
+        <v>0.82</v>
+      </c>
+      <c r="BU12">
+        <v>0.9</v>
+      </c>
+      <c r="BV12">
+        <v>0.9</v>
+      </c>
+      <c r="BW12">
+        <v>0.71</v>
+      </c>
+      <c r="BX12">
+        <v>0.69</v>
+      </c>
+      <c r="BY12">
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="BZ12">
+        <v>0.38</v>
+      </c>
+      <c r="CA12">
+        <v>0.17</v>
+      </c>
+      <c r="CB12">
+        <v>0.32</v>
+      </c>
     </row>
-    <row r="13" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -3247,8 +3895,56 @@
       <c r="BL13">
         <v>21</v>
       </c>
+      <c r="BM13">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="BN13">
+        <v>20</v>
+      </c>
+      <c r="BO13">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="BP13">
+        <v>18.7</v>
+      </c>
+      <c r="BQ13">
+        <v>10.5</v>
+      </c>
+      <c r="BR13">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="BS13">
+        <v>0.46</v>
+      </c>
+      <c r="BT13">
+        <v>0.8</v>
+      </c>
+      <c r="BU13">
+        <v>0.79</v>
+      </c>
+      <c r="BV13">
+        <v>0.77</v>
+      </c>
+      <c r="BW13">
+        <v>0.74</v>
+      </c>
+      <c r="BX13">
+        <v>0.72</v>
+      </c>
+      <c r="BY13">
+        <v>0.24</v>
+      </c>
+      <c r="BZ13">
+        <v>0.42</v>
+      </c>
+      <c r="CA13">
+        <v>0.26</v>
+      </c>
+      <c r="CB13">
+        <v>0.59</v>
+      </c>
     </row>
-    <row r="14" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -3441,8 +4137,56 @@
       <c r="BL14">
         <v>18</v>
       </c>
+      <c r="BM14">
+        <v>29.1</v>
+      </c>
+      <c r="BN14">
+        <v>24.4</v>
+      </c>
+      <c r="BO14">
+        <v>19.7</v>
+      </c>
+      <c r="BP14">
+        <v>19</v>
+      </c>
+      <c r="BQ14">
+        <v>15.7</v>
+      </c>
+      <c r="BR14">
+        <v>18.2</v>
+      </c>
+      <c r="BS14">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="BT14">
+        <v>0.85</v>
+      </c>
+      <c r="BU14">
+        <v>0.8</v>
+      </c>
+      <c r="BV14">
+        <v>0.72</v>
+      </c>
+      <c r="BW14">
+        <v>0.61</v>
+      </c>
+      <c r="BX14">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="BY14">
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="BZ14">
+        <v>0.46</v>
+      </c>
+      <c r="CA14">
+        <v>0.18</v>
+      </c>
+      <c r="CB14">
+        <v>0.61</v>
+      </c>
     </row>
-    <row r="15" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -3635,8 +4379,56 @@
       <c r="BL15">
         <v>20</v>
       </c>
+      <c r="BM15">
+        <v>33.5</v>
+      </c>
+      <c r="BN15">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="BO15">
+        <v>30.7</v>
+      </c>
+      <c r="BP15">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="BQ15">
+        <v>25.9</v>
+      </c>
+      <c r="BR15">
+        <v>37.1</v>
+      </c>
+      <c r="BS15">
+        <v>0.23</v>
+      </c>
+      <c r="BT15">
+        <v>0.8</v>
+      </c>
+      <c r="BU15">
+        <v>0.77</v>
+      </c>
+      <c r="BV15">
+        <v>0.79</v>
+      </c>
+      <c r="BW15">
+        <v>0.72</v>
+      </c>
+      <c r="BX15">
+        <v>0.72</v>
+      </c>
+      <c r="BY15">
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="BZ15">
+        <v>0.49</v>
+      </c>
+      <c r="CA15">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="CB15">
+        <v>0.52</v>
+      </c>
     </row>
-    <row r="16" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -3829,8 +4621,56 @@
       <c r="BL16">
         <v>22</v>
       </c>
+      <c r="BM16">
+        <v>44.1</v>
+      </c>
+      <c r="BN16">
+        <v>38</v>
+      </c>
+      <c r="BO16">
+        <v>27.8</v>
+      </c>
+      <c r="BP16">
+        <v>36.1</v>
+      </c>
+      <c r="BQ16">
+        <v>17</v>
+      </c>
+      <c r="BR16">
+        <v>29.8</v>
+      </c>
+      <c r="BS16">
+        <v>0.39</v>
+      </c>
+      <c r="BT16">
+        <v>0.82</v>
+      </c>
+      <c r="BU16">
+        <v>0.81</v>
+      </c>
+      <c r="BV16">
+        <v>0.8</v>
+      </c>
+      <c r="BW16">
+        <v>0.66</v>
+      </c>
+      <c r="BX16">
+        <v>0.65</v>
+      </c>
+      <c r="BY16">
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="BZ16">
+        <v>0.47</v>
+      </c>
+      <c r="CA16">
+        <v>0.3</v>
+      </c>
+      <c r="CB16">
+        <v>0.6</v>
+      </c>
     </row>
-    <row r="17" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -4023,8 +4863,56 @@
       <c r="BL17">
         <v>30</v>
       </c>
+      <c r="BM17">
+        <v>50.5</v>
+      </c>
+      <c r="BN17">
+        <v>39.4</v>
+      </c>
+      <c r="BO17">
+        <v>29.6</v>
+      </c>
+      <c r="BP17">
+        <v>33.5</v>
+      </c>
+      <c r="BQ17">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="BR17">
+        <v>27.4</v>
+      </c>
+      <c r="BS17">
+        <v>0.21</v>
+      </c>
+      <c r="BT17">
+        <v>0.81</v>
+      </c>
+      <c r="BU17">
+        <v>0.88</v>
+      </c>
+      <c r="BV17">
+        <v>0.85</v>
+      </c>
+      <c r="BW17">
+        <v>0.76</v>
+      </c>
+      <c r="BX17">
+        <v>0.74</v>
+      </c>
+      <c r="BY17">
+        <v>0.23</v>
+      </c>
+      <c r="BZ17">
+        <v>0.49</v>
+      </c>
+      <c r="CA17">
+        <v>0.36</v>
+      </c>
+      <c r="CB17">
+        <v>0.48</v>
+      </c>
     </row>
-    <row r="18" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -4217,8 +5105,56 @@
       <c r="BL18">
         <v>22</v>
       </c>
+      <c r="BM18">
+        <v>27.3</v>
+      </c>
+      <c r="BN18">
+        <v>19.8</v>
+      </c>
+      <c r="BO18">
+        <v>21.5</v>
+      </c>
+      <c r="BP18">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="BQ18">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="BR18">
+        <v>23.8</v>
+      </c>
+      <c r="BS18">
+        <v>0.42</v>
+      </c>
+      <c r="BT18">
+        <v>0.86</v>
+      </c>
+      <c r="BU18">
+        <v>0.84</v>
+      </c>
+      <c r="BV18">
+        <v>0.8</v>
+      </c>
+      <c r="BW18">
+        <v>0.59</v>
+      </c>
+      <c r="BX18">
+        <v>0.63</v>
+      </c>
+      <c r="BY18">
+        <v>0.41000000000000003</v>
+      </c>
+      <c r="BZ18">
+        <v>0.46</v>
+      </c>
+      <c r="CA18">
+        <v>0.21</v>
+      </c>
+      <c r="CB18">
+        <v>0.49</v>
+      </c>
     </row>
-    <row r="19" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -4411,8 +5347,56 @@
       <c r="BL19">
         <v>21</v>
       </c>
+      <c r="BM19">
+        <v>31.4</v>
+      </c>
+      <c r="BN19">
+        <v>24.6</v>
+      </c>
+      <c r="BO19">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="BP19">
+        <v>38.1</v>
+      </c>
+      <c r="BQ19">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="BR19">
+        <v>24</v>
+      </c>
+      <c r="BS19">
+        <v>0.54</v>
+      </c>
+      <c r="BT19">
+        <v>0.9</v>
+      </c>
+      <c r="BU19">
+        <v>0.88</v>
+      </c>
+      <c r="BV19">
+        <v>0.83</v>
+      </c>
+      <c r="BW19">
+        <v>0.68</v>
+      </c>
+      <c r="BX19">
+        <v>0.68</v>
+      </c>
+      <c r="BY19">
+        <v>0.19</v>
+      </c>
+      <c r="BZ19">
+        <v>0.45</v>
+      </c>
+      <c r="CA19">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="CB19">
+        <v>0.61</v>
+      </c>
     </row>
-    <row r="20" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -4605,8 +5589,56 @@
       <c r="BL20">
         <v>18</v>
       </c>
+      <c r="BM20">
+        <v>46.9</v>
+      </c>
+      <c r="BN20">
+        <v>44</v>
+      </c>
+      <c r="BO20">
+        <v>32.1</v>
+      </c>
+      <c r="BP20">
+        <v>40.9</v>
+      </c>
+      <c r="BQ20">
+        <v>25.5</v>
+      </c>
+      <c r="BR20">
+        <v>29.7</v>
+      </c>
+      <c r="BS20">
+        <v>0.66</v>
+      </c>
+      <c r="BT20">
+        <v>0.79</v>
+      </c>
+      <c r="BU20">
+        <v>0.74</v>
+      </c>
+      <c r="BV20">
+        <v>0.64</v>
+      </c>
+      <c r="BW20">
+        <v>0.72</v>
+      </c>
+      <c r="BX20">
+        <v>0.63</v>
+      </c>
+      <c r="BY20">
+        <v>0.2</v>
+      </c>
+      <c r="BZ20">
+        <v>0.62</v>
+      </c>
+      <c r="CA20">
+        <v>0.39</v>
+      </c>
+      <c r="CB20">
+        <v>0.89</v>
+      </c>
     </row>
-    <row r="21" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -4799,8 +5831,56 @@
       <c r="BL21">
         <v>17</v>
       </c>
+      <c r="BM21">
+        <v>30.5</v>
+      </c>
+      <c r="BN21">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="BO21">
+        <v>22.7</v>
+      </c>
+      <c r="BP21">
+        <v>43.5</v>
+      </c>
+      <c r="BQ21">
+        <v>14.2</v>
+      </c>
+      <c r="BR21">
+        <v>29.8</v>
+      </c>
+      <c r="BS21">
+        <v>0.37</v>
+      </c>
+      <c r="BT21">
+        <v>0.9</v>
+      </c>
+      <c r="BU21">
+        <v>0.85</v>
+      </c>
+      <c r="BV21">
+        <v>0.77</v>
+      </c>
+      <c r="BW21">
+        <v>0.63</v>
+      </c>
+      <c r="BX21">
+        <v>0.61</v>
+      </c>
+      <c r="BY21">
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="BZ21">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="CA21">
+        <v>0.37</v>
+      </c>
+      <c r="CB21">
+        <v>0.64</v>
+      </c>
     </row>
-    <row r="22" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -4993,8 +6073,56 @@
       <c r="BL22">
         <v>24</v>
       </c>
+      <c r="BM22">
+        <v>47.2</v>
+      </c>
+      <c r="BN22">
+        <v>41.6</v>
+      </c>
+      <c r="BO22">
+        <v>31.1</v>
+      </c>
+      <c r="BP22">
+        <v>37.1</v>
+      </c>
+      <c r="BQ22">
+        <v>18</v>
+      </c>
+      <c r="BR22">
+        <v>31.5</v>
+      </c>
+      <c r="BS22">
+        <v>0.53</v>
+      </c>
+      <c r="BT22">
+        <v>0.8</v>
+      </c>
+      <c r="BU22">
+        <v>0.87</v>
+      </c>
+      <c r="BV22">
+        <v>0.87</v>
+      </c>
+      <c r="BW22">
+        <v>0.72</v>
+      </c>
+      <c r="BX22">
+        <v>0.73</v>
+      </c>
+      <c r="BY22">
+        <v>0.27</v>
+      </c>
+      <c r="BZ22">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="CA22">
+        <v>0.38</v>
+      </c>
+      <c r="CB22">
+        <v>0.52</v>
+      </c>
     </row>
-    <row r="23" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -5187,8 +6315,56 @@
       <c r="BL23">
         <v>16</v>
       </c>
+      <c r="BM23">
+        <v>43.5</v>
+      </c>
+      <c r="BN23">
+        <v>41.9</v>
+      </c>
+      <c r="BO23">
+        <v>26.6</v>
+      </c>
+      <c r="BP23">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="BQ23">
+        <v>18.8</v>
+      </c>
+      <c r="BR23">
+        <v>31.2</v>
+      </c>
+      <c r="BS23">
+        <v>0.35</v>
+      </c>
+      <c r="BT23">
+        <v>0.73</v>
+      </c>
+      <c r="BU23">
+        <v>0.73</v>
+      </c>
+      <c r="BV23">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BW23">
+        <v>0.67</v>
+      </c>
+      <c r="BX23">
+        <v>0.6</v>
+      </c>
+      <c r="BY23">
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="BZ23">
+        <v>0.73</v>
+      </c>
+      <c r="CA23">
+        <v>0.27</v>
+      </c>
+      <c r="CB23">
+        <v>0.79</v>
+      </c>
     </row>
-    <row r="24" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -5381,8 +6557,56 @@
       <c r="BL24">
         <v>19</v>
       </c>
+      <c r="BM24">
+        <v>49.8</v>
+      </c>
+      <c r="BN24">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="BO24">
+        <v>29.7</v>
+      </c>
+      <c r="BP24">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="BQ24">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="BR24">
+        <v>28.7</v>
+      </c>
+      <c r="BS24">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="BT24">
+        <v>0.8</v>
+      </c>
+      <c r="BU24">
+        <v>0.82</v>
+      </c>
+      <c r="BV24">
+        <v>0.7</v>
+      </c>
+      <c r="BW24">
+        <v>0.78</v>
+      </c>
+      <c r="BX24">
+        <v>0.72</v>
+      </c>
+      <c r="BY24">
+        <v>0.53</v>
+      </c>
+      <c r="BZ24">
+        <v>0.71</v>
+      </c>
+      <c r="CA24">
+        <v>0.4</v>
+      </c>
+      <c r="CB24">
+        <v>0.81</v>
+      </c>
     </row>
-    <row r="25" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -5575,8 +6799,56 @@
       <c r="BL25">
         <v>21</v>
       </c>
+      <c r="BM25">
+        <v>38.5</v>
+      </c>
+      <c r="BN25">
+        <v>25.3</v>
+      </c>
+      <c r="BO25">
+        <v>20.2</v>
+      </c>
+      <c r="BP25">
+        <v>18.8</v>
+      </c>
+      <c r="BQ25">
+        <v>15.6</v>
+      </c>
+      <c r="BR25">
+        <v>23.3</v>
+      </c>
+      <c r="BS25">
+        <v>0.5</v>
+      </c>
+      <c r="BT25">
+        <v>0.76</v>
+      </c>
+      <c r="BU25">
+        <v>0.73</v>
+      </c>
+      <c r="BV25">
+        <v>0.75</v>
+      </c>
+      <c r="BW25">
+        <v>0.8</v>
+      </c>
+      <c r="BX25">
+        <v>0.8</v>
+      </c>
+      <c r="BY25">
+        <v>0.19</v>
+      </c>
+      <c r="BZ25">
+        <v>0.66</v>
+      </c>
+      <c r="CA25">
+        <v>0.49</v>
+      </c>
+      <c r="CB25">
+        <v>0.73</v>
+      </c>
     </row>
-    <row r="26" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -5769,8 +7041,56 @@
       <c r="BL26">
         <v>21</v>
       </c>
+      <c r="BM26">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="BN26">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="BO26">
+        <v>23.7</v>
+      </c>
+      <c r="BP26">
+        <v>35.9</v>
+      </c>
+      <c r="BQ26">
+        <v>17.7</v>
+      </c>
+      <c r="BR26">
+        <v>30.1</v>
+      </c>
+      <c r="BS26">
+        <v>0.35</v>
+      </c>
+      <c r="BT26">
+        <v>0.94</v>
+      </c>
+      <c r="BU26">
+        <v>0.93</v>
+      </c>
+      <c r="BV26">
+        <v>0.92</v>
+      </c>
+      <c r="BW26">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BX26">
+        <v>0.52</v>
+      </c>
+      <c r="BY26">
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="BZ26">
+        <v>0.48</v>
+      </c>
+      <c r="CA26">
+        <v>0.38</v>
+      </c>
+      <c r="CB26">
+        <v>0.68</v>
+      </c>
     </row>
-    <row r="27" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -5963,8 +7283,56 @@
       <c r="BL27">
         <v>21</v>
       </c>
+      <c r="BM27">
+        <v>31.7</v>
+      </c>
+      <c r="BN27">
+        <v>22.9</v>
+      </c>
+      <c r="BO27">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="BP27">
+        <v>28.9</v>
+      </c>
+      <c r="BQ27">
+        <v>21.1</v>
+      </c>
+      <c r="BR27">
+        <v>27.1</v>
+      </c>
+      <c r="BS27">
+        <v>0.4</v>
+      </c>
+      <c r="BT27">
+        <v>0.69</v>
+      </c>
+      <c r="BU27">
+        <v>0.67</v>
+      </c>
+      <c r="BV27">
+        <v>0.64</v>
+      </c>
+      <c r="BW27">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BX27">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="BY27">
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="BZ27">
+        <v>0.44</v>
+      </c>
+      <c r="CA27">
+        <v>0.3</v>
+      </c>
+      <c r="CB27">
+        <v>0.47</v>
+      </c>
     </row>
-    <row r="28" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -6157,8 +7525,56 @@
       <c r="BL28">
         <v>23</v>
       </c>
+      <c r="BM28">
+        <v>49.8</v>
+      </c>
+      <c r="BN28">
+        <v>37.1</v>
+      </c>
+      <c r="BO28">
+        <v>30.3</v>
+      </c>
+      <c r="BP28">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="BQ28">
+        <v>22.6</v>
+      </c>
+      <c r="BR28">
+        <v>36.1</v>
+      </c>
+      <c r="BS28">
+        <v>0.3</v>
+      </c>
+      <c r="BT28">
+        <v>0.84</v>
+      </c>
+      <c r="BU28">
+        <v>0.82</v>
+      </c>
+      <c r="BV28">
+        <v>0.81</v>
+      </c>
+      <c r="BW28">
+        <v>0.69</v>
+      </c>
+      <c r="BX28">
+        <v>0.7</v>
+      </c>
+      <c r="BY28">
+        <v>0.4</v>
+      </c>
+      <c r="BZ28">
+        <v>0.48</v>
+      </c>
+      <c r="CA28">
+        <v>0.27</v>
+      </c>
+      <c r="CB28">
+        <v>0.49</v>
+      </c>
     </row>
-    <row r="29" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -6351,8 +7767,56 @@
       <c r="BL29">
         <v>17</v>
       </c>
+      <c r="BM29">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="BN29">
+        <v>49</v>
+      </c>
+      <c r="BO29">
+        <v>41.8</v>
+      </c>
+      <c r="BP29">
+        <v>48.6</v>
+      </c>
+      <c r="BQ29">
+        <v>21.2</v>
+      </c>
+      <c r="BR29">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="BS29">
+        <v>0.33</v>
+      </c>
+      <c r="BT29">
+        <v>0.81</v>
+      </c>
+      <c r="BU29">
+        <v>0.79</v>
+      </c>
+      <c r="BV29">
+        <v>0.76</v>
+      </c>
+      <c r="BW29">
+        <v>0.52</v>
+      </c>
+      <c r="BX29">
+        <v>0.51</v>
+      </c>
+      <c r="BY29">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="BZ29">
+        <v>0.52</v>
+      </c>
+      <c r="CA29">
+        <v>0.33</v>
+      </c>
+      <c r="CB29">
+        <v>0.49</v>
+      </c>
     </row>
-    <row r="30" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -6545,8 +8009,56 @@
       <c r="BL30">
         <v>19</v>
       </c>
+      <c r="BM30">
+        <v>68.5</v>
+      </c>
+      <c r="BN30">
+        <v>63.5</v>
+      </c>
+      <c r="BO30">
+        <v>32.5</v>
+      </c>
+      <c r="BP30">
+        <v>54.4</v>
+      </c>
+      <c r="BQ30">
+        <v>28.8</v>
+      </c>
+      <c r="BR30">
+        <v>37.1</v>
+      </c>
+      <c r="BS30">
+        <v>0.69</v>
+      </c>
+      <c r="BT30">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BU30">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BV30">
+        <v>0.52</v>
+      </c>
+      <c r="BW30">
+        <v>0.62</v>
+      </c>
+      <c r="BX30">
+        <v>0.62</v>
+      </c>
+      <c r="BY30">
+        <v>0.21</v>
+      </c>
+      <c r="BZ30">
+        <v>0.72</v>
+      </c>
+      <c r="CA30">
+        <v>0.27</v>
+      </c>
+      <c r="CB30">
+        <v>0.92</v>
+      </c>
     </row>
-    <row r="31" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -6739,6 +8251,85 @@
       <c r="BL31">
         <v>17</v>
       </c>
+      <c r="BM31">
+        <v>80.7</v>
+      </c>
+      <c r="BN31">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="BO31">
+        <v>46.4</v>
+      </c>
+      <c r="BP31">
+        <v>61.5</v>
+      </c>
+      <c r="BQ31">
+        <v>31.1</v>
+      </c>
+      <c r="BR31">
+        <v>39.1</v>
+      </c>
+      <c r="BS31">
+        <v>0.65</v>
+      </c>
+      <c r="BT31">
+        <v>0.68</v>
+      </c>
+      <c r="BU31">
+        <v>0.64</v>
+      </c>
+      <c r="BV31">
+        <v>0.49</v>
+      </c>
+      <c r="BW31">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="BX31">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BY31">
+        <v>0.17000000000000004</v>
+      </c>
+      <c r="BZ31">
+        <v>0.67</v>
+      </c>
+      <c r="CA31">
+        <v>0.22</v>
+      </c>
+      <c r="CB31">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+      <c r="AG32" s="1"/>
+      <c r="AH32" s="1"/>
+      <c r="AI32" s="1"/>
+      <c r="AJ32" s="1"/>
+      <c r="AK32" s="1"/>
+      <c r="AL32" s="1"/>
+      <c r="AM32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SC Indicators Data Prep.xlsx
+++ b/SC Indicators Data Prep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emree\Desktop\CO3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81D52FC-EADD-46E2-A5E9-9EE84EFBA4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3580F4B-A12B-4EB2-B43C-B3D415990C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{55AA29CC-CDDC-4D64-AC5C-6644C21888DE}"/>
   </bookViews>
@@ -1736,34 +1736,34 @@
         <v>27.6</v>
       </c>
       <c r="BS4">
-        <v>0.47</v>
+        <v>47</v>
       </c>
       <c r="BT4">
-        <v>0.81</v>
+        <v>81</v>
       </c>
       <c r="BU4">
-        <v>0.78</v>
+        <v>78</v>
       </c>
       <c r="BV4">
-        <v>0.73</v>
+        <v>73</v>
       </c>
       <c r="BW4">
-        <v>0.64</v>
+        <v>64</v>
       </c>
       <c r="BX4">
-        <v>0.61</v>
+        <v>61</v>
       </c>
       <c r="BY4">
-        <v>0.24</v>
+        <v>24</v>
       </c>
       <c r="BZ4">
-        <v>0.53</v>
+        <v>53</v>
       </c>
       <c r="CA4">
-        <v>0.28999999999999998</v>
+        <v>28.999999999999996</v>
       </c>
       <c r="CB4">
-        <v>0.66</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:80" x14ac:dyDescent="0.25">
@@ -1930,7 +1930,7 @@
         <v>78</v>
       </c>
       <c r="BC5">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="BD5">
         <v>34</v>
@@ -1978,34 +1978,34 @@
         <v>26</v>
       </c>
       <c r="BS5">
-        <v>0.54</v>
+        <v>54</v>
       </c>
       <c r="BT5">
-        <v>0.7</v>
+        <v>70</v>
       </c>
       <c r="BU5">
-        <v>0.71</v>
+        <v>71</v>
       </c>
       <c r="BV5">
-        <v>0.66</v>
+        <v>66</v>
       </c>
       <c r="BW5">
-        <v>0.59</v>
+        <v>59</v>
       </c>
       <c r="BX5">
-        <v>0.6</v>
+        <v>60</v>
       </c>
       <c r="BY5">
-        <v>0.38</v>
+        <v>38</v>
       </c>
       <c r="BZ5">
-        <v>0.52</v>
+        <v>52</v>
       </c>
       <c r="CA5">
-        <v>0.28999999999999998</v>
+        <v>28.999999999999996</v>
       </c>
       <c r="CB5">
-        <v>0.75</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:80" x14ac:dyDescent="0.25">
@@ -2172,7 +2172,7 @@
         <v>76</v>
       </c>
       <c r="BC6">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="BD6">
         <v>27</v>
@@ -2220,34 +2220,34 @@
         <v>20.6</v>
       </c>
       <c r="BS6">
-        <v>0.27</v>
+        <v>27</v>
       </c>
       <c r="BT6">
-        <v>0.93</v>
+        <v>93</v>
       </c>
       <c r="BU6">
-        <v>0.87</v>
+        <v>87</v>
       </c>
       <c r="BV6">
-        <v>0.88</v>
+        <v>88</v>
       </c>
       <c r="BW6">
-        <v>0.57999999999999996</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="BX6">
-        <v>0.57999999999999996</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="BY6">
-        <v>0.30000000000000004</v>
+        <v>30.000000000000004</v>
       </c>
       <c r="BZ6">
-        <v>0.36</v>
+        <v>36</v>
       </c>
       <c r="CA6">
-        <v>0.19</v>
+        <v>19</v>
       </c>
       <c r="CB6">
-        <v>0.35</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:80" x14ac:dyDescent="0.25">
@@ -2414,7 +2414,7 @@
         <v>57</v>
       </c>
       <c r="BC7">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="BD7">
         <v>50</v>
@@ -2462,34 +2462,34 @@
         <v>19.5</v>
       </c>
       <c r="BS7">
-        <v>0.42</v>
+        <v>42</v>
       </c>
       <c r="BT7">
-        <v>0.77</v>
+        <v>77</v>
       </c>
       <c r="BU7">
-        <v>0.57999999999999996</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="BV7">
-        <v>0.59</v>
+        <v>59</v>
       </c>
       <c r="BW7">
-        <v>0.56000000000000005</v>
+        <v>56.000000000000007</v>
       </c>
       <c r="BX7">
-        <v>0.56999999999999995</v>
+        <v>56.999999999999993</v>
       </c>
       <c r="BY7">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="BZ7">
-        <v>0.63</v>
+        <v>63</v>
       </c>
       <c r="CA7">
-        <v>0.28000000000000003</v>
+        <v>28.000000000000004</v>
       </c>
       <c r="CB7">
-        <v>0.66</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:80" x14ac:dyDescent="0.25">
@@ -2656,7 +2656,7 @@
         <v>81</v>
       </c>
       <c r="BC8">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="BD8">
         <v>38</v>
@@ -2704,34 +2704,34 @@
         <v>33.5</v>
       </c>
       <c r="BS8">
-        <v>0.63</v>
+        <v>63</v>
       </c>
       <c r="BT8">
-        <v>0.57999999999999996</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="BU8">
-        <v>0.45</v>
+        <v>45</v>
       </c>
       <c r="BV8">
-        <v>0.4</v>
+        <v>40</v>
       </c>
       <c r="BW8">
-        <v>0.53</v>
+        <v>53</v>
       </c>
       <c r="BX8">
-        <v>0.49</v>
+        <v>49</v>
       </c>
       <c r="BY8">
-        <v>0.12</v>
+        <v>12</v>
       </c>
       <c r="BZ8">
-        <v>0.66</v>
+        <v>66</v>
       </c>
       <c r="CA8">
-        <v>0.28999999999999998</v>
+        <v>28.999999999999996</v>
       </c>
       <c r="CB8">
-        <v>0.83</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:80" x14ac:dyDescent="0.25">
@@ -2898,7 +2898,7 @@
         <v>50</v>
       </c>
       <c r="BC9">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="BD9">
         <v>49</v>
@@ -2946,34 +2946,34 @@
         <v>36.4</v>
       </c>
       <c r="BS9">
-        <v>0.53</v>
+        <v>53</v>
       </c>
       <c r="BT9">
-        <v>0.87</v>
+        <v>87</v>
       </c>
       <c r="BU9">
-        <v>0.78</v>
+        <v>78</v>
       </c>
       <c r="BV9">
-        <v>0.7</v>
+        <v>70</v>
       </c>
       <c r="BW9">
-        <v>0.55000000000000004</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="BX9">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="BY9">
-        <v>0.21</v>
+        <v>21</v>
       </c>
       <c r="BZ9">
-        <v>0.61</v>
+        <v>61</v>
       </c>
       <c r="CA9">
-        <v>0.3</v>
+        <v>30</v>
       </c>
       <c r="CB9">
-        <v>0.78</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:80" x14ac:dyDescent="0.25">
@@ -3140,7 +3140,7 @@
         <v>77</v>
       </c>
       <c r="BC10">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="BD10">
         <v>48</v>
@@ -3188,34 +3188,34 @@
         <v>46</v>
       </c>
       <c r="BS10">
-        <v>0.51</v>
+        <v>51</v>
       </c>
       <c r="BT10">
-        <v>0.84</v>
+        <v>84</v>
       </c>
       <c r="BU10">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="BV10">
-        <v>0.69</v>
+        <v>69</v>
       </c>
       <c r="BW10">
-        <v>0.46</v>
+        <v>46</v>
       </c>
       <c r="BX10">
-        <v>0.45</v>
+        <v>45</v>
       </c>
       <c r="BY10">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="BZ10">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="CA10">
-        <v>0.21</v>
+        <v>21</v>
       </c>
       <c r="CB10">
-        <v>0.6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:80" x14ac:dyDescent="0.25">
@@ -3382,7 +3382,7 @@
         <v>88</v>
       </c>
       <c r="BC11">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="BD11">
         <v>30</v>
@@ -3430,34 +3430,34 @@
         <v>27.8</v>
       </c>
       <c r="BS11">
-        <v>0.6</v>
+        <v>60</v>
       </c>
       <c r="BT11">
-        <v>0.77</v>
+        <v>77</v>
       </c>
       <c r="BU11">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="BV11">
-        <v>0.76</v>
+        <v>76</v>
       </c>
       <c r="BW11">
-        <v>0.67</v>
+        <v>67</v>
       </c>
       <c r="BX11">
-        <v>0.69</v>
+        <v>69</v>
       </c>
       <c r="BY11">
-        <v>0.23</v>
+        <v>23</v>
       </c>
       <c r="BZ11">
-        <v>0.68</v>
+        <v>68</v>
       </c>
       <c r="CA11">
-        <v>0.41</v>
+        <v>41</v>
       </c>
       <c r="CB11">
-        <v>0.78</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:80" x14ac:dyDescent="0.25">
@@ -3624,7 +3624,7 @@
         <v>71</v>
       </c>
       <c r="BC12">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="BD12">
         <v>30</v>
@@ -3672,34 +3672,34 @@
         <v>26.6</v>
       </c>
       <c r="BS12">
-        <v>0.14000000000000001</v>
+        <v>14.000000000000002</v>
       </c>
       <c r="BT12">
-        <v>0.82</v>
+        <v>82</v>
       </c>
       <c r="BU12">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="BV12">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="BW12">
-        <v>0.71</v>
+        <v>71</v>
       </c>
       <c r="BX12">
-        <v>0.69</v>
+        <v>69</v>
       </c>
       <c r="BY12">
-        <v>0.36000000000000004</v>
+        <v>36.000000000000007</v>
       </c>
       <c r="BZ12">
-        <v>0.38</v>
+        <v>38</v>
       </c>
       <c r="CA12">
-        <v>0.17</v>
+        <v>17</v>
       </c>
       <c r="CB12">
-        <v>0.32</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:80" x14ac:dyDescent="0.25">
@@ -3866,7 +3866,7 @@
         <v>57</v>
       </c>
       <c r="BC13">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="BD13">
         <v>45</v>
@@ -3914,34 +3914,34 @@
         <v>19.600000000000001</v>
       </c>
       <c r="BS13">
-        <v>0.46</v>
+        <v>46</v>
       </c>
       <c r="BT13">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="BU13">
-        <v>0.79</v>
+        <v>79</v>
       </c>
       <c r="BV13">
-        <v>0.77</v>
+        <v>77</v>
       </c>
       <c r="BW13">
-        <v>0.74</v>
+        <v>74</v>
       </c>
       <c r="BX13">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="BY13">
-        <v>0.24</v>
+        <v>24</v>
       </c>
       <c r="BZ13">
-        <v>0.42</v>
+        <v>42</v>
       </c>
       <c r="CA13">
-        <v>0.26</v>
+        <v>26</v>
       </c>
       <c r="CB13">
-        <v>0.59</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:80" x14ac:dyDescent="0.25">
@@ -4108,7 +4108,7 @@
         <v>47</v>
       </c>
       <c r="BC14">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="BD14">
         <v>50</v>
@@ -4156,34 +4156,34 @@
         <v>18.2</v>
       </c>
       <c r="BS14">
-        <v>0.55000000000000004</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="BT14">
-        <v>0.85</v>
+        <v>85</v>
       </c>
       <c r="BU14">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="BV14">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="BW14">
-        <v>0.61</v>
+        <v>61</v>
       </c>
       <c r="BX14">
-        <v>0.56000000000000005</v>
+        <v>56.000000000000007</v>
       </c>
       <c r="BY14">
-        <v>0.21000000000000002</v>
+        <v>21.000000000000004</v>
       </c>
       <c r="BZ14">
-        <v>0.46</v>
+        <v>46</v>
       </c>
       <c r="CA14">
-        <v>0.18</v>
+        <v>18</v>
       </c>
       <c r="CB14">
-        <v>0.61</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:80" x14ac:dyDescent="0.25">
@@ -4350,7 +4350,7 @@
         <v>68</v>
       </c>
       <c r="BC15">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="BD15">
         <v>38</v>
@@ -4398,34 +4398,34 @@
         <v>37.1</v>
       </c>
       <c r="BS15">
-        <v>0.23</v>
+        <v>23</v>
       </c>
       <c r="BT15">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="BU15">
-        <v>0.77</v>
+        <v>77</v>
       </c>
       <c r="BV15">
-        <v>0.79</v>
+        <v>79</v>
       </c>
       <c r="BW15">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="BX15">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="BY15">
-        <v>0.36000000000000004</v>
+        <v>36.000000000000007</v>
       </c>
       <c r="BZ15">
-        <v>0.49</v>
+        <v>49</v>
       </c>
       <c r="CA15">
-        <v>0.28999999999999998</v>
+        <v>28.999999999999996</v>
       </c>
       <c r="CB15">
-        <v>0.52</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:80" x14ac:dyDescent="0.25">
@@ -4592,7 +4592,7 @@
         <v>60</v>
       </c>
       <c r="BC16">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="BD16">
         <v>50</v>
@@ -4640,34 +4640,34 @@
         <v>29.8</v>
       </c>
       <c r="BS16">
-        <v>0.39</v>
+        <v>39</v>
       </c>
       <c r="BT16">
-        <v>0.82</v>
+        <v>82</v>
       </c>
       <c r="BU16">
-        <v>0.81</v>
+        <v>81</v>
       </c>
       <c r="BV16">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="BW16">
-        <v>0.66</v>
+        <v>66</v>
       </c>
       <c r="BX16">
-        <v>0.65</v>
+        <v>65</v>
       </c>
       <c r="BY16">
-        <v>0.31000000000000005</v>
+        <v>31.000000000000007</v>
       </c>
       <c r="BZ16">
-        <v>0.47</v>
+        <v>47</v>
       </c>
       <c r="CA16">
-        <v>0.3</v>
+        <v>30</v>
       </c>
       <c r="CB16">
-        <v>0.6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:80" x14ac:dyDescent="0.25">
@@ -4834,7 +4834,7 @@
         <v>72</v>
       </c>
       <c r="BC17">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="BD17">
         <v>29</v>
@@ -4882,34 +4882,34 @@
         <v>27.4</v>
       </c>
       <c r="BS17">
-        <v>0.21</v>
+        <v>21</v>
       </c>
       <c r="BT17">
-        <v>0.81</v>
+        <v>81</v>
       </c>
       <c r="BU17">
-        <v>0.88</v>
+        <v>88</v>
       </c>
       <c r="BV17">
-        <v>0.85</v>
+        <v>85</v>
       </c>
       <c r="BW17">
-        <v>0.76</v>
+        <v>76</v>
       </c>
       <c r="BX17">
-        <v>0.74</v>
+        <v>74</v>
       </c>
       <c r="BY17">
-        <v>0.23</v>
+        <v>23</v>
       </c>
       <c r="BZ17">
-        <v>0.49</v>
+        <v>49</v>
       </c>
       <c r="CA17">
-        <v>0.36</v>
+        <v>36</v>
       </c>
       <c r="CB17">
-        <v>0.48</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:80" x14ac:dyDescent="0.25">
@@ -5076,7 +5076,7 @@
         <v>73</v>
       </c>
       <c r="BC18">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="BD18">
         <v>38</v>
@@ -5124,34 +5124,34 @@
         <v>23.8</v>
       </c>
       <c r="BS18">
-        <v>0.42</v>
+        <v>42</v>
       </c>
       <c r="BT18">
-        <v>0.86</v>
+        <v>86</v>
       </c>
       <c r="BU18">
-        <v>0.84</v>
+        <v>84</v>
       </c>
       <c r="BV18">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="BW18">
-        <v>0.59</v>
+        <v>59</v>
       </c>
       <c r="BX18">
-        <v>0.63</v>
+        <v>63</v>
       </c>
       <c r="BY18">
-        <v>0.41000000000000003</v>
+        <v>41</v>
       </c>
       <c r="BZ18">
-        <v>0.46</v>
+        <v>46</v>
       </c>
       <c r="CA18">
-        <v>0.21</v>
+        <v>21</v>
       </c>
       <c r="CB18">
-        <v>0.49</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:80" x14ac:dyDescent="0.25">
@@ -5318,7 +5318,7 @@
         <v>78</v>
       </c>
       <c r="BC19">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="BD19">
         <v>36</v>
@@ -5366,34 +5366,34 @@
         <v>24</v>
       </c>
       <c r="BS19">
-        <v>0.54</v>
+        <v>54</v>
       </c>
       <c r="BT19">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="BU19">
-        <v>0.88</v>
+        <v>88</v>
       </c>
       <c r="BV19">
-        <v>0.83</v>
+        <v>83</v>
       </c>
       <c r="BW19">
-        <v>0.68</v>
+        <v>68</v>
       </c>
       <c r="BX19">
-        <v>0.68</v>
+        <v>68</v>
       </c>
       <c r="BY19">
-        <v>0.19</v>
+        <v>19</v>
       </c>
       <c r="BZ19">
-        <v>0.45</v>
+        <v>45</v>
       </c>
       <c r="CA19">
-        <v>0.28000000000000003</v>
+        <v>28.000000000000004</v>
       </c>
       <c r="CB19">
-        <v>0.61</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:80" x14ac:dyDescent="0.25">
@@ -5560,7 +5560,7 @@
         <v>81</v>
       </c>
       <c r="BC20">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="BD20">
         <v>30</v>
@@ -5608,34 +5608,34 @@
         <v>29.7</v>
       </c>
       <c r="BS20">
-        <v>0.66</v>
+        <v>66</v>
       </c>
       <c r="BT20">
-        <v>0.79</v>
+        <v>79</v>
       </c>
       <c r="BU20">
-        <v>0.74</v>
+        <v>74</v>
       </c>
       <c r="BV20">
-        <v>0.64</v>
+        <v>64</v>
       </c>
       <c r="BW20">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="BX20">
-        <v>0.63</v>
+        <v>63</v>
       </c>
       <c r="BY20">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="BZ20">
-        <v>0.62</v>
+        <v>62</v>
       </c>
       <c r="CA20">
-        <v>0.39</v>
+        <v>39</v>
       </c>
       <c r="CB20">
-        <v>0.89</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:80" x14ac:dyDescent="0.25">
@@ -5802,7 +5802,7 @@
         <v>72</v>
       </c>
       <c r="BC21">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="BD21">
         <v>29</v>
@@ -5850,34 +5850,34 @@
         <v>29.8</v>
       </c>
       <c r="BS21">
-        <v>0.37</v>
+        <v>37</v>
       </c>
       <c r="BT21">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="BU21">
-        <v>0.85</v>
+        <v>85</v>
       </c>
       <c r="BV21">
-        <v>0.77</v>
+        <v>77</v>
       </c>
       <c r="BW21">
-        <v>0.63</v>
+        <v>63</v>
       </c>
       <c r="BX21">
-        <v>0.61</v>
+        <v>61</v>
       </c>
       <c r="BY21">
-        <v>0.16999999999999998</v>
+        <v>17</v>
       </c>
       <c r="BZ21">
-        <v>0.55000000000000004</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="CA21">
-        <v>0.37</v>
+        <v>37</v>
       </c>
       <c r="CB21">
-        <v>0.64</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:80" x14ac:dyDescent="0.25">
@@ -6044,7 +6044,7 @@
         <v>86</v>
       </c>
       <c r="BC22">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="BD22">
         <v>26</v>
@@ -6092,34 +6092,34 @@
         <v>31.5</v>
       </c>
       <c r="BS22">
-        <v>0.53</v>
+        <v>53</v>
       </c>
       <c r="BT22">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="BU22">
-        <v>0.87</v>
+        <v>87</v>
       </c>
       <c r="BV22">
-        <v>0.87</v>
+        <v>87</v>
       </c>
       <c r="BW22">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="BX22">
-        <v>0.73</v>
+        <v>73</v>
       </c>
       <c r="BY22">
-        <v>0.27</v>
+        <v>27</v>
       </c>
       <c r="BZ22">
-        <v>0.56999999999999995</v>
+        <v>56.999999999999993</v>
       </c>
       <c r="CA22">
-        <v>0.38</v>
+        <v>38</v>
       </c>
       <c r="CB22">
-        <v>0.52</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:80" x14ac:dyDescent="0.25">
@@ -6286,7 +6286,7 @@
         <v>72</v>
       </c>
       <c r="BC23">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="BD23">
         <v>42</v>
@@ -6334,34 +6334,34 @@
         <v>31.2</v>
       </c>
       <c r="BS23">
-        <v>0.35</v>
+        <v>35</v>
       </c>
       <c r="BT23">
-        <v>0.73</v>
+        <v>73</v>
       </c>
       <c r="BU23">
-        <v>0.73</v>
+        <v>73</v>
       </c>
       <c r="BV23">
-        <v>0.57999999999999996</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="BW23">
-        <v>0.67</v>
+        <v>67</v>
       </c>
       <c r="BX23">
-        <v>0.6</v>
+        <v>60</v>
       </c>
       <c r="BY23">
-        <v>9.9999999999999992E-2</v>
+        <v>10</v>
       </c>
       <c r="BZ23">
-        <v>0.73</v>
+        <v>73</v>
       </c>
       <c r="CA23">
-        <v>0.27</v>
+        <v>27</v>
       </c>
       <c r="CB23">
-        <v>0.79</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:80" x14ac:dyDescent="0.25">
@@ -6528,7 +6528,7 @@
         <v>65</v>
       </c>
       <c r="BC24">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="BD24">
         <v>38</v>
@@ -6576,34 +6576,34 @@
         <v>28.7</v>
       </c>
       <c r="BS24">
-        <v>0.56999999999999995</v>
+        <v>56.999999999999993</v>
       </c>
       <c r="BT24">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="BU24">
-        <v>0.82</v>
+        <v>82</v>
       </c>
       <c r="BV24">
-        <v>0.7</v>
+        <v>70</v>
       </c>
       <c r="BW24">
-        <v>0.78</v>
+        <v>78</v>
       </c>
       <c r="BX24">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="BY24">
-        <v>0.53</v>
+        <v>53</v>
       </c>
       <c r="BZ24">
-        <v>0.71</v>
+        <v>71</v>
       </c>
       <c r="CA24">
-        <v>0.4</v>
+        <v>40</v>
       </c>
       <c r="CB24">
-        <v>0.81</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:80" x14ac:dyDescent="0.25">
@@ -6770,7 +6770,7 @@
         <v>52</v>
       </c>
       <c r="BC25">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="BD25">
         <v>42</v>
@@ -6818,34 +6818,34 @@
         <v>23.3</v>
       </c>
       <c r="BS25">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="BT25">
-        <v>0.76</v>
+        <v>76</v>
       </c>
       <c r="BU25">
-        <v>0.73</v>
+        <v>73</v>
       </c>
       <c r="BV25">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="BW25">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="BX25">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="BY25">
-        <v>0.19</v>
+        <v>19</v>
       </c>
       <c r="BZ25">
-        <v>0.66</v>
+        <v>66</v>
       </c>
       <c r="CA25">
-        <v>0.49</v>
+        <v>49</v>
       </c>
       <c r="CB25">
-        <v>0.73</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:80" x14ac:dyDescent="0.25">
@@ -7012,7 +7012,7 @@
         <v>79</v>
       </c>
       <c r="BC26">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="BD26">
         <v>43</v>
@@ -7060,34 +7060,34 @@
         <v>30.1</v>
       </c>
       <c r="BS26">
-        <v>0.35</v>
+        <v>35</v>
       </c>
       <c r="BT26">
-        <v>0.94</v>
+        <v>94</v>
       </c>
       <c r="BU26">
-        <v>0.93</v>
+        <v>93</v>
       </c>
       <c r="BV26">
-        <v>0.92</v>
+        <v>92</v>
       </c>
       <c r="BW26">
-        <v>0.57999999999999996</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="BX26">
-        <v>0.52</v>
+        <v>52</v>
       </c>
       <c r="BY26">
-        <v>0.22999999999999998</v>
+        <v>23</v>
       </c>
       <c r="BZ26">
-        <v>0.48</v>
+        <v>48</v>
       </c>
       <c r="CA26">
-        <v>0.38</v>
+        <v>38</v>
       </c>
       <c r="CB26">
-        <v>0.68</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:80" x14ac:dyDescent="0.25">
@@ -7254,7 +7254,7 @@
         <v>84</v>
       </c>
       <c r="BC27">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="BD27">
         <v>32</v>
@@ -7302,34 +7302,34 @@
         <v>27.1</v>
       </c>
       <c r="BS27">
-        <v>0.4</v>
+        <v>40</v>
       </c>
       <c r="BT27">
-        <v>0.69</v>
+        <v>69</v>
       </c>
       <c r="BU27">
-        <v>0.67</v>
+        <v>67</v>
       </c>
       <c r="BV27">
-        <v>0.64</v>
+        <v>64</v>
       </c>
       <c r="BW27">
-        <v>0.57999999999999996</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="BX27">
-        <v>0.56999999999999995</v>
+        <v>56.999999999999993</v>
       </c>
       <c r="BY27">
-        <v>0.35000000000000003</v>
+        <v>35</v>
       </c>
       <c r="BZ27">
-        <v>0.44</v>
+        <v>44</v>
       </c>
       <c r="CA27">
-        <v>0.3</v>
+        <v>30</v>
       </c>
       <c r="CB27">
-        <v>0.47</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:80" x14ac:dyDescent="0.25">
@@ -7496,7 +7496,7 @@
         <v>72</v>
       </c>
       <c r="BC28">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="BD28">
         <v>37</v>
@@ -7544,34 +7544,34 @@
         <v>36.1</v>
       </c>
       <c r="BS28">
-        <v>0.3</v>
+        <v>30</v>
       </c>
       <c r="BT28">
-        <v>0.84</v>
+        <v>84</v>
       </c>
       <c r="BU28">
-        <v>0.82</v>
+        <v>82</v>
       </c>
       <c r="BV28">
-        <v>0.81</v>
+        <v>81</v>
       </c>
       <c r="BW28">
-        <v>0.69</v>
+        <v>69</v>
       </c>
       <c r="BX28">
-        <v>0.7</v>
+        <v>70</v>
       </c>
       <c r="BY28">
-        <v>0.4</v>
+        <v>40</v>
       </c>
       <c r="BZ28">
-        <v>0.48</v>
+        <v>48</v>
       </c>
       <c r="CA28">
-        <v>0.27</v>
+        <v>27</v>
       </c>
       <c r="CB28">
-        <v>0.49</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:80" x14ac:dyDescent="0.25">
@@ -7738,7 +7738,7 @@
         <v>72</v>
       </c>
       <c r="BC29">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="BD29">
         <v>39</v>
@@ -7786,34 +7786,34 @@
         <v>40.200000000000003</v>
       </c>
       <c r="BS29">
-        <v>0.33</v>
+        <v>33</v>
       </c>
       <c r="BT29">
-        <v>0.81</v>
+        <v>81</v>
       </c>
       <c r="BU29">
-        <v>0.79</v>
+        <v>79</v>
       </c>
       <c r="BV29">
-        <v>0.76</v>
+        <v>76</v>
       </c>
       <c r="BW29">
-        <v>0.52</v>
+        <v>52</v>
       </c>
       <c r="BX29">
-        <v>0.51</v>
+        <v>51</v>
       </c>
       <c r="BY29">
-        <v>0.30000000000000004</v>
+        <v>30.000000000000004</v>
       </c>
       <c r="BZ29">
-        <v>0.52</v>
+        <v>52</v>
       </c>
       <c r="CA29">
-        <v>0.33</v>
+        <v>33</v>
       </c>
       <c r="CB29">
-        <v>0.49</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:80" x14ac:dyDescent="0.25">
@@ -7980,7 +7980,7 @@
         <v>76</v>
       </c>
       <c r="BC30">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="BD30">
         <v>43</v>
@@ -8028,34 +8028,34 @@
         <v>37.1</v>
       </c>
       <c r="BS30">
-        <v>0.69</v>
+        <v>69</v>
       </c>
       <c r="BT30">
-        <v>0.57999999999999996</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="BU30">
-        <v>0.57999999999999996</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="BV30">
-        <v>0.52</v>
+        <v>52</v>
       </c>
       <c r="BW30">
-        <v>0.62</v>
+        <v>62</v>
       </c>
       <c r="BX30">
-        <v>0.62</v>
+        <v>62</v>
       </c>
       <c r="BY30">
-        <v>0.21</v>
+        <v>21</v>
       </c>
       <c r="BZ30">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="CA30">
-        <v>0.27</v>
+        <v>27</v>
       </c>
       <c r="CB30">
-        <v>0.92</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:80" x14ac:dyDescent="0.25">
@@ -8222,7 +8222,7 @@
         <v>57</v>
       </c>
       <c r="BC31">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="BD31">
         <v>50</v>
@@ -8270,34 +8270,34 @@
         <v>39.1</v>
       </c>
       <c r="BS31">
-        <v>0.65</v>
+        <v>65</v>
       </c>
       <c r="BT31">
-        <v>0.68</v>
+        <v>68</v>
       </c>
       <c r="BU31">
-        <v>0.64</v>
+        <v>64</v>
       </c>
       <c r="BV31">
-        <v>0.49</v>
+        <v>49</v>
       </c>
       <c r="BW31">
-        <v>0.55000000000000004</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="BX31">
-        <v>0.57999999999999996</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="BY31">
-        <v>0.17000000000000004</v>
+        <v>17.000000000000004</v>
       </c>
       <c r="BZ31">
-        <v>0.67</v>
+        <v>67</v>
       </c>
       <c r="CA31">
-        <v>0.22</v>
+        <v>22</v>
       </c>
       <c r="CB31">
-        <v>0.89</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:80" x14ac:dyDescent="0.25">

--- a/SC Indicators Data Prep.xlsx
+++ b/SC Indicators Data Prep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emree\Desktop\CO3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3580F4B-A12B-4EB2-B43C-B3D415990C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288E9763-E6B1-4FD3-8A25-48FCFF7B6D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{55AA29CC-CDDC-4D64-AC5C-6644C21888DE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="147">
   <si>
     <t>Voted</t>
   </si>
@@ -137,9 +137,6 @@
     <t>Impact of the EU on the Daily Life</t>
   </si>
   <si>
-    <t>EU27</t>
-  </si>
-  <si>
     <t>CSOs are Important</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
     <t>Trust in The Police</t>
   </si>
   <si>
-    <t>Trust in L'armée</t>
-  </si>
-  <si>
     <t>Trust in Regional or local public authorities</t>
   </si>
   <si>
@@ -341,9 +335,6 @@
     <t>Agree-Nowadays in (YOUR COUNTRY) you have equal opportunities for getting ahead in life, like everyone else</t>
   </si>
   <si>
-    <t>Agree-Aujourd’hui, en (NOTRE PAYS), les différences de revenus entre les gens sont trop importantes</t>
-  </si>
-  <si>
     <t>Agree-The (NATIONALITY) government should take measures to reduce differences in income levels</t>
   </si>
   <si>
@@ -420,6 +411,72 @@
   </si>
   <si>
     <t>INDICATORS</t>
+  </si>
+  <si>
+    <t>EU</t>
+  </si>
+  <si>
+    <t>Familiarity with the EU Citizenship</t>
+  </si>
+  <si>
+    <t>Citizenship</t>
+  </si>
+  <si>
+    <t>Being informed about the EU Citizenship</t>
+  </si>
+  <si>
+    <t>Feeling as a European Citizen</t>
+  </si>
+  <si>
+    <t>Knowing Rights as a EU Citizen</t>
+  </si>
+  <si>
+    <t>Demand for More Information about the EU Citizenship</t>
+  </si>
+  <si>
+    <t>Respect for nature and protection of climate and the environment</t>
+  </si>
+  <si>
+    <t>Social equality and welfare</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Peace</t>
+  </si>
+  <si>
+    <t>Progress and innovation</t>
+  </si>
+  <si>
+    <t>Respect for fundamental rights and values</t>
+  </si>
+  <si>
+    <t>Tolerance and openness to others</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Respect for history and its lessons</t>
+  </si>
+  <si>
+    <t>Solidarity with countries within and outside the EU</t>
+  </si>
+  <si>
+    <t>Freedom of speech and expression</t>
+  </si>
+  <si>
+    <t>Representing citizens’ economic and trade interests in the world</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respect fo Values- EU </t>
+  </si>
+  <si>
+    <t>Citizenship Rights</t>
+  </si>
+  <si>
+    <t>Feeling</t>
+  </si>
+  <si>
+    <t>Trust in the Army</t>
+  </si>
+  <si>
+    <t>Agree-Nowadays in (OUR COUNTRY) differences in people’s incomes are too great</t>
   </si>
 </sst>
 </file>
@@ -795,12 +852,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA6585B-C499-45AD-87BE-134F9272F3A6}">
-  <dimension ref="A1:CB32"/>
+  <dimension ref="A1:CQ63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
         <v>28</v>
@@ -992,84 +1049,129 @@
         <v>28</v>
       </c>
       <c r="BM1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BN1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BO1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BP1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BQ1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BR1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BS1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BT1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BU1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BV1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BW1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BX1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BY1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="BZ1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="CA1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="CB1" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
         <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K2" t="s">
         <v>29</v>
@@ -1093,82 +1195,82 @@
         <v>29</v>
       </c>
       <c r="R2" t="s">
+        <v>115</v>
+      </c>
+      <c r="S2" t="s">
+        <v>116</v>
+      </c>
+      <c r="T2" t="s">
+        <v>116</v>
+      </c>
+      <c r="U2" t="s">
+        <v>116</v>
+      </c>
+      <c r="V2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W2" t="s">
+        <v>116</v>
+      </c>
+      <c r="X2" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA2" t="s">
         <v>118</v>
       </c>
-      <c r="S2" t="s">
+      <c r="AB2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC2" t="s">
         <v>119</v>
       </c>
-      <c r="T2" t="s">
+      <c r="AD2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH2" t="s">
         <v>119</v>
       </c>
-      <c r="U2" t="s">
+      <c r="AI2" t="s">
         <v>119</v>
       </c>
-      <c r="V2" t="s">
+      <c r="AJ2" t="s">
         <v>119</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AK2" t="s">
         <v>119</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AL2" t="s">
         <v>119</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AM2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AO2" t="s">
         <v>119</v>
       </c>
-      <c r="Z2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>122</v>
-      </c>
       <c r="AP2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AQ2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AR2" t="s">
         <v>29</v>
@@ -1201,10 +1303,10 @@
         <v>29</v>
       </c>
       <c r="BB2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="BC2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="BD2" t="s">
         <v>29</v>
@@ -1234,57 +1336,102 @@
         <v>29</v>
       </c>
       <c r="BM2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="BN2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="BO2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="BP2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="BQ2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="BR2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="BS2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BW2" t="s">
         <v>106</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BX2" t="s">
         <v>106</v>
       </c>
-      <c r="BU2" t="s">
-        <v>106</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>106</v>
-      </c>
-      <c r="BW2" t="s">
+      <c r="BY2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BZ2" t="s">
         <v>109</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="CA2" t="s">
         <v>109</v>
       </c>
-      <c r="BY2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BZ2" t="s">
-        <v>112</v>
-      </c>
-      <c r="CA2" t="s">
-        <v>112</v>
-      </c>
       <c r="CB2" t="s">
-        <v>112</v>
+        <v>109</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>144</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>143</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>144</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>143</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>143</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -1299,234 +1446,279 @@
         <v>32</v>
       </c>
       <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>37</v>
       </c>
-      <c r="I3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>38</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>39</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>40</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>41</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>42</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>43</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>45</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>46</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>47</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>48</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
+        <v>145</v>
+      </c>
+      <c r="W3" t="s">
         <v>49</v>
       </c>
-      <c r="V3" t="s">
+      <c r="X3" t="s">
         <v>50</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Y3" t="s">
         <v>51</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Z3" t="s">
         <v>52</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AA3" t="s">
         <v>53</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AB3" t="s">
         <v>54</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AC3" t="s">
         <v>55</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AD3" t="s">
         <v>56</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AE3" t="s">
         <v>57</v>
       </c>
-      <c r="AD3" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE3" t="s">
+      <c r="AF3" t="s">
         <v>59</v>
       </c>
-      <c r="AF3" t="s">
-        <v>61</v>
-      </c>
       <c r="AG3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH3" t="s">
         <v>62</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AI3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM3" t="s">
         <v>64</v>
       </c>
-      <c r="AI3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ3" t="s">
+      <c r="AN3" t="s">
         <v>68</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AO3" t="s">
         <v>69</v>
       </c>
-      <c r="AL3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN3" t="s">
+      <c r="AP3" t="s">
         <v>70</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AQ3" t="s">
         <v>71</v>
       </c>
-      <c r="AP3" t="s">
+      <c r="AR3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>88</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>90</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>91</v>
+      </c>
+      <c r="BD3" t="s">
         <v>72</v>
       </c>
-      <c r="AQ3" t="s">
+      <c r="BE3" t="s">
         <v>73</v>
       </c>
-      <c r="AR3" t="s">
-        <v>124</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>90</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>91</v>
-      </c>
-      <c r="BB3" t="s">
+      <c r="BF3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>75</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>76</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BM3" t="s">
         <v>92</v>
       </c>
-      <c r="BC3" t="s">
+      <c r="BN3" t="s">
         <v>93</v>
       </c>
-      <c r="BD3" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>76</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>77</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>78</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>79</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>81</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>82</v>
-      </c>
-      <c r="BM3" t="s">
+      <c r="BO3" t="s">
         <v>94</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BP3" t="s">
         <v>95</v>
       </c>
-      <c r="BO3" t="s">
+      <c r="BQ3" t="s">
         <v>96</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="BR3" t="s">
         <v>97</v>
       </c>
-      <c r="BQ3" t="s">
+      <c r="BS3" t="s">
         <v>98</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="BT3" t="s">
+        <v>146</v>
+      </c>
+      <c r="BU3" t="s">
         <v>99</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="BV3" t="s">
         <v>100</v>
       </c>
-      <c r="BT3" t="s">
-        <v>101</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>102</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>103</v>
-      </c>
       <c r="BW3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>105</v>
+      </c>
+      <c r="BY3" t="s">
         <v>107</v>
       </c>
-      <c r="BX3" t="s">
+      <c r="BZ3" t="s">
+        <v>110</v>
+      </c>
+      <c r="CA3" t="s">
+        <v>111</v>
+      </c>
+      <c r="CB3" t="s">
         <v>108</v>
       </c>
-      <c r="BY3" t="s">
-        <v>110</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>113</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>114</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>111</v>
+      <c r="CC3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>131</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CK3" t="s">
+        <v>135</v>
+      </c>
+      <c r="CL3" t="s">
+        <v>136</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>137</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>138</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>139</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>140</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="B4">
         <v>52</v>
@@ -1765,8 +1957,53 @@
       <c r="CB4">
         <v>66</v>
       </c>
+      <c r="CC4">
+        <v>91.3</v>
+      </c>
+      <c r="CD4">
+        <v>49.6</v>
+      </c>
+      <c r="CE4" s="1">
+        <v>74</v>
+      </c>
+      <c r="CF4" s="1">
+        <v>60</v>
+      </c>
+      <c r="CG4" s="1">
+        <v>70</v>
+      </c>
+      <c r="CH4">
+        <v>45.4</v>
+      </c>
+      <c r="CI4">
+        <v>49.3</v>
+      </c>
+      <c r="CJ4">
+        <v>45.4</v>
+      </c>
+      <c r="CK4">
+        <v>29.3</v>
+      </c>
+      <c r="CL4">
+        <v>53.1</v>
+      </c>
+      <c r="CM4">
+        <v>47.8</v>
+      </c>
+      <c r="CN4">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="CO4">
+        <v>47.6</v>
+      </c>
+      <c r="CP4">
+        <v>52.8</v>
+      </c>
+      <c r="CQ4">
+        <v>34.799999999999997</v>
+      </c>
     </row>
-    <row r="5" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -2007,8 +2244,53 @@
       <c r="CB5">
         <v>75</v>
       </c>
+      <c r="CC5">
+        <v>79.5</v>
+      </c>
+      <c r="CD5">
+        <v>35.1</v>
+      </c>
+      <c r="CE5" s="1">
+        <v>77</v>
+      </c>
+      <c r="CF5" s="1">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="CG5" s="1">
+        <v>71</v>
+      </c>
+      <c r="CH5">
+        <v>41</v>
+      </c>
+      <c r="CI5">
+        <v>49.2</v>
+      </c>
+      <c r="CJ5">
+        <v>43.5</v>
+      </c>
+      <c r="CK5">
+        <v>26.4</v>
+      </c>
+      <c r="CL5">
+        <v>49.6</v>
+      </c>
+      <c r="CM5">
+        <v>44.2</v>
+      </c>
+      <c r="CN5">
+        <v>32</v>
+      </c>
+      <c r="CO5">
+        <v>47</v>
+      </c>
+      <c r="CP5">
+        <v>51.8</v>
+      </c>
+      <c r="CQ5">
+        <v>35.299999999999997</v>
+      </c>
     </row>
-    <row r="6" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -2249,8 +2531,53 @@
       <c r="CB6">
         <v>35</v>
       </c>
+      <c r="CC6">
+        <v>95.8</v>
+      </c>
+      <c r="CD6">
+        <v>60.1</v>
+      </c>
+      <c r="CE6" s="1">
+        <v>59</v>
+      </c>
+      <c r="CF6" s="1">
+        <v>50</v>
+      </c>
+      <c r="CG6" s="1">
+        <v>73</v>
+      </c>
+      <c r="CH6">
+        <v>35.1</v>
+      </c>
+      <c r="CI6">
+        <v>33.6</v>
+      </c>
+      <c r="CJ6">
+        <v>28.1</v>
+      </c>
+      <c r="CK6">
+        <v>22.5</v>
+      </c>
+      <c r="CL6">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="CM6">
+        <v>37</v>
+      </c>
+      <c r="CN6">
+        <v>27.6</v>
+      </c>
+      <c r="CO6">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="CP6">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="CQ6">
+        <v>30.6</v>
+      </c>
     </row>
-    <row r="7" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2491,8 +2818,53 @@
       <c r="CB7">
         <v>66</v>
       </c>
+      <c r="CC7">
+        <v>86.9</v>
+      </c>
+      <c r="CD7">
+        <v>51.8</v>
+      </c>
+      <c r="CE7" s="1">
+        <v>65</v>
+      </c>
+      <c r="CF7" s="1">
+        <v>60</v>
+      </c>
+      <c r="CG7" s="1">
+        <v>66</v>
+      </c>
+      <c r="CH7">
+        <v>43</v>
+      </c>
+      <c r="CI7">
+        <v>35.4</v>
+      </c>
+      <c r="CJ7">
+        <v>37.5</v>
+      </c>
+      <c r="CK7">
+        <v>24.5</v>
+      </c>
+      <c r="CL7">
+        <v>40.4</v>
+      </c>
+      <c r="CM7">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="CN7">
+        <v>28.3</v>
+      </c>
+      <c r="CO7">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="CP7">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="CQ7">
+        <v>31.9</v>
+      </c>
     </row>
-    <row r="8" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2733,8 +3105,53 @@
       <c r="CB8">
         <v>83</v>
       </c>
+      <c r="CC8">
+        <v>94</v>
+      </c>
+      <c r="CD8">
+        <v>57</v>
+      </c>
+      <c r="CE8" s="1">
+        <v>83</v>
+      </c>
+      <c r="CF8" s="1">
+        <v>72</v>
+      </c>
+      <c r="CG8" s="1">
+        <v>64</v>
+      </c>
+      <c r="CH8">
+        <v>42.4</v>
+      </c>
+      <c r="CI8">
+        <v>49.6</v>
+      </c>
+      <c r="CJ8">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="CK8">
+        <v>30.7</v>
+      </c>
+      <c r="CL8">
+        <v>48.3</v>
+      </c>
+      <c r="CM8">
+        <v>39</v>
+      </c>
+      <c r="CN8">
+        <v>31.2</v>
+      </c>
+      <c r="CO8">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="CP8">
+        <v>50.8</v>
+      </c>
+      <c r="CQ8">
+        <v>37.4</v>
+      </c>
     </row>
-    <row r="9" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2975,8 +3392,53 @@
       <c r="CB9">
         <v>78</v>
       </c>
+      <c r="CC9">
+        <v>85.5</v>
+      </c>
+      <c r="CD9">
+        <v>60.6</v>
+      </c>
+      <c r="CE9" s="1">
+        <v>79</v>
+      </c>
+      <c r="CF9" s="1">
+        <v>71</v>
+      </c>
+      <c r="CG9" s="1">
+        <v>64</v>
+      </c>
+      <c r="CH9">
+        <v>45.4</v>
+      </c>
+      <c r="CI9">
+        <v>51.4</v>
+      </c>
+      <c r="CJ9">
+        <v>45.7</v>
+      </c>
+      <c r="CK9">
+        <v>26.4</v>
+      </c>
+      <c r="CL9">
+        <v>57.4</v>
+      </c>
+      <c r="CM9">
+        <v>49.1</v>
+      </c>
+      <c r="CN9">
+        <v>36</v>
+      </c>
+      <c r="CO9">
+        <v>47.8</v>
+      </c>
+      <c r="CP9">
+        <v>55.5</v>
+      </c>
+      <c r="CQ9">
+        <v>35.299999999999997</v>
+      </c>
     </row>
-    <row r="10" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -3217,8 +3679,53 @@
       <c r="CB10">
         <v>60</v>
       </c>
+      <c r="CC10">
+        <v>95.2</v>
+      </c>
+      <c r="CD10">
+        <v>62.9</v>
+      </c>
+      <c r="CE10" s="1">
+        <v>80</v>
+      </c>
+      <c r="CF10" s="1">
+        <v>65</v>
+      </c>
+      <c r="CG10" s="1">
+        <v>60</v>
+      </c>
+      <c r="CH10">
+        <v>59.8</v>
+      </c>
+      <c r="CI10">
+        <v>59.9</v>
+      </c>
+      <c r="CJ10">
+        <v>54.6</v>
+      </c>
+      <c r="CK10">
+        <v>29.6</v>
+      </c>
+      <c r="CL10">
+        <v>62.3</v>
+      </c>
+      <c r="CM10">
+        <v>56.9</v>
+      </c>
+      <c r="CN10">
+        <v>41.7</v>
+      </c>
+      <c r="CO10">
+        <v>52.7</v>
+      </c>
+      <c r="CP10">
+        <v>62.3</v>
+      </c>
+      <c r="CQ10">
+        <v>35.200000000000003</v>
+      </c>
     </row>
-    <row r="11" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -3459,8 +3966,53 @@
       <c r="CB11">
         <v>78</v>
       </c>
+      <c r="CC11">
+        <v>92.8</v>
+      </c>
+      <c r="CD11">
+        <v>54.8</v>
+      </c>
+      <c r="CE11" s="1">
+        <v>84</v>
+      </c>
+      <c r="CF11" s="1">
+        <v>74</v>
+      </c>
+      <c r="CG11" s="1">
+        <v>72</v>
+      </c>
+      <c r="CH11">
+        <v>41.7</v>
+      </c>
+      <c r="CI11">
+        <v>53.9</v>
+      </c>
+      <c r="CJ11">
+        <v>48.8</v>
+      </c>
+      <c r="CK11">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="CL11">
+        <v>49.2</v>
+      </c>
+      <c r="CM11">
+        <v>50.1</v>
+      </c>
+      <c r="CN11">
+        <v>38.4</v>
+      </c>
+      <c r="CO11">
+        <v>47.9</v>
+      </c>
+      <c r="CP11">
+        <v>48.7</v>
+      </c>
+      <c r="CQ11">
+        <v>48.2</v>
+      </c>
     </row>
-    <row r="12" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -3701,8 +4253,53 @@
       <c r="CB12">
         <v>32</v>
       </c>
+      <c r="CC12">
+        <v>90.2</v>
+      </c>
+      <c r="CD12">
+        <v>41.8</v>
+      </c>
+      <c r="CE12" s="1">
+        <v>61</v>
+      </c>
+      <c r="CF12" s="1">
+        <v>47</v>
+      </c>
+      <c r="CG12" s="1">
+        <v>78</v>
+      </c>
+      <c r="CH12">
+        <v>37.5</v>
+      </c>
+      <c r="CI12">
+        <v>42</v>
+      </c>
+      <c r="CJ12">
+        <v>38.1</v>
+      </c>
+      <c r="CK12">
+        <v>27</v>
+      </c>
+      <c r="CL12">
+        <v>47.3</v>
+      </c>
+      <c r="CM12">
+        <v>45.3</v>
+      </c>
+      <c r="CN12">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="CO12">
+        <v>39.1</v>
+      </c>
+      <c r="CP12">
+        <v>45.8</v>
+      </c>
+      <c r="CQ12">
+        <v>29.3</v>
+      </c>
     </row>
-    <row r="13" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -3943,8 +4540,53 @@
       <c r="CB13">
         <v>59</v>
       </c>
+      <c r="CC13">
+        <v>97.8</v>
+      </c>
+      <c r="CD13">
+        <v>45</v>
+      </c>
+      <c r="CE13" s="1">
+        <v>84</v>
+      </c>
+      <c r="CF13" s="1">
+        <v>66</v>
+      </c>
+      <c r="CG13" s="1">
+        <v>81</v>
+      </c>
+      <c r="CH13">
+        <v>48.1</v>
+      </c>
+      <c r="CI13">
+        <v>57.1</v>
+      </c>
+      <c r="CJ13">
+        <v>49.5</v>
+      </c>
+      <c r="CK13">
+        <v>37.5</v>
+      </c>
+      <c r="CL13">
+        <v>59.7</v>
+      </c>
+      <c r="CM13">
+        <v>55.1</v>
+      </c>
+      <c r="CN13">
+        <v>43.6</v>
+      </c>
+      <c r="CO13">
+        <v>52.3</v>
+      </c>
+      <c r="CP13">
+        <v>56.2</v>
+      </c>
+      <c r="CQ13">
+        <v>39.799999999999997</v>
+      </c>
     </row>
-    <row r="14" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -4185,8 +4827,53 @@
       <c r="CB14">
         <v>61</v>
       </c>
+      <c r="CC14">
+        <v>87.6</v>
+      </c>
+      <c r="CD14">
+        <v>26.1</v>
+      </c>
+      <c r="CE14" s="1">
+        <v>65</v>
+      </c>
+      <c r="CF14" s="1">
+        <v>47</v>
+      </c>
+      <c r="CG14" s="1">
+        <v>70</v>
+      </c>
+      <c r="CH14">
+        <v>41.3</v>
+      </c>
+      <c r="CI14">
+        <v>45.8</v>
+      </c>
+      <c r="CJ14">
+        <v>45.6</v>
+      </c>
+      <c r="CK14">
+        <v>22.9</v>
+      </c>
+      <c r="CL14">
+        <v>50</v>
+      </c>
+      <c r="CM14">
+        <v>42.9</v>
+      </c>
+      <c r="CN14">
+        <v>36.9</v>
+      </c>
+      <c r="CO14">
+        <v>47.8</v>
+      </c>
+      <c r="CP14">
+        <v>53.2</v>
+      </c>
+      <c r="CQ14">
+        <v>28.7</v>
+      </c>
     </row>
-    <row r="15" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -4427,8 +5114,53 @@
       <c r="CB15">
         <v>52</v>
       </c>
+      <c r="CC15">
+        <v>87.7</v>
+      </c>
+      <c r="CD15">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="CE15" s="1">
+        <v>72</v>
+      </c>
+      <c r="CF15" s="1">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="CG15" s="1">
+        <v>67</v>
+      </c>
+      <c r="CH15">
+        <v>48.6</v>
+      </c>
+      <c r="CI15">
+        <v>50.5</v>
+      </c>
+      <c r="CJ15">
+        <v>48.3</v>
+      </c>
+      <c r="CK15">
+        <v>30.4</v>
+      </c>
+      <c r="CL15">
+        <v>55</v>
+      </c>
+      <c r="CM15">
+        <v>52.4</v>
+      </c>
+      <c r="CN15">
+        <v>46.3</v>
+      </c>
+      <c r="CO15">
+        <v>55.4</v>
+      </c>
+      <c r="CP15">
+        <v>50.7</v>
+      </c>
+      <c r="CQ15">
+        <v>39.6</v>
+      </c>
     </row>
-    <row r="16" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -4669,8 +5401,53 @@
       <c r="CB16">
         <v>60</v>
       </c>
+      <c r="CC16">
+        <v>95.5</v>
+      </c>
+      <c r="CD16">
+        <v>51.1</v>
+      </c>
+      <c r="CE16" s="1">
+        <v>65</v>
+      </c>
+      <c r="CF16" s="1">
+        <v>44</v>
+      </c>
+      <c r="CG16" s="1">
+        <v>78</v>
+      </c>
+      <c r="CH16">
+        <v>44.3</v>
+      </c>
+      <c r="CI16">
+        <v>47.7</v>
+      </c>
+      <c r="CJ16">
+        <v>42.7</v>
+      </c>
+      <c r="CK16">
+        <v>27.7</v>
+      </c>
+      <c r="CL16">
+        <v>54.7</v>
+      </c>
+      <c r="CM16">
+        <v>48</v>
+      </c>
+      <c r="CN16">
+        <v>44</v>
+      </c>
+      <c r="CO16">
+        <v>48.7</v>
+      </c>
+      <c r="CP16">
+        <v>54.9</v>
+      </c>
+      <c r="CQ16">
+        <v>29.1</v>
+      </c>
     </row>
-    <row r="17" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -4911,8 +5688,53 @@
       <c r="CB17">
         <v>48</v>
       </c>
+      <c r="CC17">
+        <v>91.9</v>
+      </c>
+      <c r="CD17">
+        <v>40.6</v>
+      </c>
+      <c r="CE17" s="1">
+        <v>75</v>
+      </c>
+      <c r="CF17" s="1">
+        <v>74</v>
+      </c>
+      <c r="CG17" s="1">
+        <v>93</v>
+      </c>
+      <c r="CH17">
+        <v>49.6</v>
+      </c>
+      <c r="CI17">
+        <v>47.4</v>
+      </c>
+      <c r="CJ17">
+        <v>43.8</v>
+      </c>
+      <c r="CK17">
+        <v>26.8</v>
+      </c>
+      <c r="CL17">
+        <v>47.7</v>
+      </c>
+      <c r="CM17">
+        <v>46.8</v>
+      </c>
+      <c r="CN17">
+        <v>30.6</v>
+      </c>
+      <c r="CO17">
+        <v>47.5</v>
+      </c>
+      <c r="CP17">
+        <v>50</v>
+      </c>
+      <c r="CQ17">
+        <v>31.6</v>
+      </c>
     </row>
-    <row r="18" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -5153,8 +5975,53 @@
       <c r="CB18">
         <v>49</v>
       </c>
+      <c r="CC18">
+        <v>88</v>
+      </c>
+      <c r="CD18">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="CE18" s="1">
+        <v>82</v>
+      </c>
+      <c r="CF18" s="1">
+        <v>63</v>
+      </c>
+      <c r="CG18" s="1">
+        <v>66</v>
+      </c>
+      <c r="CH18">
+        <v>46.8</v>
+      </c>
+      <c r="CI18">
+        <v>45.7</v>
+      </c>
+      <c r="CJ18">
+        <v>48</v>
+      </c>
+      <c r="CK18">
+        <v>24.7</v>
+      </c>
+      <c r="CL18">
+        <v>47.4</v>
+      </c>
+      <c r="CM18">
+        <v>43.3</v>
+      </c>
+      <c r="CN18">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="CO18">
+        <v>48.3</v>
+      </c>
+      <c r="CP18">
+        <v>49</v>
+      </c>
+      <c r="CQ18">
+        <v>33.299999999999997</v>
+      </c>
     </row>
-    <row r="19" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -5395,8 +6262,53 @@
       <c r="CB19">
         <v>61</v>
       </c>
+      <c r="CC19">
+        <v>93</v>
+      </c>
+      <c r="CD19">
+        <v>53</v>
+      </c>
+      <c r="CE19" s="1">
+        <v>81</v>
+      </c>
+      <c r="CF19" s="1">
+        <v>72</v>
+      </c>
+      <c r="CG19" s="1">
+        <v>67</v>
+      </c>
+      <c r="CH19">
+        <v>53.1</v>
+      </c>
+      <c r="CI19">
+        <v>53.9</v>
+      </c>
+      <c r="CJ19">
+        <v>49.1</v>
+      </c>
+      <c r="CK19">
+        <v>33.9</v>
+      </c>
+      <c r="CL19">
+        <v>53.3</v>
+      </c>
+      <c r="CM19">
+        <v>51.5</v>
+      </c>
+      <c r="CN19">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="CO19">
+        <v>46.3</v>
+      </c>
+      <c r="CP19">
+        <v>54.8</v>
+      </c>
+      <c r="CQ19">
+        <v>41.3</v>
+      </c>
     </row>
-    <row r="20" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -5637,8 +6549,53 @@
       <c r="CB20">
         <v>89</v>
       </c>
+      <c r="CC20">
+        <v>87.1</v>
+      </c>
+      <c r="CD20">
+        <v>49.1</v>
+      </c>
+      <c r="CE20" s="1">
+        <v>88</v>
+      </c>
+      <c r="CF20" s="1">
+        <v>83</v>
+      </c>
+      <c r="CG20" s="1">
+        <v>80</v>
+      </c>
+      <c r="CH20">
+        <v>54</v>
+      </c>
+      <c r="CI20">
+        <v>73.7</v>
+      </c>
+      <c r="CJ20">
+        <v>68.2</v>
+      </c>
+      <c r="CK20">
+        <v>21.2</v>
+      </c>
+      <c r="CL20">
+        <v>75</v>
+      </c>
+      <c r="CM20">
+        <v>66.2</v>
+      </c>
+      <c r="CN20">
+        <v>46.5</v>
+      </c>
+      <c r="CO20">
+        <v>58.4</v>
+      </c>
+      <c r="CP20">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="CQ20">
+        <v>48.1</v>
+      </c>
     </row>
-    <row r="21" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -5879,8 +6836,53 @@
       <c r="CB21">
         <v>64</v>
       </c>
+      <c r="CC21">
+        <v>95.4</v>
+      </c>
+      <c r="CD21">
+        <v>58.5</v>
+      </c>
+      <c r="CE21" s="1">
+        <v>82</v>
+      </c>
+      <c r="CF21" s="1">
+        <v>66</v>
+      </c>
+      <c r="CG21" s="1">
+        <v>68</v>
+      </c>
+      <c r="CH21">
+        <v>33.4</v>
+      </c>
+      <c r="CI21">
+        <v>37.6</v>
+      </c>
+      <c r="CJ21">
+        <v>33.1</v>
+      </c>
+      <c r="CK21">
+        <v>23.9</v>
+      </c>
+      <c r="CL21">
+        <v>37.6</v>
+      </c>
+      <c r="CM21">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="CN21">
+        <v>25.5</v>
+      </c>
+      <c r="CO21">
+        <v>41.2</v>
+      </c>
+      <c r="CP21">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="CQ21">
+        <v>33.299999999999997</v>
+      </c>
     </row>
-    <row r="22" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -6121,8 +7123,53 @@
       <c r="CB22">
         <v>52</v>
       </c>
+      <c r="CC22">
+        <v>82.1</v>
+      </c>
+      <c r="CD22">
+        <v>49</v>
+      </c>
+      <c r="CE22" s="1">
+        <v>84</v>
+      </c>
+      <c r="CF22" s="1">
+        <v>63</v>
+      </c>
+      <c r="CG22" s="1">
+        <v>85</v>
+      </c>
+      <c r="CH22">
+        <v>43.7</v>
+      </c>
+      <c r="CI22">
+        <v>58.6</v>
+      </c>
+      <c r="CJ22">
+        <v>47.6</v>
+      </c>
+      <c r="CK22">
+        <v>30.2</v>
+      </c>
+      <c r="CL22">
+        <v>59.4</v>
+      </c>
+      <c r="CM22">
+        <v>58.7</v>
+      </c>
+      <c r="CN22">
+        <v>43.8</v>
+      </c>
+      <c r="CO22">
+        <v>46.9</v>
+      </c>
+      <c r="CP22">
+        <v>58</v>
+      </c>
+      <c r="CQ22">
+        <v>43.3</v>
+      </c>
     </row>
-    <row r="23" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -6363,8 +7410,53 @@
       <c r="CB23">
         <v>79</v>
       </c>
+      <c r="CC23">
+        <v>92.1</v>
+      </c>
+      <c r="CD23">
+        <v>51.1</v>
+      </c>
+      <c r="CE23" s="1">
+        <v>80</v>
+      </c>
+      <c r="CF23" s="1">
+        <v>69</v>
+      </c>
+      <c r="CG23" s="1">
+        <v>63</v>
+      </c>
+      <c r="CH23">
+        <v>44</v>
+      </c>
+      <c r="CI23">
+        <v>54.4</v>
+      </c>
+      <c r="CJ23">
+        <v>42.7</v>
+      </c>
+      <c r="CK23">
+        <v>33</v>
+      </c>
+      <c r="CL23">
+        <v>53.5</v>
+      </c>
+      <c r="CM23">
+        <v>45.2</v>
+      </c>
+      <c r="CN23">
+        <v>27.7</v>
+      </c>
+      <c r="CO23">
+        <v>46.6</v>
+      </c>
+      <c r="CP23">
+        <v>58.6</v>
+      </c>
+      <c r="CQ23">
+        <v>36.299999999999997</v>
+      </c>
     </row>
-    <row r="24" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -6605,8 +7697,53 @@
       <c r="CB24">
         <v>81</v>
       </c>
+      <c r="CC24">
+        <v>93.7</v>
+      </c>
+      <c r="CD24">
+        <v>54</v>
+      </c>
+      <c r="CE24" s="1">
+        <v>72</v>
+      </c>
+      <c r="CF24" s="1">
+        <v>66</v>
+      </c>
+      <c r="CG24" s="1">
+        <v>65</v>
+      </c>
+      <c r="CH24">
+        <v>47.2</v>
+      </c>
+      <c r="CI24">
+        <v>55.4</v>
+      </c>
+      <c r="CJ24">
+        <v>48.2</v>
+      </c>
+      <c r="CK24">
+        <v>22.1</v>
+      </c>
+      <c r="CL24">
+        <v>56.5</v>
+      </c>
+      <c r="CM24">
+        <v>49.3</v>
+      </c>
+      <c r="CN24">
+        <v>38.4</v>
+      </c>
+      <c r="CO24">
+        <v>46.8</v>
+      </c>
+      <c r="CP24">
+        <v>54.7</v>
+      </c>
+      <c r="CQ24">
+        <v>32.5</v>
+      </c>
     </row>
-    <row r="25" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -6847,8 +7984,53 @@
       <c r="CB25">
         <v>73</v>
       </c>
+      <c r="CC25">
+        <v>95.8</v>
+      </c>
+      <c r="CD25">
+        <v>64.3</v>
+      </c>
+      <c r="CE25" s="1">
+        <v>77</v>
+      </c>
+      <c r="CF25" s="1">
+        <v>68</v>
+      </c>
+      <c r="CG25" s="1">
+        <v>63</v>
+      </c>
+      <c r="CH25">
+        <v>55.1</v>
+      </c>
+      <c r="CI25">
+        <v>48.2</v>
+      </c>
+      <c r="CJ25">
+        <v>48.9</v>
+      </c>
+      <c r="CK25">
+        <v>38.6</v>
+      </c>
+      <c r="CL25">
+        <v>50.8</v>
+      </c>
+      <c r="CM25">
+        <v>53</v>
+      </c>
+      <c r="CN25">
+        <v>31.4</v>
+      </c>
+      <c r="CO25">
+        <v>47.7</v>
+      </c>
+      <c r="CP25">
+        <v>47</v>
+      </c>
+      <c r="CQ25">
+        <v>41.5</v>
+      </c>
     </row>
-    <row r="26" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -7089,8 +8271,53 @@
       <c r="CB26">
         <v>68</v>
       </c>
+      <c r="CC26">
+        <v>93.6</v>
+      </c>
+      <c r="CD26">
+        <v>52.5</v>
+      </c>
+      <c r="CE26" s="1">
+        <v>86</v>
+      </c>
+      <c r="CF26" s="1">
+        <v>64</v>
+      </c>
+      <c r="CG26" s="1">
+        <v>67</v>
+      </c>
+      <c r="CH26">
+        <v>51.3</v>
+      </c>
+      <c r="CI26">
+        <v>62.5</v>
+      </c>
+      <c r="CJ26">
+        <v>59.4</v>
+      </c>
+      <c r="CK26">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="CL26">
+        <v>62.9</v>
+      </c>
+      <c r="CM26">
+        <v>62.5</v>
+      </c>
+      <c r="CN26">
+        <v>47.7</v>
+      </c>
+      <c r="CO26">
+        <v>58.5</v>
+      </c>
+      <c r="CP26">
+        <v>65.3</v>
+      </c>
+      <c r="CQ26">
+        <v>42.2</v>
+      </c>
     </row>
-    <row r="27" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -7331,8 +8558,53 @@
       <c r="CB27">
         <v>47</v>
       </c>
+      <c r="CC27">
+        <v>96.2</v>
+      </c>
+      <c r="CD27">
+        <v>49.4</v>
+      </c>
+      <c r="CE27" s="1">
+        <v>65</v>
+      </c>
+      <c r="CF27" s="1">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="CG27" s="1">
+        <v>69</v>
+      </c>
+      <c r="CH27">
+        <v>43.6</v>
+      </c>
+      <c r="CI27">
+        <v>39.1</v>
+      </c>
+      <c r="CJ27">
+        <v>43</v>
+      </c>
+      <c r="CK27">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="CL27">
+        <v>45.6</v>
+      </c>
+      <c r="CM27">
+        <v>44.8</v>
+      </c>
+      <c r="CN27">
+        <v>31.9</v>
+      </c>
+      <c r="CO27">
+        <v>44.7</v>
+      </c>
+      <c r="CP27">
+        <v>46.9</v>
+      </c>
+      <c r="CQ27">
+        <v>38.5</v>
+      </c>
     </row>
-    <row r="28" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -7573,8 +8845,53 @@
       <c r="CB28">
         <v>49</v>
       </c>
+      <c r="CC28">
+        <v>94.3</v>
+      </c>
+      <c r="CD28">
+        <v>53.2</v>
+      </c>
+      <c r="CE28" s="1">
+        <v>84</v>
+      </c>
+      <c r="CF28" s="1">
+        <v>73</v>
+      </c>
+      <c r="CG28" s="1">
+        <v>66</v>
+      </c>
+      <c r="CH28">
+        <v>54.5</v>
+      </c>
+      <c r="CI28">
+        <v>51.7</v>
+      </c>
+      <c r="CJ28">
+        <v>54.8</v>
+      </c>
+      <c r="CK28">
+        <v>31.8</v>
+      </c>
+      <c r="CL28">
+        <v>58.9</v>
+      </c>
+      <c r="CM28">
+        <v>54</v>
+      </c>
+      <c r="CN28">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="CO28">
+        <v>61.6</v>
+      </c>
+      <c r="CP28">
+        <v>59.7</v>
+      </c>
+      <c r="CQ28">
+        <v>39.700000000000003</v>
+      </c>
     </row>
-    <row r="29" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -7815,8 +9132,53 @@
       <c r="CB29">
         <v>49</v>
       </c>
+      <c r="CC29">
+        <v>92.9</v>
+      </c>
+      <c r="CD29">
+        <v>51.6</v>
+      </c>
+      <c r="CE29" s="1">
+        <v>83</v>
+      </c>
+      <c r="CF29" s="1">
+        <v>64</v>
+      </c>
+      <c r="CG29" s="1">
+        <v>77</v>
+      </c>
+      <c r="CH29">
+        <v>41.7</v>
+      </c>
+      <c r="CI29">
+        <v>39.6</v>
+      </c>
+      <c r="CJ29">
+        <v>34.5</v>
+      </c>
+      <c r="CK29">
+        <v>26.1</v>
+      </c>
+      <c r="CL29">
+        <v>39.6</v>
+      </c>
+      <c r="CM29">
+        <v>37.1</v>
+      </c>
+      <c r="CN29">
+        <v>31.9</v>
+      </c>
+      <c r="CO29">
+        <v>40.4</v>
+      </c>
+      <c r="CP29">
+        <v>38</v>
+      </c>
+      <c r="CQ29">
+        <v>32.299999999999997</v>
+      </c>
     </row>
-    <row r="30" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -8057,8 +9419,53 @@
       <c r="CB30">
         <v>92</v>
       </c>
+      <c r="CC30">
+        <v>95.2</v>
+      </c>
+      <c r="CD30">
+        <v>58.2</v>
+      </c>
+      <c r="CE30" s="1">
+        <v>86</v>
+      </c>
+      <c r="CF30" s="1">
+        <v>79</v>
+      </c>
+      <c r="CG30" s="1">
+        <v>64</v>
+      </c>
+      <c r="CH30">
+        <v>61.6</v>
+      </c>
+      <c r="CI30">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="CJ30">
+        <v>62.4</v>
+      </c>
+      <c r="CK30">
+        <v>33.9</v>
+      </c>
+      <c r="CL30">
+        <v>68.2</v>
+      </c>
+      <c r="CM30">
+        <v>56.1</v>
+      </c>
+      <c r="CN30">
+        <v>40.1</v>
+      </c>
+      <c r="CO30">
+        <v>57.6</v>
+      </c>
+      <c r="CP30">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="CQ30">
+        <v>39</v>
+      </c>
     </row>
-    <row r="31" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -8299,8 +9706,53 @@
       <c r="CB31">
         <v>89</v>
       </c>
+      <c r="CC31">
+        <v>82.6</v>
+      </c>
+      <c r="CD31">
+        <v>59.4</v>
+      </c>
+      <c r="CE31" s="1">
+        <v>83</v>
+      </c>
+      <c r="CF31" s="1">
+        <v>78</v>
+      </c>
+      <c r="CG31" s="1">
+        <v>76</v>
+      </c>
+      <c r="CH31">
+        <v>49</v>
+      </c>
+      <c r="CI31">
+        <v>53</v>
+      </c>
+      <c r="CJ31">
+        <v>48.8</v>
+      </c>
+      <c r="CK31">
+        <v>26.4</v>
+      </c>
+      <c r="CL31">
+        <v>52.8</v>
+      </c>
+      <c r="CM31">
+        <v>41.5</v>
+      </c>
+      <c r="CN31">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="CO31">
+        <v>43.9</v>
+      </c>
+      <c r="CP31">
+        <v>55.5</v>
+      </c>
+      <c r="CQ31">
+        <v>38.200000000000003</v>
+      </c>
     </row>
-    <row r="32" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:95" x14ac:dyDescent="0.25">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -8331,6 +9783,146 @@
       <c r="AL32" s="1"/>
       <c r="AM32" s="1"/>
     </row>
+    <row r="36" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/SC Indicators Data Prep.xlsx
+++ b/SC Indicators Data Prep.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emree\Desktop\CO3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emree\CO3data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288E9763-E6B1-4FD3-8A25-48FCFF7B6D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C42EA00B-A49B-4BFB-802F-390B628688E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{55AA29CC-CDDC-4D64-AC5C-6644C21888DE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="200">
   <si>
     <t>Voted</t>
   </si>
@@ -477,6 +477,165 @@
   </si>
   <si>
     <t>Agree-Nowadays in (OUR COUNTRY) differences in people’s incomes are too great</t>
+  </si>
+  <si>
+    <t>Discrimination</t>
+  </si>
+  <si>
+    <t>Social Cohesion</t>
+  </si>
+  <si>
+    <t>School/University</t>
+  </si>
+  <si>
+    <t>Gender Equality-At work</t>
+  </si>
+  <si>
+    <t>Gender Equality-By medical staff</t>
+  </si>
+  <si>
+    <t>Gender Equality--In the media</t>
+  </si>
+  <si>
+    <t>Gender Equality--In advertising</t>
+  </si>
+  <si>
+    <t>Gender Equality--In politics</t>
+  </si>
+  <si>
+    <t>DiscriminationNot Widespread-Ethnic Origin</t>
+  </si>
+  <si>
+    <t>DiscriminationNot Widespread-Skin Color</t>
+  </si>
+  <si>
+    <t>DiscriminationNot Widespread-Being Roma</t>
+  </si>
+  <si>
+    <t>DiscriminationNot Widespread-Sexual Orientation</t>
+  </si>
+  <si>
+    <t>DiscriminationNot Widespread-Age</t>
+  </si>
+  <si>
+    <t>DiscriminationNot Widespread-Religion of Beliefs</t>
+  </si>
+  <si>
+    <t>DiscriminationNot Widespread-Disability</t>
+  </si>
+  <si>
+    <t>DiscriminationNot Widespread-Being Transgender</t>
+  </si>
+  <si>
+    <t>DiscriminationNot Widespread-Socioeconomic Situation</t>
+  </si>
+  <si>
+    <t>DiscriminationNot Widespread-Being Man or Woman</t>
+  </si>
+  <si>
+    <t>DiscriminationNot Widespread-Being Intersex</t>
+  </si>
+  <si>
+    <t>Gender Equality</t>
+  </si>
+  <si>
+    <t>Hope More Inclusive Europe</t>
+  </si>
+  <si>
+    <t>Being Not Discriminated</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (OUR COUNTRY) is a Member State of the European Union- Total 'Important'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> the future of the EU-Total 'Optimistic'</t>
+  </si>
+  <si>
+    <t>Benefited from the free movement of EU citizens within the EU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informed about the history (OUR COUNTRY) shares with European countries- </t>
+  </si>
+  <si>
+    <t>Net Opinion about the Public Administration of Country</t>
+  </si>
+  <si>
+    <t>A common defence and security policy among EU Member States</t>
+  </si>
+  <si>
+    <t>The EU's common trade policy</t>
+  </si>
+  <si>
+    <t>A common European policy on migration</t>
+  </si>
+  <si>
+    <t>A common energy policy among EU Member States</t>
+  </si>
+  <si>
+    <t>Further enlargement of the EU to include other countries in future years</t>
+  </si>
+  <si>
+    <t>The free movement of EU citizens who can live, work, study and do business anywhere in the EU</t>
+  </si>
+  <si>
+    <t>A common EU health policy</t>
+  </si>
+  <si>
+    <t>More money should be spent on defence in the EU</t>
+  </si>
+  <si>
+    <t>Member States' purchase of military equipment should be better coordinated</t>
+  </si>
+  <si>
+    <t>The EU needs to reinforce its capacity to produce military equipment</t>
+  </si>
+  <si>
+    <t>Attachement- Europe and my European identity</t>
+  </si>
+  <si>
+    <t>Equally attached- my local community, country and Europe</t>
+  </si>
+  <si>
+    <t>Identity</t>
+  </si>
+  <si>
+    <t>People in (OUR COUNTRY) have a lot of things in common-Total 'Agree'</t>
+  </si>
+  <si>
+    <t>People in the EU have a lot of things in common-Total 'Agree'</t>
+  </si>
+  <si>
+    <t>People in the EU's Eastern neighbourhood countries have a lot of things in common with people in the EU-Total 'Agree'</t>
+  </si>
+  <si>
+    <t>Attachement-European and (NATIONALITY), European Only</t>
+  </si>
+  <si>
+    <t>Co-operation in defence matters at EU level should be increased</t>
+  </si>
+  <si>
+    <t>The European Union -Total 'Attached'</t>
+  </si>
+  <si>
+    <t>Europe -Total 'Attached'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A common foreign policy of the Member States of the EU</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>Public Administration</t>
+  </si>
+  <si>
+    <t>The provision of public services in (OUR COUNTRY) - Total 'Good'</t>
+  </si>
+  <si>
+    <t>the Relationship between Citizen and State</t>
+  </si>
+  <si>
+    <t>Defense Policy</t>
   </si>
 </sst>
 </file>
@@ -486,7 +645,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,16 +653,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -511,16 +689,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{5ABAC1FB-A9EC-4580-89E2-6728EDE9404B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -852,10 +1050,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA6585B-C499-45AD-87BE-134F9272F3A6}">
-  <dimension ref="A1:CQ63"/>
+  <dimension ref="A1:EJ41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>122</v>
       </c>
@@ -1141,8 +1339,143 @@
       <c r="CQ1" t="s">
         <v>127</v>
       </c>
+      <c r="CR1" t="s">
+        <v>148</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>148</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>148</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>148</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>148</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>148</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>148</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>148</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>148</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>148</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>148</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>148</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>148</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>148</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>148</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>148</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>148</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>148</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>148</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DM1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DR1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DS1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DU1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DV1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DW1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>198</v>
+      </c>
+      <c r="DZ1" t="s">
+        <v>198</v>
+      </c>
+      <c r="EA1" t="s">
+        <v>198</v>
+      </c>
+      <c r="EB1" t="s">
+        <v>198</v>
+      </c>
+      <c r="EC1" t="s">
+        <v>198</v>
+      </c>
+      <c r="ED1" t="s">
+        <v>198</v>
+      </c>
+      <c r="EE1" t="s">
+        <v>198</v>
+      </c>
+      <c r="EF1" t="s">
+        <v>198</v>
+      </c>
+      <c r="EG1" t="s">
+        <v>198</v>
+      </c>
+      <c r="EH1" t="s">
+        <v>198</v>
+      </c>
+      <c r="EI1" t="s">
+        <v>198</v>
+      </c>
+      <c r="EJ1" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="2" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -1428,8 +1761,143 @@
       <c r="CQ2" t="s">
         <v>142</v>
       </c>
+      <c r="CR2" t="s">
+        <v>166</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>166</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>166</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>166</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>166</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>166</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>147</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>147</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>147</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>147</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>147</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>147</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>147</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>147</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>147</v>
+      </c>
+      <c r="DG2" t="s">
+        <v>147</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>147</v>
+      </c>
+      <c r="DI2" t="s">
+        <v>147</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>147</v>
+      </c>
+      <c r="DK2" t="s">
+        <v>186</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>186</v>
+      </c>
+      <c r="DM2" t="s">
+        <v>195</v>
+      </c>
+      <c r="DN2" t="s">
+        <v>186</v>
+      </c>
+      <c r="DO2" t="s">
+        <v>196</v>
+      </c>
+      <c r="DP2" t="s">
+        <v>196</v>
+      </c>
+      <c r="DQ2" t="s">
+        <v>195</v>
+      </c>
+      <c r="DR2" t="s">
+        <v>195</v>
+      </c>
+      <c r="DS2" t="s">
+        <v>195</v>
+      </c>
+      <c r="DT2" t="s">
+        <v>195</v>
+      </c>
+      <c r="DU2" t="s">
+        <v>195</v>
+      </c>
+      <c r="DV2" t="s">
+        <v>195</v>
+      </c>
+      <c r="DW2" t="s">
+        <v>195</v>
+      </c>
+      <c r="DX2" t="s">
+        <v>195</v>
+      </c>
+      <c r="DY2" t="s">
+        <v>186</v>
+      </c>
+      <c r="DZ2" t="s">
+        <v>186</v>
+      </c>
+      <c r="EA2" t="s">
+        <v>186</v>
+      </c>
+      <c r="EB2" t="s">
+        <v>186</v>
+      </c>
+      <c r="EC2" t="s">
+        <v>186</v>
+      </c>
+      <c r="ED2" t="s">
+        <v>186</v>
+      </c>
+      <c r="EE2" t="s">
+        <v>186</v>
+      </c>
+      <c r="EF2" t="s">
+        <v>186</v>
+      </c>
+      <c r="EG2" t="s">
+        <v>199</v>
+      </c>
+      <c r="EH2" t="s">
+        <v>199</v>
+      </c>
+      <c r="EI2" t="s">
+        <v>199</v>
+      </c>
+      <c r="EJ2" t="s">
+        <v>199</v>
+      </c>
     </row>
-    <row r="3" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -1715,8 +2183,143 @@
       <c r="CQ3" t="s">
         <v>141</v>
       </c>
+      <c r="CR3" t="s">
+        <v>149</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>150</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>151</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>152</v>
+      </c>
+      <c r="CV3" t="s">
+        <v>153</v>
+      </c>
+      <c r="CW3" t="s">
+        <v>154</v>
+      </c>
+      <c r="CX3" t="s">
+        <v>155</v>
+      </c>
+      <c r="CY3" t="s">
+        <v>156</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>157</v>
+      </c>
+      <c r="DA3" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB3" t="s">
+        <v>159</v>
+      </c>
+      <c r="DC3" t="s">
+        <v>160</v>
+      </c>
+      <c r="DD3" t="s">
+        <v>161</v>
+      </c>
+      <c r="DE3" t="s">
+        <v>162</v>
+      </c>
+      <c r="DF3" t="s">
+        <v>163</v>
+      </c>
+      <c r="DG3" t="s">
+        <v>164</v>
+      </c>
+      <c r="DH3" t="s">
+        <v>165</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>168</v>
+      </c>
+      <c r="DJ3" t="s">
+        <v>167</v>
+      </c>
+      <c r="DK3" t="s">
+        <v>169</v>
+      </c>
+      <c r="DL3" t="s">
+        <v>170</v>
+      </c>
+      <c r="DM3" t="s">
+        <v>171</v>
+      </c>
+      <c r="DN3" t="s">
+        <v>172</v>
+      </c>
+      <c r="DO3" t="s">
+        <v>173</v>
+      </c>
+      <c r="DP3" t="s">
+        <v>197</v>
+      </c>
+      <c r="DQ3" t="s">
+        <v>194</v>
+      </c>
+      <c r="DR3" t="s">
+        <v>174</v>
+      </c>
+      <c r="DS3" t="s">
+        <v>175</v>
+      </c>
+      <c r="DT3" t="s">
+        <v>176</v>
+      </c>
+      <c r="DU3" t="s">
+        <v>177</v>
+      </c>
+      <c r="DV3" t="s">
+        <v>178</v>
+      </c>
+      <c r="DW3" t="s">
+        <v>179</v>
+      </c>
+      <c r="DX3" t="s">
+        <v>180</v>
+      </c>
+      <c r="DY3" t="s">
+        <v>192</v>
+      </c>
+      <c r="DZ3" t="s">
+        <v>193</v>
+      </c>
+      <c r="EA3" t="s">
+        <v>190</v>
+      </c>
+      <c r="EB3" t="s">
+        <v>187</v>
+      </c>
+      <c r="EC3" t="s">
+        <v>188</v>
+      </c>
+      <c r="ED3" t="s">
+        <v>189</v>
+      </c>
+      <c r="EE3" t="s">
+        <v>184</v>
+      </c>
+      <c r="EF3" t="s">
+        <v>185</v>
+      </c>
+      <c r="EG3" t="s">
+        <v>191</v>
+      </c>
+      <c r="EH3" t="s">
+        <v>181</v>
+      </c>
+      <c r="EI3" t="s">
+        <v>182</v>
+      </c>
+      <c r="EJ3" t="s">
+        <v>183</v>
+      </c>
     </row>
-    <row r="4" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -2002,8 +2605,143 @@
       <c r="CQ4">
         <v>34.799999999999997</v>
       </c>
+      <c r="CR4" s="1">
+        <v>76</v>
+      </c>
+      <c r="CS4" s="1">
+        <v>46</v>
+      </c>
+      <c r="CT4" s="1">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="CU4" s="1">
+        <v>64</v>
+      </c>
+      <c r="CV4" s="1">
+        <v>68</v>
+      </c>
+      <c r="CW4" s="1">
+        <v>43</v>
+      </c>
+      <c r="CX4">
+        <v>40</v>
+      </c>
+      <c r="CY4">
+        <v>39</v>
+      </c>
+      <c r="CZ4">
+        <v>35</v>
+      </c>
+      <c r="DA4">
+        <v>46</v>
+      </c>
+      <c r="DB4">
+        <v>55</v>
+      </c>
+      <c r="DC4">
+        <v>58</v>
+      </c>
+      <c r="DD4">
+        <v>51</v>
+      </c>
+      <c r="DE4">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="DF4">
+        <v>51</v>
+      </c>
+      <c r="DG4">
+        <v>62</v>
+      </c>
+      <c r="DH4">
+        <v>53</v>
+      </c>
+      <c r="DI4">
+        <v>79</v>
+      </c>
+      <c r="DJ4">
+        <v>54</v>
+      </c>
+      <c r="DK4">
+        <v>67</v>
+      </c>
+      <c r="DL4">
+        <v>65</v>
+      </c>
+      <c r="DM4">
+        <v>93.7</v>
+      </c>
+      <c r="DN4">
+        <v>77</v>
+      </c>
+      <c r="DO4">
+        <v>-111.19999999999999</v>
+      </c>
+      <c r="DP4">
+        <v>54</v>
+      </c>
+      <c r="DQ4">
+        <v>69</v>
+      </c>
+      <c r="DR4">
+        <v>77</v>
+      </c>
+      <c r="DS4">
+        <v>71</v>
+      </c>
+      <c r="DT4">
+        <v>67</v>
+      </c>
+      <c r="DU4">
+        <v>72</v>
+      </c>
+      <c r="DV4">
+        <v>51</v>
+      </c>
+      <c r="DW4">
+        <v>84</v>
+      </c>
+      <c r="DX4">
+        <v>63</v>
+      </c>
+      <c r="DY4">
+        <v>61</v>
+      </c>
+      <c r="DZ4">
+        <v>69</v>
+      </c>
+      <c r="EA4">
+        <v>9.0000000000000018</v>
+      </c>
+      <c r="EB4">
+        <v>81</v>
+      </c>
+      <c r="EC4">
+        <v>65</v>
+      </c>
+      <c r="ED4">
+        <v>45</v>
+      </c>
+      <c r="EE4">
+        <v>14.5</v>
+      </c>
+      <c r="EF4">
+        <v>14.4</v>
+      </c>
+      <c r="EG4">
+        <v>80</v>
+      </c>
+      <c r="EH4">
+        <v>66</v>
+      </c>
+      <c r="EI4">
+        <v>80</v>
+      </c>
+      <c r="EJ4">
+        <v>71</v>
+      </c>
     </row>
-    <row r="5" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -2289,8 +3027,143 @@
       <c r="CQ5">
         <v>35.299999999999997</v>
       </c>
+      <c r="CR5" s="1">
+        <v>75</v>
+      </c>
+      <c r="CS5" s="1">
+        <v>46</v>
+      </c>
+      <c r="CT5" s="1">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="CU5" s="1">
+        <v>63</v>
+      </c>
+      <c r="CV5" s="1">
+        <v>65.999999999999986</v>
+      </c>
+      <c r="CW5" s="1">
+        <v>41</v>
+      </c>
+      <c r="CX5">
+        <v>31</v>
+      </c>
+      <c r="CY5">
+        <v>27</v>
+      </c>
+      <c r="CZ5">
+        <v>36</v>
+      </c>
+      <c r="DA5">
+        <v>43.999999999999993</v>
+      </c>
+      <c r="DB5">
+        <v>46</v>
+      </c>
+      <c r="DC5">
+        <v>40</v>
+      </c>
+      <c r="DD5">
+        <v>44.999999999999993</v>
+      </c>
+      <c r="DE5">
+        <v>37</v>
+      </c>
+      <c r="DF5">
+        <v>43.999999999999993</v>
+      </c>
+      <c r="DG5">
+        <v>56</v>
+      </c>
+      <c r="DH5">
+        <v>50</v>
+      </c>
+      <c r="DI5">
+        <v>62</v>
+      </c>
+      <c r="DJ5">
+        <v>54</v>
+      </c>
+      <c r="DK5">
+        <v>72</v>
+      </c>
+      <c r="DL5">
+        <v>69</v>
+      </c>
+      <c r="DM5">
+        <v>89</v>
+      </c>
+      <c r="DN5">
+        <v>73</v>
+      </c>
+      <c r="DO5">
+        <v>-97.799999999999983</v>
+      </c>
+      <c r="DP5">
+        <v>66</v>
+      </c>
+      <c r="DQ5">
+        <v>71</v>
+      </c>
+      <c r="DR5">
+        <v>83</v>
+      </c>
+      <c r="DS5">
+        <v>72</v>
+      </c>
+      <c r="DT5">
+        <v>72</v>
+      </c>
+      <c r="DU5">
+        <v>79</v>
+      </c>
+      <c r="DV5">
+        <v>45</v>
+      </c>
+      <c r="DW5">
+        <v>82</v>
+      </c>
+      <c r="DX5">
+        <v>70</v>
+      </c>
+      <c r="DY5">
+        <v>63</v>
+      </c>
+      <c r="DZ5">
+        <v>70</v>
+      </c>
+      <c r="EA5">
+        <v>14.000000000000002</v>
+      </c>
+      <c r="EB5">
+        <v>71</v>
+      </c>
+      <c r="EC5">
+        <v>54</v>
+      </c>
+      <c r="ED5">
+        <v>39</v>
+      </c>
+      <c r="EE5">
+        <v>21.4</v>
+      </c>
+      <c r="EF5">
+        <v>9.9</v>
+      </c>
+      <c r="EG5">
+        <v>86</v>
+      </c>
+      <c r="EH5">
+        <v>69</v>
+      </c>
+      <c r="EI5">
+        <v>84</v>
+      </c>
+      <c r="EJ5">
+        <v>75</v>
+      </c>
     </row>
-    <row r="6" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -2576,8 +3449,143 @@
       <c r="CQ6">
         <v>30.6</v>
       </c>
+      <c r="CR6" s="1">
+        <v>83</v>
+      </c>
+      <c r="CS6" s="1">
+        <v>73</v>
+      </c>
+      <c r="CT6" s="1">
+        <v>24</v>
+      </c>
+      <c r="CU6" s="1">
+        <v>78</v>
+      </c>
+      <c r="CV6" s="1">
+        <v>78</v>
+      </c>
+      <c r="CW6" s="1">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="CX6">
+        <v>62</v>
+      </c>
+      <c r="CY6">
+        <v>64</v>
+      </c>
+      <c r="CZ6">
+        <v>53</v>
+      </c>
+      <c r="DA6">
+        <v>60</v>
+      </c>
+      <c r="DB6">
+        <v>65</v>
+      </c>
+      <c r="DC6">
+        <v>78</v>
+      </c>
+      <c r="DD6">
+        <v>60</v>
+      </c>
+      <c r="DE6">
+        <v>63</v>
+      </c>
+      <c r="DF6">
+        <v>60</v>
+      </c>
+      <c r="DG6">
+        <v>81</v>
+      </c>
+      <c r="DH6">
+        <v>65</v>
+      </c>
+      <c r="DI6">
+        <v>86</v>
+      </c>
+      <c r="DJ6">
+        <v>51</v>
+      </c>
+      <c r="DK6">
+        <v>53</v>
+      </c>
+      <c r="DL6">
+        <v>60</v>
+      </c>
+      <c r="DM6">
+        <v>83.4</v>
+      </c>
+      <c r="DN6">
+        <v>70</v>
+      </c>
+      <c r="DO6">
+        <v>-126.19999999999999</v>
+      </c>
+      <c r="DP6">
+        <v>43</v>
+      </c>
+      <c r="DQ6">
+        <v>59</v>
+      </c>
+      <c r="DR6">
+        <v>66</v>
+      </c>
+      <c r="DS6">
+        <v>61</v>
+      </c>
+      <c r="DT6">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="DU6">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="DV6">
+        <v>48</v>
+      </c>
+      <c r="DW6">
+        <v>84</v>
+      </c>
+      <c r="DX6">
+        <v>64</v>
+      </c>
+      <c r="DY6">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="DZ6">
+        <v>62</v>
+      </c>
+      <c r="EA6">
+        <v>6.9999999999999991</v>
+      </c>
+      <c r="EB6">
+        <v>89</v>
+      </c>
+      <c r="EC6">
+        <v>71</v>
+      </c>
+      <c r="ED6">
+        <v>59</v>
+      </c>
+      <c r="EE6">
+        <v>15.7</v>
+      </c>
+      <c r="EF6">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="EG6">
+        <v>69</v>
+      </c>
+      <c r="EH6">
+        <v>47</v>
+      </c>
+      <c r="EI6">
+        <v>70</v>
+      </c>
+      <c r="EJ6">
+        <v>53</v>
+      </c>
     </row>
-    <row r="7" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2863,8 +3871,143 @@
       <c r="CQ7">
         <v>31.9</v>
       </c>
+      <c r="CR7" s="1">
+        <v>82</v>
+      </c>
+      <c r="CS7" s="1">
+        <v>62.000000000000014</v>
+      </c>
+      <c r="CT7" s="1">
+        <v>26</v>
+      </c>
+      <c r="CU7" s="1">
+        <v>80</v>
+      </c>
+      <c r="CV7" s="1">
+        <v>82</v>
+      </c>
+      <c r="CW7" s="1">
+        <v>55.999999999999993</v>
+      </c>
+      <c r="CX7">
+        <v>63</v>
+      </c>
+      <c r="CY7">
+        <v>61</v>
+      </c>
+      <c r="CZ7">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="DA7">
+        <v>76</v>
+      </c>
+      <c r="DB7">
+        <v>60</v>
+      </c>
+      <c r="DC7">
+        <v>87</v>
+      </c>
+      <c r="DD7">
+        <v>71</v>
+      </c>
+      <c r="DE7">
+        <v>78</v>
+      </c>
+      <c r="DF7">
+        <v>74</v>
+      </c>
+      <c r="DG7">
+        <v>80</v>
+      </c>
+      <c r="DH7">
+        <v>81</v>
+      </c>
+      <c r="DI7">
+        <v>82</v>
+      </c>
+      <c r="DJ7">
+        <v>44</v>
+      </c>
+      <c r="DK7">
+        <v>50</v>
+      </c>
+      <c r="DL7">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="DM7">
+        <v>85.3</v>
+      </c>
+      <c r="DN7">
+        <v>86</v>
+      </c>
+      <c r="DO7">
+        <v>-107.00000000000001</v>
+      </c>
+      <c r="DP7">
+        <v>74</v>
+      </c>
+      <c r="DQ7">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="DR7">
+        <v>74</v>
+      </c>
+      <c r="DS7">
+        <v>60</v>
+      </c>
+      <c r="DT7">
+        <v>40</v>
+      </c>
+      <c r="DU7">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="DV7">
+        <v>46</v>
+      </c>
+      <c r="DW7">
+        <v>85</v>
+      </c>
+      <c r="DX7">
+        <v>51</v>
+      </c>
+      <c r="DY7">
+        <v>40</v>
+      </c>
+      <c r="DZ7">
+        <v>62</v>
+      </c>
+      <c r="EA7">
+        <v>6.9999999999999991</v>
+      </c>
+      <c r="EB7">
+        <v>82</v>
+      </c>
+      <c r="EC7">
+        <v>59</v>
+      </c>
+      <c r="ED7">
+        <v>35</v>
+      </c>
+      <c r="EE7">
+        <v>12.9</v>
+      </c>
+      <c r="EF7">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="EG7">
+        <v>76</v>
+      </c>
+      <c r="EH7">
+        <v>62</v>
+      </c>
+      <c r="EI7">
+        <v>78</v>
+      </c>
+      <c r="EJ7">
+        <v>62</v>
+      </c>
     </row>
-    <row r="8" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3150,8 +4293,143 @@
       <c r="CQ8">
         <v>37.4</v>
       </c>
+      <c r="CR8" s="1">
+        <v>77</v>
+      </c>
+      <c r="CS8" s="1">
+        <v>43</v>
+      </c>
+      <c r="CT8" s="1">
+        <v>26</v>
+      </c>
+      <c r="CU8" s="1">
+        <v>54</v>
+      </c>
+      <c r="CV8" s="1">
+        <v>61</v>
+      </c>
+      <c r="CW8" s="1">
+        <v>43</v>
+      </c>
+      <c r="CX8">
+        <v>33</v>
+      </c>
+      <c r="CY8">
+        <v>37</v>
+      </c>
+      <c r="CZ8">
+        <v>43.999999999999993</v>
+      </c>
+      <c r="DA8">
+        <v>57</v>
+      </c>
+      <c r="DB8">
+        <v>53</v>
+      </c>
+      <c r="DC8">
+        <v>49</v>
+      </c>
+      <c r="DD8">
+        <v>54</v>
+      </c>
+      <c r="DE8">
+        <v>43.999999999999993</v>
+      </c>
+      <c r="DF8">
+        <v>54</v>
+      </c>
+      <c r="DG8">
+        <v>64</v>
+      </c>
+      <c r="DH8">
+        <v>60</v>
+      </c>
+      <c r="DI8">
+        <v>78</v>
+      </c>
+      <c r="DJ8">
+        <v>63</v>
+      </c>
+      <c r="DK8">
+        <v>81</v>
+      </c>
+      <c r="DL8">
+        <v>83</v>
+      </c>
+      <c r="DM8">
+        <v>84.6</v>
+      </c>
+      <c r="DN8">
+        <v>82</v>
+      </c>
+      <c r="DO8">
+        <v>-48.300000000000011</v>
+      </c>
+      <c r="DP8">
+        <v>65</v>
+      </c>
+      <c r="DQ8">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="DR8">
+        <v>78</v>
+      </c>
+      <c r="DS8">
+        <v>76</v>
+      </c>
+      <c r="DT8">
+        <v>65</v>
+      </c>
+      <c r="DU8">
+        <v>75</v>
+      </c>
+      <c r="DV8">
+        <v>61</v>
+      </c>
+      <c r="DW8">
+        <v>88</v>
+      </c>
+      <c r="DX8">
+        <v>38</v>
+      </c>
+      <c r="DY8">
+        <v>71</v>
+      </c>
+      <c r="DZ8">
+        <v>86</v>
+      </c>
+      <c r="EA8">
+        <v>8</v>
+      </c>
+      <c r="EB8">
+        <v>93</v>
+      </c>
+      <c r="EC8">
+        <v>66</v>
+      </c>
+      <c r="ED8">
+        <v>37</v>
+      </c>
+      <c r="EE8">
+        <v>12.8</v>
+      </c>
+      <c r="EF8">
+        <v>11.5</v>
+      </c>
+      <c r="EG8">
+        <v>89</v>
+      </c>
+      <c r="EH8">
+        <v>78</v>
+      </c>
+      <c r="EI8">
+        <v>90</v>
+      </c>
+      <c r="EJ8">
+        <v>87</v>
+      </c>
     </row>
-    <row r="9" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -3437,8 +4715,143 @@
       <c r="CQ9">
         <v>35.299999999999997</v>
       </c>
+      <c r="CR9" s="1">
+        <v>73</v>
+      </c>
+      <c r="CS9" s="1">
+        <v>35</v>
+      </c>
+      <c r="CT9" s="1">
+        <v>35</v>
+      </c>
+      <c r="CU9" s="1">
+        <v>63</v>
+      </c>
+      <c r="CV9" s="1">
+        <v>69</v>
+      </c>
+      <c r="CW9" s="1">
+        <v>40</v>
+      </c>
+      <c r="CX9">
+        <v>47</v>
+      </c>
+      <c r="CY9">
+        <v>44.999999999999993</v>
+      </c>
+      <c r="CZ9">
+        <v>47</v>
+      </c>
+      <c r="DA9">
+        <v>56</v>
+      </c>
+      <c r="DB9">
+        <v>71</v>
+      </c>
+      <c r="DC9">
+        <v>60</v>
+      </c>
+      <c r="DD9">
+        <v>61</v>
+      </c>
+      <c r="DE9">
+        <v>52</v>
+      </c>
+      <c r="DF9">
+        <v>58</v>
+      </c>
+      <c r="DG9">
+        <v>72</v>
+      </c>
+      <c r="DH9">
+        <v>59</v>
+      </c>
+      <c r="DI9">
+        <v>75</v>
+      </c>
+      <c r="DJ9">
+        <v>49</v>
+      </c>
+      <c r="DK9">
+        <v>67</v>
+      </c>
+      <c r="DL9">
+        <v>64</v>
+      </c>
+      <c r="DM9">
+        <v>93.6</v>
+      </c>
+      <c r="DN9">
+        <v>88</v>
+      </c>
+      <c r="DO9">
+        <v>-84.700000000000017</v>
+      </c>
+      <c r="DP9">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="DQ9">
+        <v>79</v>
+      </c>
+      <c r="DR9">
+        <v>81</v>
+      </c>
+      <c r="DS9">
+        <v>77</v>
+      </c>
+      <c r="DT9">
+        <v>75</v>
+      </c>
+      <c r="DU9">
+        <v>78</v>
+      </c>
+      <c r="DV9">
+        <v>41</v>
+      </c>
+      <c r="DW9">
+        <v>88</v>
+      </c>
+      <c r="DX9">
+        <v>61</v>
+      </c>
+      <c r="DY9">
+        <v>62</v>
+      </c>
+      <c r="DZ9">
+        <v>73</v>
+      </c>
+      <c r="EA9">
+        <v>15</v>
+      </c>
+      <c r="EB9">
+        <v>76</v>
+      </c>
+      <c r="EC9">
+        <v>65</v>
+      </c>
+      <c r="ED9">
+        <v>39</v>
+      </c>
+      <c r="EE9">
+        <v>16.2</v>
+      </c>
+      <c r="EF9">
+        <v>17.2</v>
+      </c>
+      <c r="EG9">
+        <v>80</v>
+      </c>
+      <c r="EH9">
+        <v>67</v>
+      </c>
+      <c r="EI9">
+        <v>81</v>
+      </c>
+      <c r="EJ9">
+        <v>71</v>
+      </c>
     </row>
-    <row r="10" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -3724,8 +5137,143 @@
       <c r="CQ10">
         <v>35.200000000000003</v>
       </c>
+      <c r="CR10" s="1">
+        <v>80</v>
+      </c>
+      <c r="CS10" s="1">
+        <v>62.000000000000014</v>
+      </c>
+      <c r="CT10" s="1">
+        <v>22</v>
+      </c>
+      <c r="CU10" s="1">
+        <v>69</v>
+      </c>
+      <c r="CV10" s="1">
+        <v>72.000000000000014</v>
+      </c>
+      <c r="CW10" s="1">
+        <v>44</v>
+      </c>
+      <c r="CX10">
+        <v>57</v>
+      </c>
+      <c r="CY10">
+        <v>66</v>
+      </c>
+      <c r="CZ10">
+        <v>78</v>
+      </c>
+      <c r="DA10">
+        <v>69</v>
+      </c>
+      <c r="DB10">
+        <v>49</v>
+      </c>
+      <c r="DC10">
+        <v>76</v>
+      </c>
+      <c r="DD10">
+        <v>60</v>
+      </c>
+      <c r="DE10">
+        <v>73</v>
+      </c>
+      <c r="DF10">
+        <v>59</v>
+      </c>
+      <c r="DG10">
+        <v>67</v>
+      </c>
+      <c r="DH10">
+        <v>80</v>
+      </c>
+      <c r="DI10">
+        <v>70</v>
+      </c>
+      <c r="DJ10">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="DK10">
+        <v>68</v>
+      </c>
+      <c r="DL10">
+        <v>68</v>
+      </c>
+      <c r="DM10">
+        <v>90.7</v>
+      </c>
+      <c r="DN10">
+        <v>84</v>
+      </c>
+      <c r="DO10">
+        <v>-43.800000000000011</v>
+      </c>
+      <c r="DP10">
+        <v>72</v>
+      </c>
+      <c r="DQ10">
+        <v>63</v>
+      </c>
+      <c r="DR10">
+        <v>78</v>
+      </c>
+      <c r="DS10">
+        <v>80</v>
+      </c>
+      <c r="DT10">
+        <v>44</v>
+      </c>
+      <c r="DU10">
+        <v>62</v>
+      </c>
+      <c r="DV10">
+        <v>53</v>
+      </c>
+      <c r="DW10">
+        <v>92</v>
+      </c>
+      <c r="DX10">
+        <v>64</v>
+      </c>
+      <c r="DY10">
+        <v>53</v>
+      </c>
+      <c r="DZ10">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="EA10">
+        <v>8</v>
+      </c>
+      <c r="EB10">
+        <v>80</v>
+      </c>
+      <c r="EC10">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="ED10">
+        <v>33</v>
+      </c>
+      <c r="EE10">
+        <v>14</v>
+      </c>
+      <c r="EF10">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="EG10">
+        <v>75</v>
+      </c>
+      <c r="EH10">
+        <v>60</v>
+      </c>
+      <c r="EI10">
+        <v>75</v>
+      </c>
+      <c r="EJ10">
+        <v>70</v>
+      </c>
     </row>
-    <row r="11" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -4011,8 +5559,143 @@
       <c r="CQ11">
         <v>48.2</v>
       </c>
+      <c r="CR11" s="1">
+        <v>76.999999999999986</v>
+      </c>
+      <c r="CS11" s="1">
+        <v>50</v>
+      </c>
+      <c r="CT11" s="1">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="CU11" s="1">
+        <v>57.000000000000007</v>
+      </c>
+      <c r="CV11" s="1">
+        <v>62</v>
+      </c>
+      <c r="CW11" s="1">
+        <v>32</v>
+      </c>
+      <c r="CX11">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="CY11">
+        <v>40</v>
+      </c>
+      <c r="CZ11">
+        <v>38</v>
+      </c>
+      <c r="DA11">
+        <v>54</v>
+      </c>
+      <c r="DB11">
+        <v>55</v>
+      </c>
+      <c r="DC11">
+        <v>65</v>
+      </c>
+      <c r="DD11">
+        <v>54</v>
+      </c>
+      <c r="DE11">
+        <v>46</v>
+      </c>
+      <c r="DF11">
+        <v>52</v>
+      </c>
+      <c r="DG11">
+        <v>63</v>
+      </c>
+      <c r="DH11">
+        <v>58</v>
+      </c>
+      <c r="DI11">
+        <v>83</v>
+      </c>
+      <c r="DJ11">
+        <v>74</v>
+      </c>
+      <c r="DK11">
+        <v>76</v>
+      </c>
+      <c r="DL11">
+        <v>84</v>
+      </c>
+      <c r="DM11">
+        <v>84.9</v>
+      </c>
+      <c r="DN11">
+        <v>73</v>
+      </c>
+      <c r="DO11">
+        <v>-46.000000000000014</v>
+      </c>
+      <c r="DP11">
+        <v>53</v>
+      </c>
+      <c r="DQ11">
+        <v>66</v>
+      </c>
+      <c r="DR11">
+        <v>63</v>
+      </c>
+      <c r="DS11">
+        <v>81</v>
+      </c>
+      <c r="DT11">
+        <v>70</v>
+      </c>
+      <c r="DU11">
+        <v>76</v>
+      </c>
+      <c r="DV11">
+        <v>54</v>
+      </c>
+      <c r="DW11">
+        <v>90</v>
+      </c>
+      <c r="DX11">
+        <v>74</v>
+      </c>
+      <c r="DY11">
+        <v>64</v>
+      </c>
+      <c r="DZ11">
+        <v>71</v>
+      </c>
+      <c r="EA11">
+        <v>3</v>
+      </c>
+      <c r="EB11">
+        <v>97</v>
+      </c>
+      <c r="EC11">
+        <v>82</v>
+      </c>
+      <c r="ED11">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="EE11">
+        <v>17.8</v>
+      </c>
+      <c r="EF11">
+        <v>8.9</v>
+      </c>
+      <c r="EG11">
+        <v>79</v>
+      </c>
+      <c r="EH11">
+        <v>68</v>
+      </c>
+      <c r="EI11">
+        <v>79</v>
+      </c>
+      <c r="EJ11">
+        <v>72</v>
+      </c>
     </row>
-    <row r="12" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -4298,8 +5981,143 @@
       <c r="CQ12">
         <v>29.3</v>
       </c>
+      <c r="CR12" s="1">
+        <v>87</v>
+      </c>
+      <c r="CS12" s="1">
+        <v>51</v>
+      </c>
+      <c r="CT12" s="1">
+        <v>17</v>
+      </c>
+      <c r="CU12" s="1">
+        <v>78</v>
+      </c>
+      <c r="CV12" s="1">
+        <v>82</v>
+      </c>
+      <c r="CW12" s="1">
+        <v>40</v>
+      </c>
+      <c r="CX12">
+        <v>33</v>
+      </c>
+      <c r="CY12">
+        <v>38</v>
+      </c>
+      <c r="CZ12">
+        <v>14</v>
+      </c>
+      <c r="DA12">
+        <v>26</v>
+      </c>
+      <c r="DB12">
+        <v>47</v>
+      </c>
+      <c r="DC12">
+        <v>55</v>
+      </c>
+      <c r="DD12">
+        <v>48</v>
+      </c>
+      <c r="DE12">
+        <v>38</v>
+      </c>
+      <c r="DF12">
+        <v>37</v>
+      </c>
+      <c r="DG12">
+        <v>60</v>
+      </c>
+      <c r="DH12">
+        <v>36</v>
+      </c>
+      <c r="DI12">
+        <v>87</v>
+      </c>
+      <c r="DJ12">
+        <v>53</v>
+      </c>
+      <c r="DK12">
+        <v>60</v>
+      </c>
+      <c r="DL12">
+        <v>49</v>
+      </c>
+      <c r="DM12">
+        <v>85.9</v>
+      </c>
+      <c r="DN12">
+        <v>69</v>
+      </c>
+      <c r="DO12">
+        <v>-176.3</v>
+      </c>
+      <c r="DP12">
+        <v>27</v>
+      </c>
+      <c r="DQ12">
+        <v>79</v>
+      </c>
+      <c r="DR12">
+        <v>79</v>
+      </c>
+      <c r="DS12">
+        <v>74</v>
+      </c>
+      <c r="DT12">
+        <v>77</v>
+      </c>
+      <c r="DU12">
+        <v>79</v>
+      </c>
+      <c r="DV12">
+        <v>52</v>
+      </c>
+      <c r="DW12">
+        <v>92</v>
+      </c>
+      <c r="DX12">
+        <v>82</v>
+      </c>
+      <c r="DY12">
+        <v>45</v>
+      </c>
+      <c r="DZ12">
+        <v>47</v>
+      </c>
+      <c r="EA12">
+        <v>1</v>
+      </c>
+      <c r="EB12">
+        <v>97</v>
+      </c>
+      <c r="EC12">
+        <v>73</v>
+      </c>
+      <c r="ED12">
+        <v>43</v>
+      </c>
+      <c r="EE12">
+        <v>12.8</v>
+      </c>
+      <c r="EF12">
+        <v>14.7</v>
+      </c>
+      <c r="EG12">
+        <v>84</v>
+      </c>
+      <c r="EH12">
+        <v>59</v>
+      </c>
+      <c r="EI12">
+        <v>85</v>
+      </c>
+      <c r="EJ12">
+        <v>70</v>
+      </c>
     </row>
-    <row r="13" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -4585,8 +6403,143 @@
       <c r="CQ13">
         <v>39.799999999999997</v>
       </c>
+      <c r="CR13" s="1">
+        <v>85.000000000000014</v>
+      </c>
+      <c r="CS13" s="1">
+        <v>54</v>
+      </c>
+      <c r="CT13" s="1">
+        <v>16</v>
+      </c>
+      <c r="CU13" s="1">
+        <v>71</v>
+      </c>
+      <c r="CV13" s="1">
+        <v>66</v>
+      </c>
+      <c r="CW13" s="1">
+        <v>54</v>
+      </c>
+      <c r="CX13">
+        <v>40</v>
+      </c>
+      <c r="CY13">
+        <v>42.000000000000007</v>
+      </c>
+      <c r="CZ13">
+        <v>30</v>
+      </c>
+      <c r="DA13">
+        <v>47</v>
+      </c>
+      <c r="DB13">
+        <v>49</v>
+      </c>
+      <c r="DC13">
+        <v>60</v>
+      </c>
+      <c r="DD13">
+        <v>58</v>
+      </c>
+      <c r="DE13">
+        <v>41</v>
+      </c>
+      <c r="DF13">
+        <v>47</v>
+      </c>
+      <c r="DG13">
+        <v>61</v>
+      </c>
+      <c r="DH13">
+        <v>56</v>
+      </c>
+      <c r="DI13">
+        <v>84</v>
+      </c>
+      <c r="DJ13">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="DK13">
+        <v>74</v>
+      </c>
+      <c r="DL13">
+        <v>72</v>
+      </c>
+      <c r="DM13">
+        <v>93.7</v>
+      </c>
+      <c r="DN13">
+        <v>72</v>
+      </c>
+      <c r="DO13">
+        <v>-124.89999999999999</v>
+      </c>
+      <c r="DP13">
+        <v>54</v>
+      </c>
+      <c r="DQ13">
+        <v>80</v>
+      </c>
+      <c r="DR13">
+        <v>82</v>
+      </c>
+      <c r="DS13">
+        <v>78</v>
+      </c>
+      <c r="DT13">
+        <v>83</v>
+      </c>
+      <c r="DU13">
+        <v>82</v>
+      </c>
+      <c r="DV13">
+        <v>71</v>
+      </c>
+      <c r="DW13">
+        <v>89</v>
+      </c>
+      <c r="DX13">
+        <v>70</v>
+      </c>
+      <c r="DY13">
+        <v>67</v>
+      </c>
+      <c r="DZ13">
+        <v>68</v>
+      </c>
+      <c r="EA13">
+        <v>10</v>
+      </c>
+      <c r="EB13">
+        <v>82</v>
+      </c>
+      <c r="EC13">
+        <v>67</v>
+      </c>
+      <c r="ED13">
+        <v>49</v>
+      </c>
+      <c r="EE13">
+        <v>14.3</v>
+      </c>
+      <c r="EF13">
+        <v>20.5</v>
+      </c>
+      <c r="EG13">
+        <v>78</v>
+      </c>
+      <c r="EH13">
+        <v>61</v>
+      </c>
+      <c r="EI13">
+        <v>77</v>
+      </c>
+      <c r="EJ13">
+        <v>70</v>
+      </c>
     </row>
-    <row r="14" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -4872,8 +6825,143 @@
       <c r="CQ14">
         <v>28.7</v>
       </c>
+      <c r="CR14" s="1">
+        <v>73.000000000000014</v>
+      </c>
+      <c r="CS14" s="1">
+        <v>31</v>
+      </c>
+      <c r="CT14" s="1">
+        <v>27</v>
+      </c>
+      <c r="CU14" s="1">
+        <v>51</v>
+      </c>
+      <c r="CV14" s="1">
+        <v>54</v>
+      </c>
+      <c r="CW14" s="1">
+        <v>31</v>
+      </c>
+      <c r="CX14">
+        <v>23</v>
+      </c>
+      <c r="CY14">
+        <v>22</v>
+      </c>
+      <c r="CZ14">
+        <v>24</v>
+      </c>
+      <c r="DA14">
+        <v>35</v>
+      </c>
+      <c r="DB14">
+        <v>40</v>
+      </c>
+      <c r="DC14">
+        <v>34</v>
+      </c>
+      <c r="DD14">
+        <v>32</v>
+      </c>
+      <c r="DE14">
+        <v>34</v>
+      </c>
+      <c r="DF14">
+        <v>38</v>
+      </c>
+      <c r="DG14">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="DH14">
+        <v>46</v>
+      </c>
+      <c r="DI14">
+        <v>73</v>
+      </c>
+      <c r="DJ14">
+        <v>35</v>
+      </c>
+      <c r="DK14">
+        <v>54</v>
+      </c>
+      <c r="DL14">
+        <v>42</v>
+      </c>
+      <c r="DM14">
+        <v>82.4</v>
+      </c>
+      <c r="DN14">
+        <v>76</v>
+      </c>
+      <c r="DO14">
+        <v>-133.6</v>
+      </c>
+      <c r="DP14">
+        <v>47</v>
+      </c>
+      <c r="DQ14">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="DR14">
+        <v>71</v>
+      </c>
+      <c r="DS14">
+        <v>60</v>
+      </c>
+      <c r="DT14">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="DU14">
+        <v>64</v>
+      </c>
+      <c r="DV14">
+        <v>36</v>
+      </c>
+      <c r="DW14">
+        <v>81</v>
+      </c>
+      <c r="DX14">
+        <v>59</v>
+      </c>
+      <c r="DY14">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="DZ14">
+        <v>65</v>
+      </c>
+      <c r="EA14">
+        <v>4</v>
+      </c>
+      <c r="EB14">
+        <v>71</v>
+      </c>
+      <c r="EC14">
+        <v>51</v>
+      </c>
+      <c r="ED14">
+        <v>34</v>
+      </c>
+      <c r="EE14">
+        <v>13</v>
+      </c>
+      <c r="EF14">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="EG14">
+        <v>77</v>
+      </c>
+      <c r="EH14">
+        <v>63</v>
+      </c>
+      <c r="EI14">
+        <v>79</v>
+      </c>
+      <c r="EJ14">
+        <v>68</v>
+      </c>
     </row>
-    <row r="15" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -5159,8 +7247,143 @@
       <c r="CQ15">
         <v>39.6</v>
       </c>
+      <c r="CR15" s="1">
+        <v>63</v>
+      </c>
+      <c r="CS15" s="1">
+        <v>49</v>
+      </c>
+      <c r="CT15" s="1">
+        <v>44.000000000000007</v>
+      </c>
+      <c r="CU15" s="1">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="CV15" s="1">
+        <v>58.000000000000007</v>
+      </c>
+      <c r="CW15" s="1">
+        <v>41</v>
+      </c>
+      <c r="CX15">
+        <v>59</v>
+      </c>
+      <c r="CY15">
+        <v>61</v>
+      </c>
+      <c r="CZ15">
+        <v>41</v>
+      </c>
+      <c r="DA15">
+        <v>43.999999999999993</v>
+      </c>
+      <c r="DB15">
+        <v>66</v>
+      </c>
+      <c r="DC15">
+        <v>67</v>
+      </c>
+      <c r="DD15">
+        <v>64</v>
+      </c>
+      <c r="DE15">
+        <v>51</v>
+      </c>
+      <c r="DF15">
+        <v>60</v>
+      </c>
+      <c r="DG15">
+        <v>70</v>
+      </c>
+      <c r="DH15">
+        <v>56</v>
+      </c>
+      <c r="DI15">
+        <v>79</v>
+      </c>
+      <c r="DJ15">
+        <v>65</v>
+      </c>
+      <c r="DK15">
+        <v>64</v>
+      </c>
+      <c r="DL15">
+        <v>77</v>
+      </c>
+      <c r="DM15">
+        <v>90.2</v>
+      </c>
+      <c r="DN15">
+        <v>84</v>
+      </c>
+      <c r="DO15">
+        <v>-161.10000000000002</v>
+      </c>
+      <c r="DP15">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="DQ15">
+        <v>69</v>
+      </c>
+      <c r="DR15">
+        <v>76</v>
+      </c>
+      <c r="DS15">
+        <v>71</v>
+      </c>
+      <c r="DT15">
+        <v>70</v>
+      </c>
+      <c r="DU15">
+        <v>73</v>
+      </c>
+      <c r="DV15">
+        <v>67</v>
+      </c>
+      <c r="DW15">
+        <v>89</v>
+      </c>
+      <c r="DX15">
+        <v>71</v>
+      </c>
+      <c r="DY15">
+        <v>63</v>
+      </c>
+      <c r="DZ15">
+        <v>65</v>
+      </c>
+      <c r="EA15">
+        <v>12.000000000000002</v>
+      </c>
+      <c r="EB15">
+        <v>87</v>
+      </c>
+      <c r="EC15">
+        <v>74</v>
+      </c>
+      <c r="ED15">
+        <v>64</v>
+      </c>
+      <c r="EE15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="EF15">
+        <v>9.9</v>
+      </c>
+      <c r="EG15">
+        <v>84</v>
+      </c>
+      <c r="EH15">
+        <v>72</v>
+      </c>
+      <c r="EI15">
+        <v>78</v>
+      </c>
+      <c r="EJ15">
+        <v>76</v>
+      </c>
     </row>
-    <row r="16" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -5446,8 +7669,143 @@
       <c r="CQ16">
         <v>29.1</v>
       </c>
+      <c r="CR16" s="1">
+        <v>75</v>
+      </c>
+      <c r="CS16" s="1">
+        <v>44</v>
+      </c>
+      <c r="CT16" s="1">
+        <v>29.000000000000004</v>
+      </c>
+      <c r="CU16" s="1">
+        <v>63</v>
+      </c>
+      <c r="CV16" s="1">
+        <v>67</v>
+      </c>
+      <c r="CW16" s="1">
+        <v>45</v>
+      </c>
+      <c r="CX16">
+        <v>25</v>
+      </c>
+      <c r="CY16">
+        <v>25</v>
+      </c>
+      <c r="CZ16">
+        <v>18</v>
+      </c>
+      <c r="DA16">
+        <v>28</v>
+      </c>
+      <c r="DB16">
+        <v>44.999999999999993</v>
+      </c>
+      <c r="DC16">
+        <v>58</v>
+      </c>
+      <c r="DD16">
+        <v>42.000000000000007</v>
+      </c>
+      <c r="DE16">
+        <v>26</v>
+      </c>
+      <c r="DF16">
+        <v>46</v>
+      </c>
+      <c r="DG16">
+        <v>55</v>
+      </c>
+      <c r="DH16">
+        <v>36</v>
+      </c>
+      <c r="DI16">
+        <v>82</v>
+      </c>
+      <c r="DJ16">
+        <v>63</v>
+      </c>
+      <c r="DK16">
+        <v>62</v>
+      </c>
+      <c r="DL16">
+        <v>70</v>
+      </c>
+      <c r="DM16">
+        <v>77.7</v>
+      </c>
+      <c r="DN16">
+        <v>65</v>
+      </c>
+      <c r="DO16">
+        <v>-158.4</v>
+      </c>
+      <c r="DP16">
+        <v>34</v>
+      </c>
+      <c r="DQ16">
+        <v>73</v>
+      </c>
+      <c r="DR16">
+        <v>78</v>
+      </c>
+      <c r="DS16">
+        <v>68</v>
+      </c>
+      <c r="DT16">
+        <v>78</v>
+      </c>
+      <c r="DU16">
+        <v>76</v>
+      </c>
+      <c r="DV16">
+        <v>51</v>
+      </c>
+      <c r="DW16">
+        <v>79</v>
+      </c>
+      <c r="DX16">
+        <v>66</v>
+      </c>
+      <c r="DY16">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="DZ16">
+        <v>63</v>
+      </c>
+      <c r="EA16">
+        <v>5</v>
+      </c>
+      <c r="EB16">
+        <v>82</v>
+      </c>
+      <c r="EC16">
+        <v>64</v>
+      </c>
+      <c r="ED16">
+        <v>44</v>
+      </c>
+      <c r="EE16">
+        <v>13.8</v>
+      </c>
+      <c r="EF16">
+        <v>14.6</v>
+      </c>
+      <c r="EG16">
+        <v>74</v>
+      </c>
+      <c r="EH16">
+        <v>59</v>
+      </c>
+      <c r="EI16">
+        <v>75</v>
+      </c>
+      <c r="EJ16">
+        <v>65</v>
+      </c>
     </row>
-    <row r="17" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -5733,8 +8091,143 @@
       <c r="CQ17">
         <v>31.6</v>
       </c>
+      <c r="CR17" s="1">
+        <v>79</v>
+      </c>
+      <c r="CS17" s="1">
+        <v>50</v>
+      </c>
+      <c r="CT17" s="1">
+        <v>29.000000000000004</v>
+      </c>
+      <c r="CU17" s="1">
+        <v>72.000000000000014</v>
+      </c>
+      <c r="CV17" s="1">
+        <v>81</v>
+      </c>
+      <c r="CW17" s="1">
+        <v>31</v>
+      </c>
+      <c r="CX17">
+        <v>35</v>
+      </c>
+      <c r="CY17">
+        <v>29</v>
+      </c>
+      <c r="CZ17">
+        <v>30</v>
+      </c>
+      <c r="DA17">
+        <v>33</v>
+      </c>
+      <c r="DB17">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="DC17">
+        <v>47</v>
+      </c>
+      <c r="DD17">
+        <v>48</v>
+      </c>
+      <c r="DE17">
+        <v>38</v>
+      </c>
+      <c r="DF17">
+        <v>34</v>
+      </c>
+      <c r="DG17">
+        <v>54</v>
+      </c>
+      <c r="DH17">
+        <v>39</v>
+      </c>
+      <c r="DI17">
+        <v>79</v>
+      </c>
+      <c r="DJ17">
+        <v>53</v>
+      </c>
+      <c r="DK17">
+        <v>59</v>
+      </c>
+      <c r="DL17">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="DM17">
+        <v>89</v>
+      </c>
+      <c r="DN17">
+        <v>65</v>
+      </c>
+      <c r="DO17">
+        <v>-151.29999999999998</v>
+      </c>
+      <c r="DP17">
+        <v>52</v>
+      </c>
+      <c r="DQ17">
+        <v>81</v>
+      </c>
+      <c r="DR17">
+        <v>86</v>
+      </c>
+      <c r="DS17">
+        <v>84</v>
+      </c>
+      <c r="DT17">
+        <v>72</v>
+      </c>
+      <c r="DU17">
+        <v>82</v>
+      </c>
+      <c r="DV17">
+        <v>47</v>
+      </c>
+      <c r="DW17">
+        <v>88</v>
+      </c>
+      <c r="DX17">
+        <v>87</v>
+      </c>
+      <c r="DY17">
+        <v>52</v>
+      </c>
+      <c r="DZ17">
+        <v>53</v>
+      </c>
+      <c r="EA17">
+        <v>5</v>
+      </c>
+      <c r="EB17">
+        <v>91</v>
+      </c>
+      <c r="EC17">
+        <v>74</v>
+      </c>
+      <c r="ED17">
+        <v>32</v>
+      </c>
+      <c r="EE17">
+        <v>13</v>
+      </c>
+      <c r="EF17">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="EG17">
+        <v>84</v>
+      </c>
+      <c r="EH17">
+        <v>70</v>
+      </c>
+      <c r="EI17">
+        <v>86</v>
+      </c>
+      <c r="EJ17">
+        <v>73</v>
+      </c>
     </row>
-    <row r="18" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -6020,8 +8513,143 @@
       <c r="CQ18">
         <v>33.299999999999997</v>
       </c>
+      <c r="CR18" s="1">
+        <v>87</v>
+      </c>
+      <c r="CS18" s="1">
+        <v>74</v>
+      </c>
+      <c r="CT18" s="1">
+        <v>17</v>
+      </c>
+      <c r="CU18" s="1">
+        <v>83</v>
+      </c>
+      <c r="CV18" s="1">
+        <v>84</v>
+      </c>
+      <c r="CW18" s="1">
+        <v>61.000000000000007</v>
+      </c>
+      <c r="CX18">
+        <v>67</v>
+      </c>
+      <c r="CY18">
+        <v>78</v>
+      </c>
+      <c r="CZ18">
+        <v>69</v>
+      </c>
+      <c r="DA18">
+        <v>67</v>
+      </c>
+      <c r="DB18">
+        <v>56</v>
+      </c>
+      <c r="DC18">
+        <v>89</v>
+      </c>
+      <c r="DD18">
+        <v>63</v>
+      </c>
+      <c r="DE18">
+        <v>73</v>
+      </c>
+      <c r="DF18">
+        <v>64</v>
+      </c>
+      <c r="DG18">
+        <v>78</v>
+      </c>
+      <c r="DH18">
+        <v>80</v>
+      </c>
+      <c r="DI18">
+        <v>82</v>
+      </c>
+      <c r="DJ18">
+        <v>59</v>
+      </c>
+      <c r="DK18">
+        <v>64</v>
+      </c>
+      <c r="DL18">
+        <v>70</v>
+      </c>
+      <c r="DM18">
+        <v>94.1</v>
+      </c>
+      <c r="DN18">
+        <v>87</v>
+      </c>
+      <c r="DO18">
+        <v>-103.89999999999999</v>
+      </c>
+      <c r="DP18">
+        <v>59</v>
+      </c>
+      <c r="DQ18">
+        <v>72</v>
+      </c>
+      <c r="DR18">
+        <v>83</v>
+      </c>
+      <c r="DS18">
+        <v>74</v>
+      </c>
+      <c r="DT18">
+        <v>49</v>
+      </c>
+      <c r="DU18">
+        <v>65</v>
+      </c>
+      <c r="DV18">
+        <v>64</v>
+      </c>
+      <c r="DW18">
+        <v>95</v>
+      </c>
+      <c r="DX18">
+        <v>78</v>
+      </c>
+      <c r="DY18">
+        <v>75</v>
+      </c>
+      <c r="DZ18">
+        <v>75</v>
+      </c>
+      <c r="EA18">
+        <v>16</v>
+      </c>
+      <c r="EB18">
+        <v>78</v>
+      </c>
+      <c r="EC18">
+        <v>60</v>
+      </c>
+      <c r="ED18">
+        <v>36</v>
+      </c>
+      <c r="EE18">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="EF18">
+        <v>15.6</v>
+      </c>
+      <c r="EG18">
+        <v>81</v>
+      </c>
+      <c r="EH18">
+        <v>67</v>
+      </c>
+      <c r="EI18">
+        <v>77</v>
+      </c>
+      <c r="EJ18">
+        <v>76</v>
+      </c>
     </row>
-    <row r="19" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -6307,8 +8935,143 @@
       <c r="CQ19">
         <v>41.3</v>
       </c>
+      <c r="CR19" s="1">
+        <v>84.000000000000014</v>
+      </c>
+      <c r="CS19" s="1">
+        <v>67</v>
+      </c>
+      <c r="CT19" s="1">
+        <v>17</v>
+      </c>
+      <c r="CU19" s="1">
+        <v>79</v>
+      </c>
+      <c r="CV19" s="1">
+        <v>81</v>
+      </c>
+      <c r="CW19" s="1">
+        <v>61</v>
+      </c>
+      <c r="CX19">
+        <v>73</v>
+      </c>
+      <c r="CY19">
+        <v>75</v>
+      </c>
+      <c r="CZ19">
+        <v>48</v>
+      </c>
+      <c r="DA19">
+        <v>47</v>
+      </c>
+      <c r="DB19">
+        <v>47</v>
+      </c>
+      <c r="DC19">
+        <v>86</v>
+      </c>
+      <c r="DD19">
+        <v>58</v>
+      </c>
+      <c r="DE19">
+        <v>54</v>
+      </c>
+      <c r="DF19">
+        <v>58</v>
+      </c>
+      <c r="DG19">
+        <v>73</v>
+      </c>
+      <c r="DH19">
+        <v>60</v>
+      </c>
+      <c r="DI19">
+        <v>83</v>
+      </c>
+      <c r="DJ19">
+        <v>75</v>
+      </c>
+      <c r="DK19">
+        <v>79</v>
+      </c>
+      <c r="DL19">
+        <v>79</v>
+      </c>
+      <c r="DM19">
+        <v>93.7</v>
+      </c>
+      <c r="DN19">
+        <v>76</v>
+      </c>
+      <c r="DO19">
+        <v>-84.300000000000011</v>
+      </c>
+      <c r="DP19">
+        <v>67</v>
+      </c>
+      <c r="DQ19">
+        <v>78</v>
+      </c>
+      <c r="DR19">
+        <v>87</v>
+      </c>
+      <c r="DS19">
+        <v>81</v>
+      </c>
+      <c r="DT19">
+        <v>63</v>
+      </c>
+      <c r="DU19">
+        <v>75</v>
+      </c>
+      <c r="DV19">
+        <v>71</v>
+      </c>
+      <c r="DW19">
+        <v>95</v>
+      </c>
+      <c r="DX19">
+        <v>74</v>
+      </c>
+      <c r="DY19">
+        <v>71</v>
+      </c>
+      <c r="DZ19">
+        <v>73</v>
+      </c>
+      <c r="EA19">
+        <v>8</v>
+      </c>
+      <c r="EB19">
+        <v>90</v>
+      </c>
+      <c r="EC19">
+        <v>74</v>
+      </c>
+      <c r="ED19">
+        <v>52</v>
+      </c>
+      <c r="EE19">
+        <v>12.9</v>
+      </c>
+      <c r="EF19">
+        <v>14.9</v>
+      </c>
+      <c r="EG19">
+        <v>90</v>
+      </c>
+      <c r="EH19">
+        <v>76</v>
+      </c>
+      <c r="EI19">
+        <v>85</v>
+      </c>
+      <c r="EJ19">
+        <v>84</v>
+      </c>
     </row>
-    <row r="20" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -6594,8 +9357,143 @@
       <c r="CQ20">
         <v>48.1</v>
       </c>
+      <c r="CR20" s="1">
+        <v>81</v>
+      </c>
+      <c r="CS20" s="1">
+        <v>42.000000000000007</v>
+      </c>
+      <c r="CT20" s="1">
+        <v>19</v>
+      </c>
+      <c r="CU20" s="1">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="CV20" s="1">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="CW20" s="1">
+        <v>31</v>
+      </c>
+      <c r="CX20">
+        <v>48</v>
+      </c>
+      <c r="CY20">
+        <v>44.999999999999993</v>
+      </c>
+      <c r="CZ20">
+        <v>43.999999999999993</v>
+      </c>
+      <c r="DA20">
+        <v>62</v>
+      </c>
+      <c r="DB20">
+        <v>64</v>
+      </c>
+      <c r="DC20">
+        <v>67</v>
+      </c>
+      <c r="DD20">
+        <v>64</v>
+      </c>
+      <c r="DE20">
+        <v>58</v>
+      </c>
+      <c r="DF20">
+        <v>48</v>
+      </c>
+      <c r="DG20">
+        <v>67</v>
+      </c>
+      <c r="DH20">
+        <v>70</v>
+      </c>
+      <c r="DI20">
+        <v>71</v>
+      </c>
+      <c r="DJ20">
+        <v>50</v>
+      </c>
+      <c r="DK20">
+        <v>82</v>
+      </c>
+      <c r="DL20">
+        <v>66</v>
+      </c>
+      <c r="DM20">
+        <v>87.3</v>
+      </c>
+      <c r="DN20">
+        <v>75</v>
+      </c>
+      <c r="DO20">
+        <v>6.7999999999999972</v>
+      </c>
+      <c r="DP20">
+        <v>94</v>
+      </c>
+      <c r="DQ20">
+        <v>76</v>
+      </c>
+      <c r="DR20">
+        <v>82</v>
+      </c>
+      <c r="DS20">
+        <v>78</v>
+      </c>
+      <c r="DT20">
+        <v>81</v>
+      </c>
+      <c r="DU20">
+        <v>83</v>
+      </c>
+      <c r="DV20">
+        <v>46</v>
+      </c>
+      <c r="DW20">
+        <v>93</v>
+      </c>
+      <c r="DX20">
+        <v>74</v>
+      </c>
+      <c r="DY20">
+        <v>76</v>
+      </c>
+      <c r="DZ20">
+        <v>84</v>
+      </c>
+      <c r="EA20">
+        <v>20</v>
+      </c>
+      <c r="EB20">
+        <v>71</v>
+      </c>
+      <c r="EC20">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="ED20">
+        <v>37</v>
+      </c>
+      <c r="EE20">
+        <v>16.2</v>
+      </c>
+      <c r="EF20">
+        <v>14.1</v>
+      </c>
+      <c r="EG20">
+        <v>87</v>
+      </c>
+      <c r="EH20">
+        <v>68</v>
+      </c>
+      <c r="EI20">
+        <v>81</v>
+      </c>
+      <c r="EJ20">
+        <v>74</v>
+      </c>
     </row>
-    <row r="21" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -6881,8 +9779,143 @@
       <c r="CQ21">
         <v>33.299999999999997</v>
       </c>
+      <c r="CR21" s="1">
+        <v>76.999999999999986</v>
+      </c>
+      <c r="CS21" s="1">
+        <v>57.000000000000007</v>
+      </c>
+      <c r="CT21" s="1">
+        <v>31</v>
+      </c>
+      <c r="CU21" s="1">
+        <v>72</v>
+      </c>
+      <c r="CV21" s="1">
+        <v>78</v>
+      </c>
+      <c r="CW21" s="1">
+        <v>46</v>
+      </c>
+      <c r="CX21">
+        <v>38</v>
+      </c>
+      <c r="CY21">
+        <v>40</v>
+      </c>
+      <c r="CZ21">
+        <v>26</v>
+      </c>
+      <c r="DA21">
+        <v>47</v>
+      </c>
+      <c r="DB21">
+        <v>50</v>
+      </c>
+      <c r="DC21">
+        <v>67</v>
+      </c>
+      <c r="DD21">
+        <v>50</v>
+      </c>
+      <c r="DE21">
+        <v>53</v>
+      </c>
+      <c r="DF21">
+        <v>46</v>
+      </c>
+      <c r="DG21">
+        <v>62</v>
+      </c>
+      <c r="DH21">
+        <v>61</v>
+      </c>
+      <c r="DI21">
+        <v>87</v>
+      </c>
+      <c r="DJ21">
+        <v>64</v>
+      </c>
+      <c r="DK21">
+        <v>68</v>
+      </c>
+      <c r="DL21">
+        <v>68</v>
+      </c>
+      <c r="DM21">
+        <v>89.3</v>
+      </c>
+      <c r="DN21">
+        <v>77</v>
+      </c>
+      <c r="DO21">
+        <v>-70.799999999999983</v>
+      </c>
+      <c r="DP21">
+        <v>65</v>
+      </c>
+      <c r="DQ21">
+        <v>62</v>
+      </c>
+      <c r="DR21">
+        <v>70</v>
+      </c>
+      <c r="DS21">
+        <v>72</v>
+      </c>
+      <c r="DT21">
+        <v>43</v>
+      </c>
+      <c r="DU21">
+        <v>69</v>
+      </c>
+      <c r="DV21">
+        <v>66</v>
+      </c>
+      <c r="DW21">
+        <v>87</v>
+      </c>
+      <c r="DX21">
+        <v>71</v>
+      </c>
+      <c r="DY21">
+        <v>69</v>
+      </c>
+      <c r="DZ21">
+        <v>82</v>
+      </c>
+      <c r="EA21">
+        <v>14.000000000000002</v>
+      </c>
+      <c r="EB21">
+        <v>81</v>
+      </c>
+      <c r="EC21">
+        <v>70</v>
+      </c>
+      <c r="ED21">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="EE21">
+        <v>12.9</v>
+      </c>
+      <c r="EF21">
+        <v>20</v>
+      </c>
+      <c r="EG21">
+        <v>82</v>
+      </c>
+      <c r="EH21">
+        <v>73</v>
+      </c>
+      <c r="EI21">
+        <v>80</v>
+      </c>
+      <c r="EJ21">
+        <v>68</v>
+      </c>
     </row>
-    <row r="22" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7168,8 +10201,143 @@
       <c r="CQ22">
         <v>43.3</v>
       </c>
+      <c r="CR22" s="1">
+        <v>90</v>
+      </c>
+      <c r="CS22" s="1">
+        <v>64</v>
+      </c>
+      <c r="CT22" s="1">
+        <v>12</v>
+      </c>
+      <c r="CU22" s="1">
+        <v>77</v>
+      </c>
+      <c r="CV22" s="1">
+        <v>75</v>
+      </c>
+      <c r="CW22" s="1">
+        <v>54</v>
+      </c>
+      <c r="CX22">
+        <v>38</v>
+      </c>
+      <c r="CY22">
+        <v>30</v>
+      </c>
+      <c r="CZ22">
+        <v>69</v>
+      </c>
+      <c r="DA22">
+        <v>63</v>
+      </c>
+      <c r="DB22">
+        <v>65</v>
+      </c>
+      <c r="DC22">
+        <v>72</v>
+      </c>
+      <c r="DD22">
+        <v>52</v>
+      </c>
+      <c r="DE22">
+        <v>51</v>
+      </c>
+      <c r="DF22">
+        <v>42.000000000000007</v>
+      </c>
+      <c r="DG22">
+        <v>70</v>
+      </c>
+      <c r="DH22">
+        <v>68</v>
+      </c>
+      <c r="DI22">
+        <v>78</v>
+      </c>
+      <c r="DJ22">
+        <v>70</v>
+      </c>
+      <c r="DK22">
+        <v>74</v>
+      </c>
+      <c r="DL22">
+        <v>74</v>
+      </c>
+      <c r="DM22">
+        <v>94.5</v>
+      </c>
+      <c r="DN22">
+        <v>66</v>
+      </c>
+      <c r="DO22">
+        <v>-14.899999999999977</v>
+      </c>
+      <c r="DP22">
+        <v>60</v>
+      </c>
+      <c r="DQ22">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="DR22">
+        <v>68</v>
+      </c>
+      <c r="DS22">
+        <v>80</v>
+      </c>
+      <c r="DT22">
+        <v>64</v>
+      </c>
+      <c r="DU22">
+        <v>81</v>
+      </c>
+      <c r="DV22">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="DW22">
+        <v>91</v>
+      </c>
+      <c r="DX22">
+        <v>87</v>
+      </c>
+      <c r="DY22">
+        <v>63</v>
+      </c>
+      <c r="DZ22">
+        <v>74</v>
+      </c>
+      <c r="EA22">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="EB22">
+        <v>89</v>
+      </c>
+      <c r="EC22">
+        <v>68</v>
+      </c>
+      <c r="ED22">
+        <v>36</v>
+      </c>
+      <c r="EE22">
+        <v>22</v>
+      </c>
+      <c r="EF22">
+        <v>11.3</v>
+      </c>
+      <c r="EG22">
+        <v>78</v>
+      </c>
+      <c r="EH22">
+        <v>65</v>
+      </c>
+      <c r="EI22">
+        <v>79</v>
+      </c>
+      <c r="EJ22">
+        <v>56.999999999999993</v>
+      </c>
     </row>
-    <row r="23" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -7455,8 +10623,143 @@
       <c r="CQ23">
         <v>36.299999999999997</v>
       </c>
+      <c r="CR23" s="1">
+        <v>68</v>
+      </c>
+      <c r="CS23" s="1">
+        <v>31.999999999999996</v>
+      </c>
+      <c r="CT23" s="1">
+        <v>31</v>
+      </c>
+      <c r="CU23" s="1">
+        <v>48</v>
+      </c>
+      <c r="CV23" s="1">
+        <v>62</v>
+      </c>
+      <c r="CW23" s="1">
+        <v>36</v>
+      </c>
+      <c r="CX23">
+        <v>18</v>
+      </c>
+      <c r="CY23">
+        <v>22</v>
+      </c>
+      <c r="CZ23">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="DA23">
+        <v>38</v>
+      </c>
+      <c r="DB23">
+        <v>46</v>
+      </c>
+      <c r="DC23">
+        <v>46</v>
+      </c>
+      <c r="DD23">
+        <v>38</v>
+      </c>
+      <c r="DE23">
+        <v>31</v>
+      </c>
+      <c r="DF23">
+        <v>46</v>
+      </c>
+      <c r="DG23">
+        <v>52</v>
+      </c>
+      <c r="DH23">
+        <v>47</v>
+      </c>
+      <c r="DI23">
+        <v>75</v>
+      </c>
+      <c r="DJ23">
+        <v>49</v>
+      </c>
+      <c r="DK23">
+        <v>81</v>
+      </c>
+      <c r="DL23">
+        <v>74</v>
+      </c>
+      <c r="DM23">
+        <v>88.2</v>
+      </c>
+      <c r="DN23">
+        <v>89</v>
+      </c>
+      <c r="DO23">
+        <v>-48.399999999999991</v>
+      </c>
+      <c r="DP23">
+        <v>86</v>
+      </c>
+      <c r="DQ23">
+        <v>76</v>
+      </c>
+      <c r="DR23">
+        <v>85</v>
+      </c>
+      <c r="DS23">
+        <v>80</v>
+      </c>
+      <c r="DT23">
+        <v>83</v>
+      </c>
+      <c r="DU23">
+        <v>79</v>
+      </c>
+      <c r="DV23">
+        <v>50</v>
+      </c>
+      <c r="DW23">
+        <v>86</v>
+      </c>
+      <c r="DX23">
+        <v>60</v>
+      </c>
+      <c r="DY23">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="DZ23">
+        <v>69</v>
+      </c>
+      <c r="EA23">
+        <v>11</v>
+      </c>
+      <c r="EB23">
+        <v>80</v>
+      </c>
+      <c r="EC23">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="ED23">
+        <v>37</v>
+      </c>
+      <c r="EE23">
+        <v>13.7</v>
+      </c>
+      <c r="EF23">
+        <v>12.2</v>
+      </c>
+      <c r="EG23">
+        <v>92</v>
+      </c>
+      <c r="EH23">
+        <v>82</v>
+      </c>
+      <c r="EI23">
+        <v>91</v>
+      </c>
+      <c r="EJ23">
+        <v>84</v>
+      </c>
     </row>
-    <row r="24" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -7742,8 +11045,143 @@
       <c r="CQ24">
         <v>32.5</v>
       </c>
+      <c r="CR24" s="1">
+        <v>70</v>
+      </c>
+      <c r="CS24" s="1">
+        <v>46</v>
+      </c>
+      <c r="CT24" s="1">
+        <v>33</v>
+      </c>
+      <c r="CU24" s="1">
+        <v>66</v>
+      </c>
+      <c r="CV24" s="1">
+        <v>70</v>
+      </c>
+      <c r="CW24" s="1">
+        <v>52</v>
+      </c>
+      <c r="CX24">
+        <v>50</v>
+      </c>
+      <c r="CY24">
+        <v>44.999999999999993</v>
+      </c>
+      <c r="CZ24">
+        <v>53</v>
+      </c>
+      <c r="DA24">
+        <v>57</v>
+      </c>
+      <c r="DB24">
+        <v>58</v>
+      </c>
+      <c r="DC24">
+        <v>63</v>
+      </c>
+      <c r="DD24">
+        <v>54</v>
+      </c>
+      <c r="DE24">
+        <v>54</v>
+      </c>
+      <c r="DF24">
+        <v>58</v>
+      </c>
+      <c r="DG24">
+        <v>61</v>
+      </c>
+      <c r="DH24">
+        <v>63</v>
+      </c>
+      <c r="DI24">
+        <v>71</v>
+      </c>
+      <c r="DJ24">
+        <v>54</v>
+      </c>
+      <c r="DK24">
+        <v>59</v>
+      </c>
+      <c r="DL24">
+        <v>59</v>
+      </c>
+      <c r="DM24">
+        <v>87.5</v>
+      </c>
+      <c r="DN24">
+        <v>77</v>
+      </c>
+      <c r="DO24">
+        <v>-56.900000000000006</v>
+      </c>
+      <c r="DP24">
+        <v>78</v>
+      </c>
+      <c r="DQ24" s="1">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="DR24" s="1">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="DS24" s="1">
+        <v>60</v>
+      </c>
+      <c r="DT24" s="1">
+        <v>49</v>
+      </c>
+      <c r="DU24" s="1">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="DV24">
+        <v>35</v>
+      </c>
+      <c r="DW24">
+        <v>68</v>
+      </c>
+      <c r="DX24">
+        <v>43</v>
+      </c>
+      <c r="DY24">
+        <v>52</v>
+      </c>
+      <c r="DZ24">
+        <v>64</v>
+      </c>
+      <c r="EA24">
+        <v>11</v>
+      </c>
+      <c r="EB24">
+        <v>87</v>
+      </c>
+      <c r="EC24">
+        <v>64</v>
+      </c>
+      <c r="ED24">
+        <v>51</v>
+      </c>
+      <c r="EE24">
+        <v>17.2</v>
+      </c>
+      <c r="EF24">
+        <v>14.7</v>
+      </c>
+      <c r="EG24">
+        <v>74</v>
+      </c>
+      <c r="EH24">
+        <v>59</v>
+      </c>
+      <c r="EI24">
+        <v>72</v>
+      </c>
+      <c r="EJ24">
+        <v>61</v>
+      </c>
     </row>
-    <row r="25" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -8029,8 +11467,143 @@
       <c r="CQ25">
         <v>41.5</v>
       </c>
+      <c r="CR25" s="1">
+        <v>77</v>
+      </c>
+      <c r="CS25" s="1">
+        <v>60.000000000000007</v>
+      </c>
+      <c r="CT25" s="1">
+        <v>29.000000000000004</v>
+      </c>
+      <c r="CU25" s="1">
+        <v>73</v>
+      </c>
+      <c r="CV25" s="1">
+        <v>76</v>
+      </c>
+      <c r="CW25" s="1">
+        <v>53</v>
+      </c>
+      <c r="CX25">
+        <v>64</v>
+      </c>
+      <c r="CY25">
+        <v>58</v>
+      </c>
+      <c r="CZ25">
+        <v>51</v>
+      </c>
+      <c r="DA25">
+        <v>46</v>
+      </c>
+      <c r="DB25">
+        <v>73</v>
+      </c>
+      <c r="DC25">
+        <v>75</v>
+      </c>
+      <c r="DD25">
+        <v>66</v>
+      </c>
+      <c r="DE25">
+        <v>46</v>
+      </c>
+      <c r="DF25">
+        <v>69</v>
+      </c>
+      <c r="DG25">
+        <v>79</v>
+      </c>
+      <c r="DH25">
+        <v>52</v>
+      </c>
+      <c r="DI25">
+        <v>86</v>
+      </c>
+      <c r="DJ25">
+        <v>69</v>
+      </c>
+      <c r="DK25">
+        <v>73</v>
+      </c>
+      <c r="DL25">
+        <v>78</v>
+      </c>
+      <c r="DM25">
+        <v>90.2</v>
+      </c>
+      <c r="DN25">
+        <v>77</v>
+      </c>
+      <c r="DO25">
+        <v>-138.90000000000003</v>
+      </c>
+      <c r="DP25">
+        <v>65</v>
+      </c>
+      <c r="DQ25" s="1">
+        <v>67</v>
+      </c>
+      <c r="DR25" s="1">
+        <v>80</v>
+      </c>
+      <c r="DS25" s="1">
+        <v>68</v>
+      </c>
+      <c r="DT25" s="1">
+        <v>50</v>
+      </c>
+      <c r="DU25" s="1">
+        <v>62</v>
+      </c>
+      <c r="DV25">
+        <v>64</v>
+      </c>
+      <c r="DW25">
+        <v>80</v>
+      </c>
+      <c r="DX25">
+        <v>66</v>
+      </c>
+      <c r="DY25">
+        <v>72</v>
+      </c>
+      <c r="DZ25">
+        <v>77</v>
+      </c>
+      <c r="EA25">
+        <v>4</v>
+      </c>
+      <c r="EB25">
+        <v>90</v>
+      </c>
+      <c r="EC25">
+        <v>75</v>
+      </c>
+      <c r="ED25">
+        <v>60</v>
+      </c>
+      <c r="EE25">
+        <v>11.5</v>
+      </c>
+      <c r="EF25">
+        <v>13.9</v>
+      </c>
+      <c r="EG25">
+        <v>88</v>
+      </c>
+      <c r="EH25">
+        <v>84</v>
+      </c>
+      <c r="EI25">
+        <v>85</v>
+      </c>
+      <c r="EJ25">
+        <v>86</v>
+      </c>
     </row>
-    <row r="26" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -8316,8 +11889,143 @@
       <c r="CQ26">
         <v>42.2</v>
       </c>
+      <c r="CR26" s="1">
+        <v>85</v>
+      </c>
+      <c r="CS26" s="1">
+        <v>52</v>
+      </c>
+      <c r="CT26" s="1">
+        <v>13</v>
+      </c>
+      <c r="CU26" s="1">
+        <v>83</v>
+      </c>
+      <c r="CV26" s="1">
+        <v>84</v>
+      </c>
+      <c r="CW26" s="1">
+        <v>44</v>
+      </c>
+      <c r="CX26">
+        <v>41</v>
+      </c>
+      <c r="CY26">
+        <v>39</v>
+      </c>
+      <c r="CZ26">
+        <v>14</v>
+      </c>
+      <c r="DA26">
+        <v>30</v>
+      </c>
+      <c r="DB26">
+        <v>53</v>
+      </c>
+      <c r="DC26">
+        <v>68</v>
+      </c>
+      <c r="DD26">
+        <v>33</v>
+      </c>
+      <c r="DE26">
+        <v>32</v>
+      </c>
+      <c r="DF26">
+        <v>48</v>
+      </c>
+      <c r="DG26">
+        <v>65</v>
+      </c>
+      <c r="DH26">
+        <v>43.999999999999993</v>
+      </c>
+      <c r="DI26">
+        <v>90</v>
+      </c>
+      <c r="DJ26">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="DK26">
+        <v>83</v>
+      </c>
+      <c r="DL26">
+        <v>77</v>
+      </c>
+      <c r="DM26">
+        <v>94</v>
+      </c>
+      <c r="DN26">
+        <v>63</v>
+      </c>
+      <c r="DO26">
+        <v>-106.59999999999997</v>
+      </c>
+      <c r="DP26">
+        <v>38</v>
+      </c>
+      <c r="DQ26">
+        <v>59</v>
+      </c>
+      <c r="DR26">
+        <v>65</v>
+      </c>
+      <c r="DS26">
+        <v>78</v>
+      </c>
+      <c r="DT26">
+        <v>63</v>
+      </c>
+      <c r="DU26">
+        <v>77</v>
+      </c>
+      <c r="DV26">
+        <v>46</v>
+      </c>
+      <c r="DW26">
+        <v>85</v>
+      </c>
+      <c r="DX26">
+        <v>67</v>
+      </c>
+      <c r="DY26">
+        <v>62</v>
+      </c>
+      <c r="DZ26">
+        <v>62</v>
+      </c>
+      <c r="EA26">
+        <v>2</v>
+      </c>
+      <c r="EB26">
+        <v>95</v>
+      </c>
+      <c r="EC26">
+        <v>78</v>
+      </c>
+      <c r="ED26">
+        <v>36</v>
+      </c>
+      <c r="EE26">
+        <v>14.8</v>
+      </c>
+      <c r="EF26">
+        <v>14.9</v>
+      </c>
+      <c r="EG26">
+        <v>77</v>
+      </c>
+      <c r="EH26">
+        <v>70</v>
+      </c>
+      <c r="EI26">
+        <v>77</v>
+      </c>
+      <c r="EJ26">
+        <v>70</v>
+      </c>
     </row>
-    <row r="27" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -8603,8 +12311,143 @@
       <c r="CQ27">
         <v>38.5</v>
       </c>
+      <c r="CR27" s="1">
+        <v>75</v>
+      </c>
+      <c r="CS27" s="1">
+        <v>67</v>
+      </c>
+      <c r="CT27" s="1">
+        <v>32</v>
+      </c>
+      <c r="CU27" s="1">
+        <v>67</v>
+      </c>
+      <c r="CV27" s="1">
+        <v>71</v>
+      </c>
+      <c r="CW27" s="1">
+        <v>49</v>
+      </c>
+      <c r="CX27">
+        <v>60</v>
+      </c>
+      <c r="CY27">
+        <v>62</v>
+      </c>
+      <c r="CZ27">
+        <v>47</v>
+      </c>
+      <c r="DA27">
+        <v>59</v>
+      </c>
+      <c r="DB27">
+        <v>51</v>
+      </c>
+      <c r="DC27">
+        <v>69</v>
+      </c>
+      <c r="DD27">
+        <v>56</v>
+      </c>
+      <c r="DE27">
+        <v>63</v>
+      </c>
+      <c r="DF27">
+        <v>55</v>
+      </c>
+      <c r="DG27">
+        <v>65</v>
+      </c>
+      <c r="DH27">
+        <v>62</v>
+      </c>
+      <c r="DI27">
+        <v>80</v>
+      </c>
+      <c r="DJ27">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="DK27">
+        <v>68</v>
+      </c>
+      <c r="DL27">
+        <v>68</v>
+      </c>
+      <c r="DM27">
+        <v>81.2</v>
+      </c>
+      <c r="DN27">
+        <v>70</v>
+      </c>
+      <c r="DO27">
+        <v>-106.09999999999998</v>
+      </c>
+      <c r="DP27">
+        <v>50</v>
+      </c>
+      <c r="DQ27">
+        <v>64</v>
+      </c>
+      <c r="DR27">
+        <v>69</v>
+      </c>
+      <c r="DS27">
+        <v>60</v>
+      </c>
+      <c r="DT27">
+        <v>53</v>
+      </c>
+      <c r="DU27">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="DV27">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="DW27">
+        <v>72</v>
+      </c>
+      <c r="DX27">
+        <v>62</v>
+      </c>
+      <c r="DY27">
+        <v>62</v>
+      </c>
+      <c r="DZ27">
+        <v>64</v>
+      </c>
+      <c r="EA27">
+        <v>12</v>
+      </c>
+      <c r="EB27">
+        <v>82</v>
+      </c>
+      <c r="EC27">
+        <v>69</v>
+      </c>
+      <c r="ED27">
+        <v>63</v>
+      </c>
+      <c r="EE27">
+        <v>15.3</v>
+      </c>
+      <c r="EF27">
+        <v>10.9</v>
+      </c>
+      <c r="EG27">
+        <v>70</v>
+      </c>
+      <c r="EH27">
+        <v>64</v>
+      </c>
+      <c r="EI27">
+        <v>72</v>
+      </c>
+      <c r="EJ27">
+        <v>70</v>
+      </c>
     </row>
-    <row r="28" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -8890,8 +12733,143 @@
       <c r="CQ28">
         <v>39.700000000000003</v>
       </c>
+      <c r="CR28" s="1">
+        <v>82</v>
+      </c>
+      <c r="CS28" s="1">
+        <v>53</v>
+      </c>
+      <c r="CT28" s="1">
+        <v>20</v>
+      </c>
+      <c r="CU28" s="1">
+        <v>78</v>
+      </c>
+      <c r="CV28" s="1">
+        <v>87</v>
+      </c>
+      <c r="CW28" s="1">
+        <v>39</v>
+      </c>
+      <c r="CX28">
+        <v>53</v>
+      </c>
+      <c r="CY28">
+        <v>60</v>
+      </c>
+      <c r="CZ28">
+        <v>39</v>
+      </c>
+      <c r="DA28">
+        <v>48</v>
+      </c>
+      <c r="DB28">
+        <v>59</v>
+      </c>
+      <c r="DC28">
+        <v>61</v>
+      </c>
+      <c r="DD28">
+        <v>59</v>
+      </c>
+      <c r="DE28">
+        <v>49</v>
+      </c>
+      <c r="DF28">
+        <v>47</v>
+      </c>
+      <c r="DG28">
+        <v>69</v>
+      </c>
+      <c r="DH28">
+        <v>53</v>
+      </c>
+      <c r="DI28">
+        <v>87</v>
+      </c>
+      <c r="DJ28">
+        <v>47</v>
+      </c>
+      <c r="DK28">
+        <v>67</v>
+      </c>
+      <c r="DL28">
+        <v>67</v>
+      </c>
+      <c r="DM28">
+        <v>92.3</v>
+      </c>
+      <c r="DN28">
+        <v>86</v>
+      </c>
+      <c r="DO28">
+        <v>-62.500000000000014</v>
+      </c>
+      <c r="DP28">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="DQ28">
+        <v>68</v>
+      </c>
+      <c r="DR28">
+        <v>79</v>
+      </c>
+      <c r="DS28">
+        <v>77</v>
+      </c>
+      <c r="DT28">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="DU28">
+        <v>72</v>
+      </c>
+      <c r="DV28">
+        <v>64</v>
+      </c>
+      <c r="DW28">
+        <v>88</v>
+      </c>
+      <c r="DX28">
+        <v>66</v>
+      </c>
+      <c r="DY28">
+        <v>72</v>
+      </c>
+      <c r="DZ28">
+        <v>77</v>
+      </c>
+      <c r="EA28">
+        <v>6</v>
+      </c>
+      <c r="EB28">
+        <v>81</v>
+      </c>
+      <c r="EC28">
+        <v>60</v>
+      </c>
+      <c r="ED28">
+        <v>38</v>
+      </c>
+      <c r="EE28">
+        <v>13.2</v>
+      </c>
+      <c r="EF28">
+        <v>12.8</v>
+      </c>
+      <c r="EG28">
+        <v>71</v>
+      </c>
+      <c r="EH28">
+        <v>51</v>
+      </c>
+      <c r="EI28">
+        <v>77</v>
+      </c>
+      <c r="EJ28">
+        <v>56.999999999999993</v>
+      </c>
     </row>
-    <row r="29" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -9177,8 +13155,143 @@
       <c r="CQ29">
         <v>32.299999999999997</v>
       </c>
+      <c r="CR29" s="1">
+        <v>80</v>
+      </c>
+      <c r="CS29" s="1">
+        <v>59.000000000000007</v>
+      </c>
+      <c r="CT29" s="1">
+        <v>23</v>
+      </c>
+      <c r="CU29" s="1">
+        <v>75</v>
+      </c>
+      <c r="CV29" s="1">
+        <v>77.999999999999986</v>
+      </c>
+      <c r="CW29" s="1">
+        <v>54</v>
+      </c>
+      <c r="CX29">
+        <v>64</v>
+      </c>
+      <c r="CY29">
+        <v>62</v>
+      </c>
+      <c r="CZ29">
+        <v>44.999999999999993</v>
+      </c>
+      <c r="DA29">
+        <v>69</v>
+      </c>
+      <c r="DB29">
+        <v>58</v>
+      </c>
+      <c r="DC29">
+        <v>84</v>
+      </c>
+      <c r="DD29">
+        <v>64</v>
+      </c>
+      <c r="DE29">
+        <v>71</v>
+      </c>
+      <c r="DF29">
+        <v>62</v>
+      </c>
+      <c r="DG29">
+        <v>71</v>
+      </c>
+      <c r="DH29">
+        <v>72</v>
+      </c>
+      <c r="DI29">
+        <v>81</v>
+      </c>
+      <c r="DJ29">
+        <v>53</v>
+      </c>
+      <c r="DK29">
+        <v>59</v>
+      </c>
+      <c r="DL29">
+        <v>66</v>
+      </c>
+      <c r="DM29">
+        <v>89.1</v>
+      </c>
+      <c r="DN29">
+        <v>86</v>
+      </c>
+      <c r="DO29">
+        <v>-127.29999999999998</v>
+      </c>
+      <c r="DP29">
+        <v>62</v>
+      </c>
+      <c r="DQ29">
+        <v>70</v>
+      </c>
+      <c r="DR29">
+        <v>77</v>
+      </c>
+      <c r="DS29">
+        <v>70</v>
+      </c>
+      <c r="DT29">
+        <v>48</v>
+      </c>
+      <c r="DU29">
+        <v>68</v>
+      </c>
+      <c r="DV29">
+        <v>49</v>
+      </c>
+      <c r="DW29">
+        <v>92</v>
+      </c>
+      <c r="DX29">
+        <v>72</v>
+      </c>
+      <c r="DY29">
+        <v>71</v>
+      </c>
+      <c r="DZ29">
+        <v>74</v>
+      </c>
+      <c r="EA29">
+        <v>9</v>
+      </c>
+      <c r="EB29">
+        <v>87</v>
+      </c>
+      <c r="EC29">
+        <v>74</v>
+      </c>
+      <c r="ED29">
+        <v>52</v>
+      </c>
+      <c r="EE29">
+        <v>17.8</v>
+      </c>
+      <c r="EF29">
+        <v>17.5</v>
+      </c>
+      <c r="EG29">
+        <v>69</v>
+      </c>
+      <c r="EH29">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="EI29">
+        <v>73</v>
+      </c>
+      <c r="EJ29">
+        <v>52</v>
+      </c>
     </row>
-    <row r="30" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -9464,8 +13577,143 @@
       <c r="CQ30">
         <v>39</v>
       </c>
+      <c r="CR30" s="1">
+        <v>83</v>
+      </c>
+      <c r="CS30" s="1">
+        <v>48.000000000000007</v>
+      </c>
+      <c r="CT30" s="1">
+        <v>17</v>
+      </c>
+      <c r="CU30" s="1">
+        <v>57.000000000000007</v>
+      </c>
+      <c r="CV30" s="1">
+        <v>64</v>
+      </c>
+      <c r="CW30" s="1">
+        <v>40</v>
+      </c>
+      <c r="CX30">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="CY30">
+        <v>47</v>
+      </c>
+      <c r="CZ30">
+        <v>28</v>
+      </c>
+      <c r="DA30">
+        <v>61</v>
+      </c>
+      <c r="DB30">
+        <v>51</v>
+      </c>
+      <c r="DC30">
+        <v>73</v>
+      </c>
+      <c r="DD30">
+        <v>58</v>
+      </c>
+      <c r="DE30">
+        <v>52</v>
+      </c>
+      <c r="DF30">
+        <v>69</v>
+      </c>
+      <c r="DG30">
+        <v>79</v>
+      </c>
+      <c r="DH30">
+        <v>68</v>
+      </c>
+      <c r="DI30">
+        <v>81</v>
+      </c>
+      <c r="DJ30">
+        <v>71</v>
+      </c>
+      <c r="DK30">
+        <v>78</v>
+      </c>
+      <c r="DL30">
+        <v>72</v>
+      </c>
+      <c r="DM30">
+        <v>88.6</v>
+      </c>
+      <c r="DN30">
+        <v>92</v>
+      </c>
+      <c r="DO30">
+        <v>-44.499999999999986</v>
+      </c>
+      <c r="DP30">
+        <v>67</v>
+      </c>
+      <c r="DQ30">
+        <v>67</v>
+      </c>
+      <c r="DR30">
+        <v>82</v>
+      </c>
+      <c r="DS30">
+        <v>73</v>
+      </c>
+      <c r="DT30">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="DU30">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="DV30">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="DW30">
+        <v>94</v>
+      </c>
+      <c r="DX30">
+        <v>48</v>
+      </c>
+      <c r="DY30">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="DZ30">
+        <v>82</v>
+      </c>
+      <c r="EA30">
+        <v>6</v>
+      </c>
+      <c r="EB30">
+        <v>92</v>
+      </c>
+      <c r="EC30">
+        <v>66</v>
+      </c>
+      <c r="ED30">
+        <v>38</v>
+      </c>
+      <c r="EE30">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="EF30">
+        <v>10.3</v>
+      </c>
+      <c r="EG30">
+        <v>92</v>
+      </c>
+      <c r="EH30">
+        <v>76</v>
+      </c>
+      <c r="EI30">
+        <v>79</v>
+      </c>
+      <c r="EJ30">
+        <v>83</v>
+      </c>
     </row>
-    <row r="31" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:140" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -9751,8 +13999,143 @@
       <c r="CQ31">
         <v>38.200000000000003</v>
       </c>
+      <c r="CR31" s="1">
+        <v>65</v>
+      </c>
+      <c r="CS31" s="1">
+        <v>38</v>
+      </c>
+      <c r="CT31" s="1">
+        <v>44</v>
+      </c>
+      <c r="CU31" s="1">
+        <v>42.000000000000007</v>
+      </c>
+      <c r="CV31" s="1">
+        <v>47</v>
+      </c>
+      <c r="CW31" s="1">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="CX31">
+        <v>27</v>
+      </c>
+      <c r="CY31">
+        <v>30</v>
+      </c>
+      <c r="CZ31">
+        <v>22</v>
+      </c>
+      <c r="DA31">
+        <v>54</v>
+      </c>
+      <c r="DB31">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="DC31">
+        <v>42.000000000000007</v>
+      </c>
+      <c r="DD31">
+        <v>35</v>
+      </c>
+      <c r="DE31">
+        <v>32</v>
+      </c>
+      <c r="DF31">
+        <v>42.000000000000007</v>
+      </c>
+      <c r="DG31">
+        <v>50</v>
+      </c>
+      <c r="DH31">
+        <v>58</v>
+      </c>
+      <c r="DI31">
+        <v>72</v>
+      </c>
+      <c r="DJ31">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="DK31">
+        <v>73</v>
+      </c>
+      <c r="DL31">
+        <v>72</v>
+      </c>
+      <c r="DM31">
+        <v>88.8</v>
+      </c>
+      <c r="DN31">
+        <v>91</v>
+      </c>
+      <c r="DO31">
+        <v>3.2000000000000028</v>
+      </c>
+      <c r="DP31">
+        <v>69</v>
+      </c>
+      <c r="DQ31">
+        <v>54</v>
+      </c>
+      <c r="DR31">
+        <v>64</v>
+      </c>
+      <c r="DS31">
+        <v>78</v>
+      </c>
+      <c r="DT31">
+        <v>76</v>
+      </c>
+      <c r="DU31">
+        <v>64</v>
+      </c>
+      <c r="DV31">
+        <v>61</v>
+      </c>
+      <c r="DW31">
+        <v>90</v>
+      </c>
+      <c r="DX31">
+        <v>48</v>
+      </c>
+      <c r="DY31">
+        <v>64</v>
+      </c>
+      <c r="DZ31">
+        <v>85</v>
+      </c>
+      <c r="EA31">
+        <v>6.0000000000000009</v>
+      </c>
+      <c r="EB31">
+        <v>95</v>
+      </c>
+      <c r="EC31">
+        <v>83</v>
+      </c>
+      <c r="ED31">
+        <v>66</v>
+      </c>
+      <c r="EE31">
+        <v>14.3</v>
+      </c>
+      <c r="EF31">
+        <v>11.1</v>
+      </c>
+      <c r="EG31">
+        <v>82</v>
+      </c>
+      <c r="EH31">
+        <v>68</v>
+      </c>
+      <c r="EI31">
+        <v>78</v>
+      </c>
+      <c r="EJ31">
+        <v>76</v>
+      </c>
     </row>
-    <row r="32" spans="1:95" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:140" x14ac:dyDescent="0.25">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -9783,145 +14166,30 @@
       <c r="AL32" s="1"/>
       <c r="AM32" s="1"/>
     </row>
-    <row r="36" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-    </row>
-    <row r="38" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-    </row>
-    <row r="39" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-    </row>
-    <row r="40" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-    </row>
-    <row r="41" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-    </row>
-    <row r="43" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-    </row>
-    <row r="44" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-    </row>
-    <row r="45" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-    </row>
-    <row r="46" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-    </row>
-    <row r="47" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-    </row>
-    <row r="48" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-    </row>
-    <row r="49" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-    </row>
-    <row r="50" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-    </row>
-    <row r="51" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-    </row>
-    <row r="52" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-    </row>
-    <row r="53" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-    </row>
-    <row r="54" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-    </row>
-    <row r="55" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-    </row>
-    <row r="56" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-    </row>
-    <row r="57" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-    </row>
-    <row r="58" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-    </row>
-    <row r="59" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-    </row>
-    <row r="60" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-    </row>
-    <row r="61" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-    </row>
-    <row r="62" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-    </row>
-    <row r="63" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
+    <row r="41" spans="50:72" x14ac:dyDescent="0.25">
+      <c r="AX41" s="2"/>
+      <c r="AY41" s="2"/>
+      <c r="AZ41" s="2"/>
+      <c r="BA41" s="2"/>
+      <c r="BB41" s="2"/>
+      <c r="BC41" s="2"/>
+      <c r="BD41" s="2"/>
+      <c r="BE41" s="2"/>
+      <c r="BF41" s="2"/>
+      <c r="BG41" s="2"/>
+      <c r="BH41" s="2"/>
+      <c r="BI41" s="2"/>
+      <c r="BJ41" s="2"/>
+      <c r="BK41" s="2"/>
+      <c r="BL41" s="2"/>
+      <c r="BM41" s="2"/>
+      <c r="BN41" s="2"/>
+      <c r="BO41" s="2"/>
+      <c r="BP41" s="2"/>
+      <c r="BQ41" s="2"/>
+      <c r="BR41" s="2"/>
+      <c r="BS41" s="2"/>
+      <c r="BT41" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SC Indicators Data Prep.xlsx
+++ b/SC Indicators Data Prep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emree\CO3data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C42EA00B-A49B-4BFB-802F-390B628688E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64381B89-32B7-48E3-B562-AF1C048EBA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{55AA29CC-CDDC-4D64-AC5C-6644C21888DE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="232">
   <si>
     <t>Voted</t>
   </si>
@@ -636,6 +636,102 @@
   </si>
   <si>
     <t>Defense Policy</t>
+  </si>
+  <si>
+    <t>COVID19 Measures- National Government-Total 'Satisfied'</t>
+  </si>
+  <si>
+    <t>COVID19 Measures- the EU-Total 'Satisfied'</t>
+  </si>
+  <si>
+    <t>COVID19</t>
+  </si>
+  <si>
+    <t>Support for -A common European Asylum system</t>
+  </si>
+  <si>
+    <t>Support for -A reinforcement of EU external borders</t>
+  </si>
+  <si>
+    <t>Immigration</t>
+  </si>
+  <si>
+    <t>Immigration of people from other EU Member StatesğTotal 'Positive'</t>
+  </si>
+  <si>
+    <t>Immigration of people from outside the EU- Total 'Positive'</t>
+  </si>
+  <si>
+    <t>Immigrants contribute positively to (OUR COUNTRY)- Total 'Agree'</t>
+  </si>
+  <si>
+    <t>(OUR COUNTRY) should help refugees- Total 'Agree'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> You often come across disinformation- Total 'Disagree'</t>
+  </si>
+  <si>
+    <t>It is easy for you to identify disinformation- Total 'Agree'</t>
+  </si>
+  <si>
+    <t>The rapid spread of disinformation is a major problem for democracy- Total 'Agree'</t>
+  </si>
+  <si>
+    <t>Disinformation</t>
+  </si>
+  <si>
+    <t>Climate change- Total Satisfied</t>
+  </si>
+  <si>
+    <t>The economic and financial situation- - Total Satisfied</t>
+  </si>
+  <si>
+    <t>Russia's invasion of Ukraine - - Total Satisfied</t>
+  </si>
+  <si>
+    <t>Migration - - Total Satisfied</t>
+  </si>
+  <si>
+    <t>Brexit - - Total Satisfied</t>
+  </si>
+  <si>
+    <t>EU Response's Effectiveness</t>
+  </si>
+  <si>
+    <t>Managing health emergencies (e.g. COVID-19 pandemic, epidemics)- Total 'Effective'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Providing relief for large natural disasters (e.g. floods, wildfires, earthquakes)- Total 'Effective'</t>
+  </si>
+  <si>
+    <t>Dealing with the impact on the EU of violent conflicts (e.g. Russia’s war of aggression against Ukraine)- Total 'Effective'</t>
+  </si>
+  <si>
+    <t>strength of the EU’s democracy in the next five years?- Total 'Confident'</t>
+  </si>
+  <si>
+    <t>the performance of the EU’s economy in the next five years- Total 'Confident'</t>
+  </si>
+  <si>
+    <t>the EU’s security in the next five years?- Total 'Confident'</t>
+  </si>
+  <si>
+    <t>Confidence in the EU</t>
+  </si>
+  <si>
+    <t>(Youth) exposed to disinformation and fake news- Rarely &amp; Never</t>
+  </si>
+  <si>
+    <t>(Youth) You can recognise disinformation when you encounter it -Total 'Confident'</t>
+  </si>
+  <si>
+    <t>Awareness about the EU Response</t>
+  </si>
+  <si>
+    <t>EU Response</t>
+  </si>
+  <si>
+    <t>Resilience to Crises</t>
   </si>
 </sst>
 </file>
@@ -1050,10 +1146,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA6585B-C499-45AD-87BE-134F9272F3A6}">
-  <dimension ref="A1:EJ41"/>
+  <dimension ref="A1:FI41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>122</v>
       </c>
@@ -1474,8 +1570,83 @@
       <c r="EJ1" t="s">
         <v>198</v>
       </c>
+      <c r="EK1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EL1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EM1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EN1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EO1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EP1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EQ1" t="s">
+        <v>231</v>
+      </c>
+      <c r="ER1" t="s">
+        <v>231</v>
+      </c>
+      <c r="ES1" t="s">
+        <v>231</v>
+      </c>
+      <c r="ET1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EV1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EW1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EX1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EY1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EZ1" t="s">
+        <v>231</v>
+      </c>
+      <c r="FA1" t="s">
+        <v>231</v>
+      </c>
+      <c r="FB1" t="s">
+        <v>231</v>
+      </c>
+      <c r="FC1" t="s">
+        <v>231</v>
+      </c>
+      <c r="FD1" t="s">
+        <v>231</v>
+      </c>
+      <c r="FE1" t="s">
+        <v>231</v>
+      </c>
+      <c r="FF1" t="s">
+        <v>231</v>
+      </c>
+      <c r="FG1" t="s">
+        <v>231</v>
+      </c>
+      <c r="FH1" t="s">
+        <v>231</v>
+      </c>
+      <c r="FI1" t="s">
+        <v>231</v>
+      </c>
     </row>
-    <row r="2" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -1896,8 +2067,83 @@
       <c r="EJ2" t="s">
         <v>199</v>
       </c>
+      <c r="EK2" t="s">
+        <v>202</v>
+      </c>
+      <c r="EL2" t="s">
+        <v>202</v>
+      </c>
+      <c r="EM2" t="s">
+        <v>205</v>
+      </c>
+      <c r="EN2" t="s">
+        <v>205</v>
+      </c>
+      <c r="EO2" t="s">
+        <v>205</v>
+      </c>
+      <c r="EP2" t="s">
+        <v>205</v>
+      </c>
+      <c r="EQ2" t="s">
+        <v>205</v>
+      </c>
+      <c r="ER2" t="s">
+        <v>205</v>
+      </c>
+      <c r="ES2" t="s">
+        <v>213</v>
+      </c>
+      <c r="ET2" t="s">
+        <v>213</v>
+      </c>
+      <c r="EU2" t="s">
+        <v>213</v>
+      </c>
+      <c r="EV2" t="s">
+        <v>219</v>
+      </c>
+      <c r="EW2" t="s">
+        <v>219</v>
+      </c>
+      <c r="EX2" t="s">
+        <v>219</v>
+      </c>
+      <c r="EY2" t="s">
+        <v>219</v>
+      </c>
+      <c r="EZ2" t="s">
+        <v>219</v>
+      </c>
+      <c r="FA2" t="s">
+        <v>230</v>
+      </c>
+      <c r="FB2" t="s">
+        <v>219</v>
+      </c>
+      <c r="FC2" t="s">
+        <v>219</v>
+      </c>
+      <c r="FD2" t="s">
+        <v>219</v>
+      </c>
+      <c r="FE2" t="s">
+        <v>226</v>
+      </c>
+      <c r="FF2" t="s">
+        <v>226</v>
+      </c>
+      <c r="FG2" t="s">
+        <v>226</v>
+      </c>
+      <c r="FH2" t="s">
+        <v>213</v>
+      </c>
+      <c r="FI2" t="s">
+        <v>213</v>
+      </c>
     </row>
-    <row r="3" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -2318,8 +2564,83 @@
       <c r="EJ3" t="s">
         <v>183</v>
       </c>
+      <c r="EK3" t="s">
+        <v>200</v>
+      </c>
+      <c r="EL3" t="s">
+        <v>201</v>
+      </c>
+      <c r="EM3" t="s">
+        <v>203</v>
+      </c>
+      <c r="EN3" t="s">
+        <v>204</v>
+      </c>
+      <c r="EO3" t="s">
+        <v>206</v>
+      </c>
+      <c r="EP3" t="s">
+        <v>207</v>
+      </c>
+      <c r="EQ3" t="s">
+        <v>208</v>
+      </c>
+      <c r="ER3" t="s">
+        <v>209</v>
+      </c>
+      <c r="ES3" t="s">
+        <v>210</v>
+      </c>
+      <c r="ET3" t="s">
+        <v>211</v>
+      </c>
+      <c r="EU3" t="s">
+        <v>212</v>
+      </c>
+      <c r="EV3" t="s">
+        <v>214</v>
+      </c>
+      <c r="EW3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EX3" t="s">
+        <v>216</v>
+      </c>
+      <c r="EY3" t="s">
+        <v>217</v>
+      </c>
+      <c r="EZ3" t="s">
+        <v>218</v>
+      </c>
+      <c r="FA3" t="s">
+        <v>229</v>
+      </c>
+      <c r="FB3" t="s">
+        <v>220</v>
+      </c>
+      <c r="FC3" t="s">
+        <v>221</v>
+      </c>
+      <c r="FD3" t="s">
+        <v>222</v>
+      </c>
+      <c r="FE3" t="s">
+        <v>223</v>
+      </c>
+      <c r="FF3" t="s">
+        <v>224</v>
+      </c>
+      <c r="FG3" t="s">
+        <v>225</v>
+      </c>
+      <c r="FH3" t="s">
+        <v>227</v>
+      </c>
+      <c r="FI3" t="s">
+        <v>228</v>
+      </c>
     </row>
-    <row r="4" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -2740,8 +3061,83 @@
       <c r="EJ4">
         <v>71</v>
       </c>
+      <c r="EK4">
+        <v>49</v>
+      </c>
+      <c r="EL4">
+        <v>46</v>
+      </c>
+      <c r="EM4">
+        <v>65</v>
+      </c>
+      <c r="EN4">
+        <v>75</v>
+      </c>
+      <c r="EO4">
+        <v>68</v>
+      </c>
+      <c r="EP4">
+        <v>46</v>
+      </c>
+      <c r="EQ4">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="ER4">
+        <v>75</v>
+      </c>
+      <c r="ES4">
+        <v>25</v>
+      </c>
+      <c r="ET4">
+        <v>61</v>
+      </c>
+      <c r="EU4">
+        <v>86</v>
+      </c>
+      <c r="EV4">
+        <v>33</v>
+      </c>
+      <c r="EW4">
+        <v>37</v>
+      </c>
+      <c r="EX4">
+        <v>36</v>
+      </c>
+      <c r="EY4">
+        <v>24</v>
+      </c>
+      <c r="EZ4">
+        <v>38</v>
+      </c>
+      <c r="FA4">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="FB4">
+        <v>61.3</v>
+      </c>
+      <c r="FC4">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="FD4">
+        <v>47.4</v>
+      </c>
+      <c r="FE4">
+        <v>55.2</v>
+      </c>
+      <c r="FF4">
+        <v>50.5</v>
+      </c>
+      <c r="FG4">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="FH4">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="FI4">
+        <v>70</v>
+      </c>
     </row>
-    <row r="5" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -3162,8 +3558,83 @@
       <c r="EJ5">
         <v>75</v>
       </c>
+      <c r="EK5">
+        <v>65</v>
+      </c>
+      <c r="EL5">
+        <v>59</v>
+      </c>
+      <c r="EM5">
+        <v>71</v>
+      </c>
+      <c r="EN5">
+        <v>70</v>
+      </c>
+      <c r="EO5">
+        <v>64</v>
+      </c>
+      <c r="EP5">
+        <v>48</v>
+      </c>
+      <c r="EQ5">
+        <v>51</v>
+      </c>
+      <c r="ER5">
+        <v>69</v>
+      </c>
+      <c r="ES5">
+        <v>32</v>
+      </c>
+      <c r="ET5">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="EU5">
+        <v>85</v>
+      </c>
+      <c r="EV5">
+        <v>38</v>
+      </c>
+      <c r="EW5">
+        <v>43</v>
+      </c>
+      <c r="EX5">
+        <v>46</v>
+      </c>
+      <c r="EY5">
+        <v>32</v>
+      </c>
+      <c r="EZ5">
+        <v>49</v>
+      </c>
+      <c r="FA5">
+        <v>25.8</v>
+      </c>
+      <c r="FB5">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="FC5">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="FD5">
+        <v>48.3</v>
+      </c>
+      <c r="FE5">
+        <v>50.2</v>
+      </c>
+      <c r="FF5">
+        <v>43.8</v>
+      </c>
+      <c r="FG5">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="FH5">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="FI5">
+        <v>78.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -3584,8 +4055,83 @@
       <c r="EJ6">
         <v>53</v>
       </c>
+      <c r="EK6">
+        <v>38</v>
+      </c>
+      <c r="EL6">
+        <v>44</v>
+      </c>
+      <c r="EM6">
+        <v>54</v>
+      </c>
+      <c r="EN6">
+        <v>80</v>
+      </c>
+      <c r="EO6">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="EP6">
+        <v>28.999999999999996</v>
+      </c>
+      <c r="EQ6">
+        <v>27</v>
+      </c>
+      <c r="ER6">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="ES6">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="ET6">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="EU6">
+        <v>82</v>
+      </c>
+      <c r="EV6">
+        <v>37</v>
+      </c>
+      <c r="EW6">
+        <v>35</v>
+      </c>
+      <c r="EX6">
+        <v>28.999999999999996</v>
+      </c>
+      <c r="EY6">
+        <v>28.999999999999996</v>
+      </c>
+      <c r="EZ6">
+        <v>32</v>
+      </c>
+      <c r="FA6">
+        <v>37.6</v>
+      </c>
+      <c r="FB6">
+        <v>56.5</v>
+      </c>
+      <c r="FC6">
+        <v>61.8</v>
+      </c>
+      <c r="FD6">
+        <v>43.3</v>
+      </c>
+      <c r="FE6">
+        <v>52</v>
+      </c>
+      <c r="FF6">
+        <v>54.2</v>
+      </c>
+      <c r="FG6">
+        <v>62.8</v>
+      </c>
+      <c r="FH6">
+        <v>21.5</v>
+      </c>
+      <c r="FI6">
+        <v>85.1</v>
+      </c>
     </row>
-    <row r="7" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4006,8 +4552,83 @@
       <c r="EJ7">
         <v>62</v>
       </c>
+      <c r="EK7">
+        <v>40</v>
+      </c>
+      <c r="EL7">
+        <v>39</v>
+      </c>
+      <c r="EM7">
+        <v>36</v>
+      </c>
+      <c r="EN7">
+        <v>82</v>
+      </c>
+      <c r="EO7">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="EP7">
+        <v>21</v>
+      </c>
+      <c r="EQ7">
+        <v>34</v>
+      </c>
+      <c r="ER7">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="ES7">
+        <v>27</v>
+      </c>
+      <c r="ET7">
+        <v>59</v>
+      </c>
+      <c r="EU7">
+        <v>59</v>
+      </c>
+      <c r="EV7">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="EW7">
+        <v>27</v>
+      </c>
+      <c r="EX7">
+        <v>35</v>
+      </c>
+      <c r="EY7">
+        <v>15</v>
+      </c>
+      <c r="EZ7">
+        <v>42</v>
+      </c>
+      <c r="FA7">
+        <v>29.9</v>
+      </c>
+      <c r="FB7">
+        <v>54.1</v>
+      </c>
+      <c r="FC7">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="FD7">
+        <v>48.7</v>
+      </c>
+      <c r="FE7">
+        <v>46.2</v>
+      </c>
+      <c r="FF7">
+        <v>45.2</v>
+      </c>
+      <c r="FG7">
+        <v>68.5</v>
+      </c>
+      <c r="FH7">
+        <v>28.4</v>
+      </c>
+      <c r="FI7">
+        <v>72.3</v>
+      </c>
     </row>
-    <row r="8" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -4428,8 +5049,83 @@
       <c r="EJ8">
         <v>87</v>
       </c>
+      <c r="EK8">
+        <v>81</v>
+      </c>
+      <c r="EL8">
+        <v>67</v>
+      </c>
+      <c r="EM8">
+        <v>72</v>
+      </c>
+      <c r="EN8">
+        <v>68</v>
+      </c>
+      <c r="EO8">
+        <v>82</v>
+      </c>
+      <c r="EP8">
+        <v>45</v>
+      </c>
+      <c r="EQ8">
+        <v>74</v>
+      </c>
+      <c r="ER8">
+        <v>92</v>
+      </c>
+      <c r="ES8">
+        <v>31</v>
+      </c>
+      <c r="ET8">
+        <v>67</v>
+      </c>
+      <c r="EU8">
+        <v>89</v>
+      </c>
+      <c r="EV8">
+        <v>42</v>
+      </c>
+      <c r="EW8">
+        <v>68</v>
+      </c>
+      <c r="EX8">
+        <v>65</v>
+      </c>
+      <c r="EY8">
+        <v>43</v>
+      </c>
+      <c r="EZ8">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="FA8">
+        <v>29.5</v>
+      </c>
+      <c r="FB8">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="FC8">
+        <v>65.8</v>
+      </c>
+      <c r="FD8">
+        <v>57.6</v>
+      </c>
+      <c r="FE8">
+        <v>62.5</v>
+      </c>
+      <c r="FF8">
+        <v>56.2</v>
+      </c>
+      <c r="FG8">
+        <v>62.8</v>
+      </c>
+      <c r="FH8">
+        <v>18.5</v>
+      </c>
+      <c r="FI8">
+        <v>71.3</v>
+      </c>
     </row>
-    <row r="9" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -4850,8 +5546,83 @@
       <c r="EJ9">
         <v>71</v>
       </c>
+      <c r="EK9">
+        <v>52</v>
+      </c>
+      <c r="EL9">
+        <v>39</v>
+      </c>
+      <c r="EM9">
+        <v>75</v>
+      </c>
+      <c r="EN9">
+        <v>75</v>
+      </c>
+      <c r="EO9">
+        <v>68</v>
+      </c>
+      <c r="EP9">
+        <v>40</v>
+      </c>
+      <c r="EQ9">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="ER9">
+        <v>76</v>
+      </c>
+      <c r="ES9">
+        <v>34</v>
+      </c>
+      <c r="ET9">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="EU9">
+        <v>84</v>
+      </c>
+      <c r="EV9">
+        <v>28.999999999999996</v>
+      </c>
+      <c r="EW9">
+        <v>39</v>
+      </c>
+      <c r="EX9">
+        <v>32</v>
+      </c>
+      <c r="EY9">
+        <v>19</v>
+      </c>
+      <c r="EZ9">
+        <v>43</v>
+      </c>
+      <c r="FA9">
+        <v>36</v>
+      </c>
+      <c r="FB9">
+        <v>51.9</v>
+      </c>
+      <c r="FC9">
+        <v>62.9</v>
+      </c>
+      <c r="FD9">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="FE9">
+        <v>58.2</v>
+      </c>
+      <c r="FF9">
+        <v>51.3</v>
+      </c>
+      <c r="FG9">
+        <v>57.5</v>
+      </c>
+      <c r="FH9">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="FI9">
+        <v>62.6</v>
+      </c>
     </row>
-    <row r="10" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -5272,8 +6043,83 @@
       <c r="EJ10">
         <v>70</v>
       </c>
+      <c r="EK10">
+        <v>45</v>
+      </c>
+      <c r="EL10">
+        <v>34</v>
+      </c>
+      <c r="EM10">
+        <v>43</v>
+      </c>
+      <c r="EN10">
+        <v>77</v>
+      </c>
+      <c r="EO10">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="EP10">
+        <v>20</v>
+      </c>
+      <c r="EQ10">
+        <v>28.999999999999996</v>
+      </c>
+      <c r="ER10">
+        <v>60</v>
+      </c>
+      <c r="ES10">
+        <v>36</v>
+      </c>
+      <c r="ET10">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="EU10">
+        <v>85</v>
+      </c>
+      <c r="EV10">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="EW10">
+        <v>26</v>
+      </c>
+      <c r="EX10">
+        <v>34</v>
+      </c>
+      <c r="EY10">
+        <v>23</v>
+      </c>
+      <c r="EZ10">
+        <v>33</v>
+      </c>
+      <c r="FA10">
+        <v>24.7</v>
+      </c>
+      <c r="FB10">
+        <v>57.9</v>
+      </c>
+      <c r="FC10">
+        <v>60.3</v>
+      </c>
+      <c r="FD10">
+        <v>46.6</v>
+      </c>
+      <c r="FE10">
+        <v>54.5</v>
+      </c>
+      <c r="FF10">
+        <v>43.6</v>
+      </c>
+      <c r="FG10">
+        <v>64.3</v>
+      </c>
+      <c r="FH10">
+        <v>32.6</v>
+      </c>
+      <c r="FI10">
+        <v>73.900000000000006</v>
+      </c>
     </row>
-    <row r="11" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -5694,8 +6540,83 @@
       <c r="EJ11">
         <v>72</v>
       </c>
+      <c r="EK11">
+        <v>82</v>
+      </c>
+      <c r="EL11">
+        <v>81</v>
+      </c>
+      <c r="EM11">
+        <v>66</v>
+      </c>
+      <c r="EN11">
+        <v>78</v>
+      </c>
+      <c r="EO11">
+        <v>82</v>
+      </c>
+      <c r="EP11">
+        <v>64</v>
+      </c>
+      <c r="EQ11">
+        <v>78</v>
+      </c>
+      <c r="ER11">
+        <v>81</v>
+      </c>
+      <c r="ES11">
+        <v>18</v>
+      </c>
+      <c r="ET11">
+        <v>67</v>
+      </c>
+      <c r="EU11">
+        <v>83</v>
+      </c>
+      <c r="EV11">
+        <v>48</v>
+      </c>
+      <c r="EW11">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="EX11">
+        <v>42</v>
+      </c>
+      <c r="EY11">
+        <v>37</v>
+      </c>
+      <c r="EZ11">
+        <v>53</v>
+      </c>
+      <c r="FA11">
+        <v>51.5</v>
+      </c>
+      <c r="FB11">
+        <v>76.3</v>
+      </c>
+      <c r="FC11">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="FD11">
+        <v>61.3</v>
+      </c>
+      <c r="FE11">
+        <v>68.8</v>
+      </c>
+      <c r="FF11">
+        <v>66.3</v>
+      </c>
+      <c r="FG11">
+        <v>67.2</v>
+      </c>
+      <c r="FH11">
+        <v>28.3</v>
+      </c>
+      <c r="FI11">
+        <v>86.8</v>
+      </c>
     </row>
-    <row r="12" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -6116,8 +7037,83 @@
       <c r="EJ12">
         <v>70</v>
       </c>
+      <c r="EK12">
+        <v>34</v>
+      </c>
+      <c r="EL12">
+        <v>33</v>
+      </c>
+      <c r="EM12">
+        <v>78</v>
+      </c>
+      <c r="EN12">
+        <v>88</v>
+      </c>
+      <c r="EO12">
+        <v>63</v>
+      </c>
+      <c r="EP12">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="EQ12">
+        <v>38</v>
+      </c>
+      <c r="ER12">
+        <v>80</v>
+      </c>
+      <c r="ES12">
+        <v>6</v>
+      </c>
+      <c r="ET12">
+        <v>64</v>
+      </c>
+      <c r="EU12">
+        <v>91</v>
+      </c>
+      <c r="EV12">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="EW12">
+        <v>16</v>
+      </c>
+      <c r="EX12">
+        <v>30</v>
+      </c>
+      <c r="EY12">
+        <v>14.000000000000002</v>
+      </c>
+      <c r="EZ12">
+        <v>35</v>
+      </c>
+      <c r="FA12">
+        <v>42.2</v>
+      </c>
+      <c r="FB12">
+        <v>62</v>
+      </c>
+      <c r="FC12">
+        <v>62.8</v>
+      </c>
+      <c r="FD12">
+        <v>46.7</v>
+      </c>
+      <c r="FE12">
+        <v>48.9</v>
+      </c>
+      <c r="FF12">
+        <v>40.4</v>
+      </c>
+      <c r="FG12">
+        <v>66</v>
+      </c>
+      <c r="FH12">
+        <v>15.100000000000001</v>
+      </c>
+      <c r="FI12">
+        <v>69.5</v>
+      </c>
     </row>
-    <row r="13" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -6538,8 +7534,83 @@
       <c r="EJ13">
         <v>70</v>
       </c>
+      <c r="EK13">
+        <v>42</v>
+      </c>
+      <c r="EL13">
+        <v>46</v>
+      </c>
+      <c r="EM13">
+        <v>80</v>
+      </c>
+      <c r="EN13">
+        <v>71</v>
+      </c>
+      <c r="EO13">
+        <v>80</v>
+      </c>
+      <c r="EP13">
+        <v>66</v>
+      </c>
+      <c r="EQ13">
+        <v>73</v>
+      </c>
+      <c r="ER13">
+        <v>91</v>
+      </c>
+      <c r="ES13">
+        <v>13</v>
+      </c>
+      <c r="ET13">
+        <v>62</v>
+      </c>
+      <c r="EU13">
+        <v>91</v>
+      </c>
+      <c r="EV13">
+        <v>26</v>
+      </c>
+      <c r="EW13">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="EX13">
+        <v>27</v>
+      </c>
+      <c r="EY13">
+        <v>20</v>
+      </c>
+      <c r="EZ13">
+        <v>27</v>
+      </c>
+      <c r="FA13">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="FB13">
+        <v>66.8</v>
+      </c>
+      <c r="FC13">
+        <v>69</v>
+      </c>
+      <c r="FD13">
+        <v>49.7</v>
+      </c>
+      <c r="FE13">
+        <v>51.5</v>
+      </c>
+      <c r="FF13">
+        <v>46.1</v>
+      </c>
+      <c r="FG13">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="FH13">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="FI13">
+        <v>65.900000000000006</v>
+      </c>
     </row>
-    <row r="14" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -6960,8 +8031,83 @@
       <c r="EJ14">
         <v>68</v>
       </c>
+      <c r="EK14">
+        <v>52</v>
+      </c>
+      <c r="EL14">
+        <v>41</v>
+      </c>
+      <c r="EM14">
+        <v>52</v>
+      </c>
+      <c r="EN14">
+        <v>71</v>
+      </c>
+      <c r="EO14">
+        <v>61</v>
+      </c>
+      <c r="EP14">
+        <v>42</v>
+      </c>
+      <c r="EQ14">
+        <v>51</v>
+      </c>
+      <c r="ER14">
+        <v>66</v>
+      </c>
+      <c r="ES14">
+        <v>28.999999999999996</v>
+      </c>
+      <c r="ET14">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="EU14">
+        <v>88</v>
+      </c>
+      <c r="EV14">
+        <v>23</v>
+      </c>
+      <c r="EW14">
+        <v>24</v>
+      </c>
+      <c r="EX14">
+        <v>34</v>
+      </c>
+      <c r="EY14">
+        <v>18</v>
+      </c>
+      <c r="EZ14">
+        <v>31</v>
+      </c>
+      <c r="FA14">
+        <v>23</v>
+      </c>
+      <c r="FB14">
+        <v>62.5</v>
+      </c>
+      <c r="FC14">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="FD14">
+        <v>44.2</v>
+      </c>
+      <c r="FE14">
+        <v>46.9</v>
+      </c>
+      <c r="FF14">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="FG14">
+        <v>70.7</v>
+      </c>
+      <c r="FH14">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="FI14">
+        <v>72.5</v>
+      </c>
     </row>
-    <row r="15" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -7382,8 +8528,83 @@
       <c r="EJ15">
         <v>76</v>
       </c>
+      <c r="EK15">
+        <v>32</v>
+      </c>
+      <c r="EL15">
+        <v>37</v>
+      </c>
+      <c r="EM15">
+        <v>66</v>
+      </c>
+      <c r="EN15">
+        <v>76</v>
+      </c>
+      <c r="EO15">
+        <v>68</v>
+      </c>
+      <c r="EP15">
+        <v>47</v>
+      </c>
+      <c r="EQ15">
+        <v>41</v>
+      </c>
+      <c r="ER15">
+        <v>75</v>
+      </c>
+      <c r="ES15">
+        <v>18</v>
+      </c>
+      <c r="ET15">
+        <v>71</v>
+      </c>
+      <c r="EU15">
+        <v>89</v>
+      </c>
+      <c r="EV15">
+        <v>31</v>
+      </c>
+      <c r="EW15">
+        <v>33</v>
+      </c>
+      <c r="EX15">
+        <v>34</v>
+      </c>
+      <c r="EY15">
+        <v>27</v>
+      </c>
+      <c r="EZ15">
+        <v>38</v>
+      </c>
+      <c r="FA15">
+        <v>38.5</v>
+      </c>
+      <c r="FB15">
+        <v>56.4</v>
+      </c>
+      <c r="FC15">
+        <v>74.3</v>
+      </c>
+      <c r="FD15">
+        <v>43.6</v>
+      </c>
+      <c r="FE15">
+        <v>62.9</v>
+      </c>
+      <c r="FF15">
+        <v>66</v>
+      </c>
+      <c r="FG15">
+        <v>70</v>
+      </c>
+      <c r="FH15">
+        <v>28.7</v>
+      </c>
+      <c r="FI15">
+        <v>82.5</v>
+      </c>
     </row>
-    <row r="16" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -7804,8 +9025,83 @@
       <c r="EJ16">
         <v>65</v>
       </c>
+      <c r="EK16">
+        <v>45</v>
+      </c>
+      <c r="EL16">
+        <v>45</v>
+      </c>
+      <c r="EM16">
+        <v>70</v>
+      </c>
+      <c r="EN16">
+        <v>75</v>
+      </c>
+      <c r="EO16">
+        <v>63</v>
+      </c>
+      <c r="EP16">
+        <v>49</v>
+      </c>
+      <c r="EQ16">
+        <v>48</v>
+      </c>
+      <c r="ER16">
+        <v>70</v>
+      </c>
+      <c r="ES16">
+        <v>21</v>
+      </c>
+      <c r="ET16">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="EU16">
+        <v>86</v>
+      </c>
+      <c r="EV16">
+        <v>33</v>
+      </c>
+      <c r="EW16">
+        <v>31</v>
+      </c>
+      <c r="EX16">
+        <v>31</v>
+      </c>
+      <c r="EY16">
+        <v>22</v>
+      </c>
+      <c r="EZ16">
+        <v>33</v>
+      </c>
+      <c r="FA16">
+        <v>44.099999999999994</v>
+      </c>
+      <c r="FB16">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="FC16">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="FD16">
+        <v>48.7</v>
+      </c>
+      <c r="FE16">
+        <v>56</v>
+      </c>
+      <c r="FF16">
+        <v>51.5</v>
+      </c>
+      <c r="FG16">
+        <v>59.4</v>
+      </c>
+      <c r="FH16">
+        <v>21.5</v>
+      </c>
+      <c r="FI16">
+        <v>71.2</v>
+      </c>
     </row>
-    <row r="17" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -8226,8 +9522,83 @@
       <c r="EJ17">
         <v>73</v>
       </c>
+      <c r="EK17">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="EL17">
+        <v>56.000000000000007</v>
+      </c>
+      <c r="EM17">
+        <v>70</v>
+      </c>
+      <c r="EN17">
+        <v>86</v>
+      </c>
+      <c r="EO17">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="EP17">
+        <v>24</v>
+      </c>
+      <c r="EQ17">
+        <v>28.999999999999996</v>
+      </c>
+      <c r="ER17">
+        <v>63</v>
+      </c>
+      <c r="ES17">
+        <v>9</v>
+      </c>
+      <c r="ET17">
+        <v>67</v>
+      </c>
+      <c r="EU17">
+        <v>94</v>
+      </c>
+      <c r="EV17">
+        <v>44</v>
+      </c>
+      <c r="EW17">
+        <v>26</v>
+      </c>
+      <c r="EX17">
+        <v>20</v>
+      </c>
+      <c r="EY17">
+        <v>11</v>
+      </c>
+      <c r="EZ17">
+        <v>27</v>
+      </c>
+      <c r="FA17">
+        <v>30.099999999999998</v>
+      </c>
+      <c r="FB17">
+        <v>67.8</v>
+      </c>
+      <c r="FC17">
+        <v>69</v>
+      </c>
+      <c r="FD17">
+        <v>36.9</v>
+      </c>
+      <c r="FE17">
+        <v>53.3</v>
+      </c>
+      <c r="FF17">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="FG17">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="FH17">
+        <v>15.6</v>
+      </c>
+      <c r="FI17">
+        <v>84.7</v>
+      </c>
     </row>
-    <row r="18" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -8648,8 +10019,83 @@
       <c r="EJ18">
         <v>76</v>
       </c>
+      <c r="EK18">
+        <v>35</v>
+      </c>
+      <c r="EL18">
+        <v>41</v>
+      </c>
+      <c r="EM18">
+        <v>48</v>
+      </c>
+      <c r="EN18">
+        <v>76</v>
+      </c>
+      <c r="EO18">
+        <v>62</v>
+      </c>
+      <c r="EP18">
+        <v>22</v>
+      </c>
+      <c r="EQ18">
+        <v>27</v>
+      </c>
+      <c r="ER18">
+        <v>64</v>
+      </c>
+      <c r="ES18">
+        <v>28.999999999999996</v>
+      </c>
+      <c r="ET18">
+        <v>69</v>
+      </c>
+      <c r="EU18">
+        <v>83</v>
+      </c>
+      <c r="EV18">
+        <v>35</v>
+      </c>
+      <c r="EW18">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="EX18">
+        <v>33</v>
+      </c>
+      <c r="EY18">
+        <v>20</v>
+      </c>
+      <c r="EZ18">
+        <v>26</v>
+      </c>
+      <c r="FA18">
+        <v>30.700000000000003</v>
+      </c>
+      <c r="FB18">
+        <v>50.2</v>
+      </c>
+      <c r="FC18">
+        <v>58.2</v>
+      </c>
+      <c r="FD18">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="FE18">
+        <v>60.4</v>
+      </c>
+      <c r="FF18">
+        <v>54.2</v>
+      </c>
+      <c r="FG18">
+        <v>71.5</v>
+      </c>
+      <c r="FH18">
+        <v>22.8</v>
+      </c>
+      <c r="FI18">
+        <v>79.8</v>
+      </c>
     </row>
-    <row r="19" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -9070,8 +10516,83 @@
       <c r="EJ19">
         <v>84</v>
       </c>
+      <c r="EK19">
+        <v>50</v>
+      </c>
+      <c r="EL19">
+        <v>54</v>
+      </c>
+      <c r="EM19">
+        <v>60</v>
+      </c>
+      <c r="EN19">
+        <v>86</v>
+      </c>
+      <c r="EO19">
+        <v>74</v>
+      </c>
+      <c r="EP19">
+        <v>32</v>
+      </c>
+      <c r="EQ19">
+        <v>47</v>
+      </c>
+      <c r="ER19">
+        <v>70</v>
+      </c>
+      <c r="ES19">
+        <v>26</v>
+      </c>
+      <c r="ET19">
+        <v>67</v>
+      </c>
+      <c r="EU19">
+        <v>85</v>
+      </c>
+      <c r="EV19">
+        <v>49</v>
+      </c>
+      <c r="EW19">
+        <v>51</v>
+      </c>
+      <c r="EX19">
+        <v>42</v>
+      </c>
+      <c r="EY19">
+        <v>41</v>
+      </c>
+      <c r="EZ19">
+        <v>33</v>
+      </c>
+      <c r="FA19">
+        <v>29</v>
+      </c>
+      <c r="FB19">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="FC19">
+        <v>75.5</v>
+      </c>
+      <c r="FD19">
+        <v>58.8</v>
+      </c>
+      <c r="FE19">
+        <v>76.5</v>
+      </c>
+      <c r="FF19">
+        <v>77.400000000000006</v>
+      </c>
+      <c r="FG19">
+        <v>73</v>
+      </c>
+      <c r="FH19">
+        <v>24.5</v>
+      </c>
+      <c r="FI19">
+        <v>72.5</v>
+      </c>
     </row>
-    <row r="20" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -9492,8 +11013,83 @@
       <c r="EJ20">
         <v>74</v>
       </c>
+      <c r="EK20">
+        <v>80</v>
+      </c>
+      <c r="EL20">
+        <v>67</v>
+      </c>
+      <c r="EM20">
+        <v>76</v>
+      </c>
+      <c r="EN20">
+        <v>69</v>
+      </c>
+      <c r="EO20">
+        <v>87</v>
+      </c>
+      <c r="EP20">
+        <v>69</v>
+      </c>
+      <c r="EQ20">
+        <v>86</v>
+      </c>
+      <c r="ER20">
+        <v>87</v>
+      </c>
+      <c r="ES20">
+        <v>26</v>
+      </c>
+      <c r="ET20">
+        <v>73</v>
+      </c>
+      <c r="EU20">
+        <v>88</v>
+      </c>
+      <c r="EV20">
+        <v>36</v>
+      </c>
+      <c r="EW20">
+        <v>51</v>
+      </c>
+      <c r="EX20">
+        <v>35</v>
+      </c>
+      <c r="EY20">
+        <v>38</v>
+      </c>
+      <c r="EZ20">
+        <v>40</v>
+      </c>
+      <c r="FA20">
+        <v>29.3</v>
+      </c>
+      <c r="FB20">
+        <v>68.2</v>
+      </c>
+      <c r="FC20">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="FD20">
+        <v>41.2</v>
+      </c>
+      <c r="FE20">
+        <v>56.5</v>
+      </c>
+      <c r="FF20">
+        <v>54.5</v>
+      </c>
+      <c r="FG20">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="FH20">
+        <v>11.3</v>
+      </c>
+      <c r="FI20">
+        <v>80.7</v>
+      </c>
     </row>
-    <row r="21" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -9914,8 +11510,83 @@
       <c r="EJ21">
         <v>68</v>
       </c>
+      <c r="EK21">
+        <v>63</v>
+      </c>
+      <c r="EL21">
+        <v>62</v>
+      </c>
+      <c r="EM21">
+        <v>45</v>
+      </c>
+      <c r="EN21">
+        <v>85</v>
+      </c>
+      <c r="EO21">
+        <v>67</v>
+      </c>
+      <c r="EP21">
+        <v>30</v>
+      </c>
+      <c r="EQ21">
+        <v>38</v>
+      </c>
+      <c r="ER21">
+        <v>61</v>
+      </c>
+      <c r="ES21">
+        <v>13</v>
+      </c>
+      <c r="ET21">
+        <v>68</v>
+      </c>
+      <c r="EU21">
+        <v>90</v>
+      </c>
+      <c r="EV21">
+        <v>45</v>
+      </c>
+      <c r="EW21">
+        <v>42</v>
+      </c>
+      <c r="EX21">
+        <v>31</v>
+      </c>
+      <c r="EY21">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="EZ21">
+        <v>39</v>
+      </c>
+      <c r="FA21">
+        <v>27.9</v>
+      </c>
+      <c r="FB21">
+        <v>59.7</v>
+      </c>
+      <c r="FC21">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="FD21">
+        <v>46</v>
+      </c>
+      <c r="FE21">
+        <v>50.1</v>
+      </c>
+      <c r="FF21">
+        <v>50.4</v>
+      </c>
+      <c r="FG21">
+        <v>65.7</v>
+      </c>
+      <c r="FH21">
+        <v>9.7000000000000011</v>
+      </c>
+      <c r="FI21">
+        <v>70.7</v>
+      </c>
     </row>
-    <row r="22" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -10336,8 +12007,83 @@
       <c r="EJ22">
         <v>56.999999999999993</v>
       </c>
+      <c r="EK22">
+        <v>80</v>
+      </c>
+      <c r="EL22">
+        <v>79</v>
+      </c>
+      <c r="EM22">
+        <v>74</v>
+      </c>
+      <c r="EN22">
+        <v>90</v>
+      </c>
+      <c r="EO22">
+        <v>73</v>
+      </c>
+      <c r="EP22">
+        <v>25</v>
+      </c>
+      <c r="EQ22">
+        <v>46</v>
+      </c>
+      <c r="ER22">
+        <v>88</v>
+      </c>
+      <c r="ES22">
+        <v>11</v>
+      </c>
+      <c r="ET22">
+        <v>62</v>
+      </c>
+      <c r="EU22">
+        <v>93</v>
+      </c>
+      <c r="EV22">
+        <v>25</v>
+      </c>
+      <c r="EW22">
+        <v>54</v>
+      </c>
+      <c r="EX22">
+        <v>32</v>
+      </c>
+      <c r="EY22">
+        <v>13</v>
+      </c>
+      <c r="EZ22">
+        <v>21</v>
+      </c>
+      <c r="FA22">
+        <v>30.8</v>
+      </c>
+      <c r="FB22">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="FC22">
+        <v>74.5</v>
+      </c>
+      <c r="FD22">
+        <v>48.8</v>
+      </c>
+      <c r="FE22">
+        <v>69.3</v>
+      </c>
+      <c r="FF22">
+        <v>65.2</v>
+      </c>
+      <c r="FG22">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="FH22">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="FI22">
+        <v>88.5</v>
+      </c>
     </row>
-    <row r="23" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -10758,8 +12504,83 @@
       <c r="EJ23">
         <v>84</v>
       </c>
+      <c r="EK23">
+        <v>61</v>
+      </c>
+      <c r="EL23">
+        <v>44</v>
+      </c>
+      <c r="EM23">
+        <v>82</v>
+      </c>
+      <c r="EN23">
+        <v>70</v>
+      </c>
+      <c r="EO23">
+        <v>72</v>
+      </c>
+      <c r="EP23">
+        <v>49</v>
+      </c>
+      <c r="EQ23">
+        <v>64</v>
+      </c>
+      <c r="ER23">
+        <v>85</v>
+      </c>
+      <c r="ES23">
+        <v>38</v>
+      </c>
+      <c r="ET23">
+        <v>70</v>
+      </c>
+      <c r="EU23">
+        <v>94</v>
+      </c>
+      <c r="EV23">
+        <v>35</v>
+      </c>
+      <c r="EW23">
+        <v>64</v>
+      </c>
+      <c r="EX23">
+        <v>62</v>
+      </c>
+      <c r="EY23">
+        <v>23</v>
+      </c>
+      <c r="EZ23">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="FA23">
+        <v>24.7</v>
+      </c>
+      <c r="FB23">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="FC23">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="FD23">
+        <v>62.1</v>
+      </c>
+      <c r="FE23">
+        <v>60.6</v>
+      </c>
+      <c r="FF23">
+        <v>57.6</v>
+      </c>
+      <c r="FG23">
+        <v>59.6</v>
+      </c>
+      <c r="FH23">
+        <v>19.7</v>
+      </c>
+      <c r="FI23">
+        <v>71.2</v>
+      </c>
     </row>
-    <row r="24" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -11180,8 +13001,83 @@
       <c r="EJ24">
         <v>61</v>
       </c>
+      <c r="EK24">
+        <v>42</v>
+      </c>
+      <c r="EL24">
+        <v>39</v>
+      </c>
+      <c r="EM24">
+        <v>47</v>
+      </c>
+      <c r="EN24">
+        <v>73</v>
+      </c>
+      <c r="EO24">
+        <v>63</v>
+      </c>
+      <c r="EP24">
+        <v>41</v>
+      </c>
+      <c r="EQ24">
+        <v>53</v>
+      </c>
+      <c r="ER24">
+        <v>72</v>
+      </c>
+      <c r="ES24">
+        <v>35</v>
+      </c>
+      <c r="ET24">
+        <v>65</v>
+      </c>
+      <c r="EU24">
+        <v>81</v>
+      </c>
+      <c r="EV24">
+        <v>36</v>
+      </c>
+      <c r="EW24">
+        <v>34</v>
+      </c>
+      <c r="EX24">
+        <v>35</v>
+      </c>
+      <c r="EY24">
+        <v>23</v>
+      </c>
+      <c r="EZ24">
+        <v>44</v>
+      </c>
+      <c r="FA24">
+        <v>32.4</v>
+      </c>
+      <c r="FB24">
+        <v>45.8</v>
+      </c>
+      <c r="FC24">
+        <v>63.7</v>
+      </c>
+      <c r="FD24">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="FE24">
+        <v>52</v>
+      </c>
+      <c r="FF24">
+        <v>48.1</v>
+      </c>
+      <c r="FG24">
+        <v>67</v>
+      </c>
+      <c r="FH24">
+        <v>15.899999999999999</v>
+      </c>
+      <c r="FI24">
+        <v>60.4</v>
+      </c>
     </row>
-    <row r="25" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -11602,8 +13498,83 @@
       <c r="EJ25">
         <v>86</v>
       </c>
+      <c r="EK25">
+        <v>45</v>
+      </c>
+      <c r="EL25">
+        <v>61</v>
+      </c>
+      <c r="EM25">
+        <v>51</v>
+      </c>
+      <c r="EN25">
+        <v>82</v>
+      </c>
+      <c r="EO25">
+        <v>72</v>
+      </c>
+      <c r="EP25">
+        <v>46</v>
+      </c>
+      <c r="EQ25">
+        <v>56.999999999999993</v>
+      </c>
+      <c r="ER25">
+        <v>72</v>
+      </c>
+      <c r="ES25">
+        <v>19</v>
+      </c>
+      <c r="ET25">
+        <v>65</v>
+      </c>
+      <c r="EU25">
+        <v>87</v>
+      </c>
+      <c r="EV25">
+        <v>49</v>
+      </c>
+      <c r="EW25">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="EX25">
+        <v>48</v>
+      </c>
+      <c r="EY25">
+        <v>42</v>
+      </c>
+      <c r="EZ25">
+        <v>41</v>
+      </c>
+      <c r="FA25">
+        <v>30.9</v>
+      </c>
+      <c r="FB25">
+        <v>60.7</v>
+      </c>
+      <c r="FC25">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="FD25">
+        <v>49.1</v>
+      </c>
+      <c r="FE25">
+        <v>52.9</v>
+      </c>
+      <c r="FF25">
+        <v>50.9</v>
+      </c>
+      <c r="FG25">
+        <v>70.5</v>
+      </c>
+      <c r="FH25">
+        <v>18.099999999999998</v>
+      </c>
+      <c r="FI25">
+        <v>67.7</v>
+      </c>
     </row>
-    <row r="26" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -12024,8 +13995,83 @@
       <c r="EJ26">
         <v>70</v>
       </c>
+      <c r="EK26">
+        <v>65</v>
+      </c>
+      <c r="EL26">
+        <v>61</v>
+      </c>
+      <c r="EM26">
+        <v>63</v>
+      </c>
+      <c r="EN26">
+        <v>86</v>
+      </c>
+      <c r="EO26">
+        <v>66</v>
+      </c>
+      <c r="EP26">
+        <v>52</v>
+      </c>
+      <c r="EQ26">
+        <v>65</v>
+      </c>
+      <c r="ER26">
+        <v>84</v>
+      </c>
+      <c r="ES26">
+        <v>36</v>
+      </c>
+      <c r="ET26">
+        <v>44</v>
+      </c>
+      <c r="EU26">
+        <v>69</v>
+      </c>
+      <c r="EV26">
+        <v>38</v>
+      </c>
+      <c r="EW26">
+        <v>33</v>
+      </c>
+      <c r="EX26">
+        <v>53</v>
+      </c>
+      <c r="EY26">
+        <v>34</v>
+      </c>
+      <c r="EZ26">
+        <v>49</v>
+      </c>
+      <c r="FA26">
+        <v>41</v>
+      </c>
+      <c r="FB26">
+        <v>79</v>
+      </c>
+      <c r="FC26">
+        <v>71.8</v>
+      </c>
+      <c r="FD26">
+        <v>54.3</v>
+      </c>
+      <c r="FE26">
+        <v>72.5</v>
+      </c>
+      <c r="FF26">
+        <v>67.3</v>
+      </c>
+      <c r="FG26">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="FH26">
+        <v>15.6</v>
+      </c>
+      <c r="FI26">
+        <v>72.5</v>
+      </c>
     </row>
-    <row r="27" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -12446,8 +14492,83 @@
       <c r="EJ27">
         <v>70</v>
       </c>
+      <c r="EK27">
+        <v>30</v>
+      </c>
+      <c r="EL27">
+        <v>46</v>
+      </c>
+      <c r="EM27">
+        <v>52</v>
+      </c>
+      <c r="EN27">
+        <v>68</v>
+      </c>
+      <c r="EO27">
+        <v>66</v>
+      </c>
+      <c r="EP27">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="EQ27">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="ER27">
+        <v>68</v>
+      </c>
+      <c r="ES27">
+        <v>22</v>
+      </c>
+      <c r="ET27">
+        <v>63</v>
+      </c>
+      <c r="EU27">
+        <v>79</v>
+      </c>
+      <c r="EV27">
+        <v>46</v>
+      </c>
+      <c r="EW27">
+        <v>39</v>
+      </c>
+      <c r="EX27">
+        <v>39</v>
+      </c>
+      <c r="EY27">
+        <v>39</v>
+      </c>
+      <c r="EZ27">
+        <v>36</v>
+      </c>
+      <c r="FA27">
+        <v>35.5</v>
+      </c>
+      <c r="FB27">
+        <v>60.5</v>
+      </c>
+      <c r="FC27">
+        <v>73.8</v>
+      </c>
+      <c r="FD27">
+        <v>64</v>
+      </c>
+      <c r="FE27">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="FF27">
+        <v>67.099999999999994</v>
+      </c>
+      <c r="FG27">
+        <v>67.099999999999994</v>
+      </c>
+      <c r="FH27">
+        <v>28.9</v>
+      </c>
+      <c r="FI27">
+        <v>80.8</v>
+      </c>
     </row>
-    <row r="28" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -12868,8 +14989,83 @@
       <c r="EJ28">
         <v>56.999999999999993</v>
       </c>
+      <c r="EK28">
+        <v>41</v>
+      </c>
+      <c r="EL28">
+        <v>43</v>
+      </c>
+      <c r="EM28">
+        <v>54</v>
+      </c>
+      <c r="EN28">
+        <v>78</v>
+      </c>
+      <c r="EO28">
+        <v>62</v>
+      </c>
+      <c r="EP28">
+        <v>32</v>
+      </c>
+      <c r="EQ28">
+        <v>42</v>
+      </c>
+      <c r="ER28">
+        <v>63</v>
+      </c>
+      <c r="ES28">
+        <v>22</v>
+      </c>
+      <c r="ET28">
+        <v>66</v>
+      </c>
+      <c r="EU28">
+        <v>90</v>
+      </c>
+      <c r="EV28">
+        <v>32</v>
+      </c>
+      <c r="EW28">
+        <v>35</v>
+      </c>
+      <c r="EX28">
+        <v>23</v>
+      </c>
+      <c r="EY28">
+        <v>18</v>
+      </c>
+      <c r="EZ28">
+        <v>30</v>
+      </c>
+      <c r="FA28">
+        <v>31.7</v>
+      </c>
+      <c r="FB28">
+        <v>48.4</v>
+      </c>
+      <c r="FC28">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="FD28">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="FE28">
+        <v>37.4</v>
+      </c>
+      <c r="FF28">
+        <v>41.9</v>
+      </c>
+      <c r="FG28">
+        <v>58.6</v>
+      </c>
+      <c r="FH28">
+        <v>16.7</v>
+      </c>
+      <c r="FI28">
+        <v>63.2</v>
+      </c>
     </row>
-    <row r="29" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -13290,8 +15486,83 @@
       <c r="EJ29">
         <v>52</v>
       </c>
+      <c r="EK29">
+        <v>26</v>
+      </c>
+      <c r="EL29">
+        <v>28.999999999999996</v>
+      </c>
+      <c r="EM29">
+        <v>42</v>
+      </c>
+      <c r="EN29">
+        <v>85</v>
+      </c>
+      <c r="EO29">
+        <v>59</v>
+      </c>
+      <c r="EP29">
+        <v>26</v>
+      </c>
+      <c r="EQ29">
+        <v>46</v>
+      </c>
+      <c r="ER29">
+        <v>65</v>
+      </c>
+      <c r="ES29">
+        <v>15</v>
+      </c>
+      <c r="ET29">
+        <v>63</v>
+      </c>
+      <c r="EU29">
+        <v>86</v>
+      </c>
+      <c r="EV29">
+        <v>35</v>
+      </c>
+      <c r="EW29">
+        <v>33</v>
+      </c>
+      <c r="EX29">
+        <v>37</v>
+      </c>
+      <c r="EY29">
+        <v>23</v>
+      </c>
+      <c r="EZ29">
+        <v>42</v>
+      </c>
+      <c r="FA29">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="FB29">
+        <v>52.9</v>
+      </c>
+      <c r="FC29">
+        <v>65.2</v>
+      </c>
+      <c r="FD29">
+        <v>46.4</v>
+      </c>
+      <c r="FE29">
+        <v>53.1</v>
+      </c>
+      <c r="FF29">
+        <v>50.6</v>
+      </c>
+      <c r="FG29">
+        <v>62.2</v>
+      </c>
+      <c r="FH29">
+        <v>24.6</v>
+      </c>
+      <c r="FI29">
+        <v>71</v>
+      </c>
     </row>
-    <row r="30" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -13712,8 +15983,83 @@
       <c r="EJ30">
         <v>83</v>
       </c>
+      <c r="EK30">
+        <v>66</v>
+      </c>
+      <c r="EL30">
+        <v>54</v>
+      </c>
+      <c r="EM30">
+        <v>67</v>
+      </c>
+      <c r="EN30">
+        <v>78</v>
+      </c>
+      <c r="EO30">
+        <v>86</v>
+      </c>
+      <c r="EP30">
+        <v>47</v>
+      </c>
+      <c r="EQ30">
+        <v>72</v>
+      </c>
+      <c r="ER30">
+        <v>82</v>
+      </c>
+      <c r="ES30">
+        <v>31</v>
+      </c>
+      <c r="ET30">
+        <v>74</v>
+      </c>
+      <c r="EU30">
+        <v>89</v>
+      </c>
+      <c r="EV30">
+        <v>48</v>
+      </c>
+      <c r="EW30">
+        <v>44</v>
+      </c>
+      <c r="EX30">
+        <v>54</v>
+      </c>
+      <c r="EY30">
+        <v>34</v>
+      </c>
+      <c r="EZ30">
+        <v>39</v>
+      </c>
+      <c r="FA30">
+        <v>29.9</v>
+      </c>
+      <c r="FB30">
+        <v>66.3</v>
+      </c>
+      <c r="FC30">
+        <v>69</v>
+      </c>
+      <c r="FD30">
+        <v>48.1</v>
+      </c>
+      <c r="FE30">
+        <v>69.8</v>
+      </c>
+      <c r="FF30">
+        <v>62</v>
+      </c>
+      <c r="FG30">
+        <v>54.7</v>
+      </c>
+      <c r="FH30">
+        <v>17.099999999999998</v>
+      </c>
+      <c r="FI30">
+        <v>79.5</v>
+      </c>
     </row>
-    <row r="31" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:165" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -14134,8 +16480,83 @@
       <c r="EJ31">
         <v>76</v>
       </c>
+      <c r="EK31">
+        <v>76</v>
+      </c>
+      <c r="EL31">
+        <v>59</v>
+      </c>
+      <c r="EM31">
+        <v>75</v>
+      </c>
+      <c r="EN31">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="EO31">
+        <v>89</v>
+      </c>
+      <c r="EP31">
+        <v>67</v>
+      </c>
+      <c r="EQ31">
+        <v>87</v>
+      </c>
+      <c r="ER31">
+        <v>92</v>
+      </c>
+      <c r="ES31">
+        <v>26</v>
+      </c>
+      <c r="ET31">
+        <v>72</v>
+      </c>
+      <c r="EU31">
+        <v>96</v>
+      </c>
+      <c r="EV31">
+        <v>34</v>
+      </c>
+      <c r="EW31">
+        <v>54</v>
+      </c>
+      <c r="EX31">
+        <v>67</v>
+      </c>
+      <c r="EY31">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="EZ31">
+        <v>53</v>
+      </c>
+      <c r="FA31">
+        <v>32.1</v>
+      </c>
+      <c r="FB31">
+        <v>59.6</v>
+      </c>
+      <c r="FC31">
+        <v>71.8</v>
+      </c>
+      <c r="FD31">
+        <v>52.9</v>
+      </c>
+      <c r="FE31">
+        <v>63.3</v>
+      </c>
+      <c r="FF31">
+        <v>56.9</v>
+      </c>
+      <c r="FG31">
+        <v>46.4</v>
+      </c>
+      <c r="FH31">
+        <v>21.7</v>
+      </c>
+      <c r="FI31">
+        <v>70.3</v>
+      </c>
     </row>
-    <row r="32" spans="1:140" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:165" x14ac:dyDescent="0.25">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -14166,7 +16587,8 @@
       <c r="AL32" s="1"/>
       <c r="AM32" s="1"/>
     </row>
-    <row r="41" spans="50:72" x14ac:dyDescent="0.25">
+    <row r="41" spans="49:71" x14ac:dyDescent="0.25">
+      <c r="AW41" s="2"/>
       <c r="AX41" s="2"/>
       <c r="AY41" s="2"/>
       <c r="AZ41" s="2"/>
@@ -14189,7 +16611,6 @@
       <c r="BQ41" s="2"/>
       <c r="BR41" s="2"/>
       <c r="BS41" s="2"/>
-      <c r="BT41" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
